--- a/results/benchmark_results.xlsx
+++ b/results/benchmark_results.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T04:04:54+00:00</t>
+          <t>2026-09-16T04:33:10+00:00</t>
         </is>
       </c>
     </row>

--- a/results/benchmark_results.xlsx
+++ b/results/benchmark_results.xlsx
@@ -8,28 +8,30 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summarization" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hallucination" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CrossLingual" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SurfaceFacts" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Usage" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Judge" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runs" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summarization" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hallucination" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CrossLingual" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SurfaceFacts" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Usage" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Judge" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runs" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leaderboard'!$A$1:$AK$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summarization'!$A$1:$P$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Hallucination'!$A$1:$O$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Classification'!$A$1:$I$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'CrossLingual'!$A$1:$M$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'SurfaceFacts'!$A$1:$L$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Cost'!$A$1:$S$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Usage'!$A$1:$M$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Judge'!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Runs'!$A$1:$T$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Legend'!$A$1:$D$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Leaderboard'!$A$1:$AK$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Summarization'!$A$1:$P$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Hallucination'!$A$1:$O$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Classification'!$A$1:$I$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'CrossLingual'!$A$1:$M$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'SurfaceFacts'!$A$1:$L$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Cost'!$A$1:$S$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Usage'!$A$1:$M$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Judge'!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Runs'!$A$1:$T$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -512,7 +514,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16T04:33:10+00:00</t>
+          <t>2026-09-16T04:55:22+00:00</t>
         </is>
       </c>
     </row>
@@ -601,6 +603,34 @@
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Mean the metric was not computed (e.g. BERTScore extra not installed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Metric directions</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>↑ 높을수록 좋음 · ↓ 낮을수록 좋음 · — 좋고 나쁨이 아니라 해석용</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Legend sheet</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Explains every metric column: what it means and which way is better.</t>
         </is>
       </c>
     </row>
@@ -610,6 +640,778 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>display_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>successful_cases</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>prompt_tokens</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>cached_tokens</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>cache_write_tokens</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>completion_tokens</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>reasoning_tokens</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>total_tokens</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>cache_hits</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>cache_misses</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>openrouter_api_calls</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>openrouter_http_attempts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-v4-flash-0731</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Flash 0731</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>1190712</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>369477</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>63519</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>1254231</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>google/gemini-2.5-flash-lite</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Gemini 2.5 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>1097914</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>54986</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>1152900</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>google/gemini-3.1-flash-lite</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Gemini 3.1 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1098022</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>55664</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1153686</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>1217</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>1217</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mistralai/ministral-14b-2512</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ministral 3 14B</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1092316</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>295936</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>71944</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1164260</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mistralai/ministral-3b-2512</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ministral 3 3B</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1092316</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>318592</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>69602</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>1161918</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mistralai/ministral-8b-2512</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ministral 3 8B</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1092316</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>299392</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>71698</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>1164014</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mistralai/mistral-small-2603</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mistral Small 4</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1107916</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>183856</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>62923</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>1170839</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>openai/gpt-4.1-nano</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GPT-4.1 Nano</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1108245</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>36224</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>55419</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>1163664</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>openai/gpt-5-nano</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GPT-5 Nano</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1106945</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>40320</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>548399</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>433920</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1655344</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>openai/gpt-5.4-nano</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GPT-5.4 Nano</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1106945</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>75745</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>1182690</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>openai/gpt-5.6-luna</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Luna</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1106945</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>458921</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>55276</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>1162221</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Qwen3 30B A3B Instruct 2507</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1213604</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>102934</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>72595</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>1286199</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>qwen/qwen3.7-flash</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Flash</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1061596</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>24960</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>51608</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>1113204</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>qwen/qwen3.8-flash</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Qwen3.8 Flash</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1061596</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>265984</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>52179</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>1113775</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1293055</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>104384</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>119092</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>35855</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>1412147</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M16"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -634,7 +1436,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -649,7 +1451,7 @@
     <col width="27" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="46" customWidth="1" min="10" max="10"/>
@@ -662,7 +1464,7 @@
     <col width="46" customWidth="1" min="17" max="17"/>
     <col width="46" customWidth="1" min="18" max="18"/>
     <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="46" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1415,22 +2217,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ABORTED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>run-20260916T032329-e99b731d</t>
+          <t>run-20260916T044051-1b0d71da</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:30+00:00</t>
+          <t>2026-09-16T04:51:21+00:00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:29+00:00</t>
+          <t>2026-09-16T04:40:51+00:00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1438,8 +2240,14 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -1485,11 +2293,7 @@
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>10 consecutive failures (limit 10); aborting before the rest of the run; [16x] Reasoning is mandatory for this endpoint and cannot be disabled.; Nothing was stored for the cases that were skipped, so a re-run picks them up normally once the cause is fixed.</t>
-        </is>
-      </c>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1899,22 +2703,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ABORTED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>run-20260916T034332-3a35b9e6</t>
+          <t>run-20260916T044139-f5eda9f3</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:43:32+00:00</t>
+          <t>2026-09-16T04:51:13+00:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-16T03:43:32+00:00</t>
+          <t>2026-09-16T04:41:39+00:00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1922,8 +2726,14 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
+        </is>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -1969,11 +2779,7 @@
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>10 consecutive failures (limit 10); aborting before the rest of the run; [17x] Reasoning is mandatory for this endpoint and cannot be disabled.; Nothing was stored for the cases that were skipped, so a re-run picks them up normally once the cause is fixed.</t>
-        </is>
-      </c>
+      <c r="T16" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:T16"/>
@@ -1982,6 +2788,1193 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>지표</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>방향</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>의미</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Summarization</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cases</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>채점 대상 케이스 수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Summarization</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ROUGE-Lsum</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>참조 요약과의 최장 공통 부분열 기반 F1 (0~1). 문장 단위로 계산. 한국어는 문자 단위 토큰화라 영어 값과 직접 비교 불가.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Summarization</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>chrF++</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>문자 n-gram + 단어 bigram F-score (0~100). 어형 변화에 강해 한국어에 비교적 공정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Summarization</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BERTScore</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>다국어 임베딩 기반 의미 유사도 F1 (0~1). 표현이 달라도 뜻이 같으면 점수를 줍니다. 선택 설치.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Summarization</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Surface facts</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>요약에서 뽑은 표면적 사실 중 원문에서 확인되는 비율 (0~1). 진단 지표.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Summarization</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Compression</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>출력 길이 ÷ 원문 길이. 낮으면 압축적, 높으면 장황. 낮다고 무조건 좋은 것은 아닙니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Summarization</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Out tokens</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>평균 출력 길이(추정 토큰).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Summarization</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Empty</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>빈 출력 비율.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Summarization</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Refusal</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>거부 응답 비율. 빈 출력과 거부는 분모에서 빼지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Hallucination</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>`OK` 또는 `SKIPPED`(해당 언어 데이터 미준비).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Hallucination</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cases</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>케이스 수. 문서 수 × 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Hallucination</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>전체 정답률 (0~1). 레이블이 반반이므로 0.5가 무작위 수준.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Hallucination</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Macro-F1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>두 레이블 F1의 단순 평균 (0~1). 한쪽 레이블만 찍는 모델을 걸러냅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Hallucination</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Halu P</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>HALLUCINATED 라고 답한 것 중 실제로 맞은 비율. 낮으면 멀쩡한 요약을 환각이라고 의심.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Hallucination</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Halu R</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>실제 HALLUCINATED 중 잡아낸 비율. 낮으면 환각을 놓침.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Hallucination</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Halu F1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Halu P 와 Halu R 의 조화평균. 환각 탐지 성능의 대표값.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Hallucination</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Supported R</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>실제 SUPPORTED 중 맞힌 비율. 이 값만 낮으면 과도하게 의심하는 모델.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Hallucination</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>레이블로 파싱할 수 없는 출력 비율. **오답으로 계산됩니다.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>`en` / `ko` / `overall`(두 언어 합산).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cases</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>분류한 발화 수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>정답률 (0~1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Macro-F1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>60개 인텐트별 F1의 평균 (0~1). 드문 인텐트를 무시하는 모델에 불리하게 작동합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Invalid</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>형식을 못 지켜 답을 못 읽은 비율. 오답으로 계산됩니다. 배치 형식을 못 지키면 여기가 올라갑니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CrossLingual</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Pairs</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>비교한 EN/KO 쌍의 수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CrossLingual</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Consistency</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>두 언어에서 정오답이 일치한 비율(둘 다 맞음 + 둘 다 틀림). 높을수록 언어에 따라 흔들리지 않음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CrossLingual</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Pred. agreement</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>정답 여부와 무관하게 **같은 인텐트** 를 예측한 비율. 정확도와 분리된 안정성 지표.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CrossLingual</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Both correct</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>두 언어 모두 맞힌 비율.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CrossLingual</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>EN only</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>영어만 맞힌 비율. 높으면 한국어가 약함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CrossLingual</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>KO only</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>한국어만 맞힌 비율. 높으면 영어가 약함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CrossLingual</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Both wrong</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>두 언어 모두 틀린 비율.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SurfaceFacts</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Facts</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>요약에서 추출된 사실의 총 개수. 적으면 아래 비율의 신뢰도가 낮습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SurfaceFacts</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>그중 원문에서 확인된 비율 (0~1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SurfaceFacts</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>원문에 없는 숫자 건수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SurfaceFacts</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Percent</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>원문과 다른 백분율 건수. (원문 12% → 요약 21% 같은 경우)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SurfaceFacts</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>원문에 없는 날짜 건수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SurfaceFacts</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>원문에 없는 금액 건수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SurfaceFacts</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>원문에 없는 고유명사 건수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Summarization / Hallucination / Classification</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>벤치마크별 누적 청구액.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Retry/error</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>실패했지만 과금된 시도의 합. 0이 아니면 재시도가 돈을 쓴 것.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Judge</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>LLM-as-a-Judge 비용. 기본 예산과 별도로 집계합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>이 모델 캐시를 만드는 데 지금까지 지불한 총액.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Fresh this run</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>마지막 실행에서 **새로** 청구된 금액. 캐시가 다 맞으면 $0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Cache savings</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>캐시 덕분에 다시 내지 않은 금액.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Cases</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>성공적으로 저장된 케이스 수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Prompt / Completion / Total</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>입력·출력·합계 토큰.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Cached</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>프롬프트 캐시로 할인된 입력 토큰.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>thinking 토큰. thinking 을 끌 수 없는 모델만 0이 아닙니다. 과금 대상입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>API calls</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>실제로 OpenRouter 로 나간 요청 수. 재실행에서 0이면 캐시가 완전히 맞은 것.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Cache hits</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>캐시로 처리해 요청하지 않은 수.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Judge</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Self-judge</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>`예` 면 모델이 자기 출력을 채점한 것. 신뢰하지 마세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Judge</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Factual / Coverage / Conciseness / Overall</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>각 1~5 정수 채점의 평균.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Judge</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Judge cost</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>judge 호출의 실제 청구액.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D53"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2711,17 +4704,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>deepseek/deepseek-v4-flash-0731</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2730,13 +4723,13 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.055</v>
+        <v>0.05</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2745,40 +4738,40 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-16T03:43:32+00:00</t>
+          <t>2026-09-16T04:40:49+00:00</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.1602129689146955</v>
+        <v>0.1299020365576643</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2187402179219718</v>
+        <v>0.1992896265281343</v>
       </c>
       <c r="L6" t="n">
-        <v>26.38968843606158</v>
+        <v>23.01138546667206</v>
       </c>
       <c r="M6" t="n">
-        <v>13.34734148800115</v>
+        <v>11.48522300950568</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" s="4" t="n">
-        <v>0.8983156581409857</v>
+        <v>0.949200376293509</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.958904109589041</v>
+        <v>0.9549738219895288</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.7204030226700252</v>
+        <v>0.6814814814814814</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.6525821596244131</v>
+        <v>0.328125</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.7225</v>
+        <v>0.6775</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.63</v>
+        <v>0.57</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -2786,46 +4779,46 @@
         </is>
       </c>
       <c r="W6" t="n">
-        <v>0.803</v>
+        <v>0.842</v>
       </c>
       <c r="X6" t="n">
-        <v>0.802</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.7737251717218584</v>
+        <v>0.8314865753296514</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.7760490357248214</v>
+        <v>0.8034449936517111</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>0.8025</v>
+        <v>0.8285</v>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>0.7750244596849166</v>
+        <v>0.8179267929293625</v>
       </c>
       <c r="AC6" s="4" t="n">
-        <v>0.851</v>
+        <v>0.863</v>
       </c>
       <c r="AD6" s="5" t="n">
-        <v>1190712</v>
+        <v>1106945</v>
       </c>
       <c r="AE6" s="5" t="n">
-        <v>63519</v>
+        <v>548399</v>
       </c>
       <c r="AF6" s="5" t="n">
-        <v>369477</v>
+        <v>40320</v>
       </c>
       <c r="AG6" s="5" t="n">
-        <v>0</v>
+        <v>433920</v>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>0.087699192003</v>
+        <v>0.27289245</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.08769919200300014</v>
+        <v>0.2728924500000001</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>0</v>
@@ -2834,17 +4827,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>z-ai/glm-5.3-flash</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GLM 5.3 Flash</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>z-ai</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2853,12 +4846,14 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.04815</v>
+        <v>0.1</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.19305</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
+        <v>0.3333</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0.02</v>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>openrouter</t>
@@ -2866,40 +4861,40 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-16T03:34:40+00:00</t>
+          <t>2026-09-16T04:41:38+00:00</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.1416464777859414</v>
+        <v>0.1442957203978096</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2093037662697218</v>
+        <v>0.2059639679861038</v>
       </c>
       <c r="L7" t="n">
-        <v>24.38575174114155</v>
+        <v>24.60010668803035</v>
       </c>
       <c r="M7" t="n">
-        <v>12.78420991940304</v>
+        <v>13.49752283326942</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" s="4" t="n">
-        <v>0.9091375770020534</v>
+        <v>0.9221978021978022</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.9739027283511269</v>
+        <v>0.9633928571428572</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.6089743589743589</v>
+        <v>0.72544080604534</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.4191176470588235</v>
+        <v>0.5555555555555557</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.695</v>
+        <v>0.7275</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.605</v>
+        <v>0.64</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2907,46 +4902,46 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.858</v>
       </c>
       <c r="X7" t="n">
-        <v>0.794</v>
+        <v>0.797</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>0.7992131261387427</v>
+        <v>0.846487306452871</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.7717528819109728</v>
+        <v>0.7859849948864567</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>0.8015</v>
+        <v>0.8275</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>0.7855676169719019</v>
+        <v>0.8155753958777252</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>0.865</v>
+        <v>0.867</v>
       </c>
       <c r="AD7" s="5" t="n">
-        <v>1213604</v>
+        <v>1293055</v>
       </c>
       <c r="AE7" s="5" t="n">
-        <v>72595</v>
+        <v>119092</v>
       </c>
       <c r="AF7" s="5" t="n">
-        <v>102934</v>
+        <v>104384</v>
       </c>
       <c r="AG7" s="5" t="n">
-        <v>0</v>
+        <v>35855</v>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>0.12323393625</v>
+        <v>0.21471714348</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>0.1232339362500001</v>
+        <v>0.2147171434799998</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>0</v>
@@ -2955,17 +4950,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>deepseek/deepseek-v4-flash-0731</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2974,13 +4969,13 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.03</v>
+        <v>0.055</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2989,40 +4984,40 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-16T03:31:23+00:00</t>
+          <t>2026-09-16T03:43:32+00:00</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.1608350962342315</v>
+        <v>0.1602129689146955</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2302580020788956</v>
+        <v>0.2187402179219718</v>
       </c>
       <c r="L8" t="n">
-        <v>26.04951109641535</v>
+        <v>26.38968843606158</v>
       </c>
       <c r="M8" t="n">
-        <v>13.75572799407668</v>
+        <v>13.34734148800115</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" s="4" t="n">
-        <v>0.8816067653276956</v>
+        <v>0.8983156581409857</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.947463768115942</v>
+        <v>0.958904109589041</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.6589595375722543</v>
+        <v>0.7204030226700252</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.5407166123778501</v>
+        <v>0.6525821596244131</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.705</v>
+        <v>0.7225</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.6475</v>
+        <v>0.63</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -3030,46 +5025,46 @@
         </is>
       </c>
       <c r="W8" t="n">
-        <v>0.796</v>
+        <v>0.803</v>
       </c>
       <c r="X8" t="n">
-        <v>0.76</v>
+        <v>0.802</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>0.7792340968020122</v>
+        <v>0.7737251717218584</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>0.7439524644750251</v>
+        <v>0.7760490357248214</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>0.778</v>
+        <v>0.8025</v>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>0.7614406146917927</v>
+        <v>0.7750244596849166</v>
       </c>
       <c r="AC8" s="4" t="n">
-        <v>0.832</v>
+        <v>0.851</v>
       </c>
       <c r="AD8" s="5" t="n">
-        <v>1061596</v>
+        <v>1190712</v>
       </c>
       <c r="AE8" s="5" t="n">
-        <v>51608</v>
+        <v>63519</v>
       </c>
       <c r="AF8" s="5" t="n">
-        <v>24960</v>
+        <v>369477</v>
       </c>
       <c r="AG8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>0.03791827</v>
+        <v>0.087699192003</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.03791826999999996</v>
+        <v>0.08769919200300014</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>0</v>
@@ -3078,17 +5073,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mistralai</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3097,14 +5092,12 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.2</v>
+        <v>0.04815</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.19305</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>openrouter</t>
@@ -3112,40 +5105,40 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-16T03:10:41+00:00</t>
+          <t>2026-09-16T03:34:40+00:00</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.1340643496794257</v>
+        <v>0.1416464777859414</v>
       </c>
       <c r="K9" t="n">
-        <v>0.200848621976299</v>
+        <v>0.2093037662697218</v>
       </c>
       <c r="L9" t="n">
-        <v>23.15600037313629</v>
+        <v>24.38575174114155</v>
       </c>
       <c r="M9" t="n">
-        <v>12.32917653667287</v>
+        <v>12.78420991940304</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" s="4" t="n">
-        <v>0.8982440342188204</v>
+        <v>0.9091375770020534</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.9363636363636364</v>
+        <v>0.9739027283511269</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.7163461538461539</v>
+        <v>0.6089743589743589</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.683291770573566</v>
+        <v>0.4191176470588235</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.705</v>
+        <v>0.695</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.6825</v>
+        <v>0.605</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -3153,46 +5146,46 @@
         </is>
       </c>
       <c r="W9" t="n">
-        <v>0.78</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>0.744</v>
+        <v>0.794</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>0.7603515978750895</v>
+        <v>0.7992131261387427</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.7113942857254609</v>
+        <v>0.7717528819109728</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>0.762</v>
+        <v>0.8015</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>0.736163325053324</v>
+        <v>0.7855676169719019</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>0.824</v>
+        <v>0.865</v>
       </c>
       <c r="AD9" s="5" t="n">
-        <v>1092316</v>
+        <v>1213604</v>
       </c>
       <c r="AE9" s="5" t="n">
-        <v>71944</v>
+        <v>72595</v>
       </c>
       <c r="AF9" s="5" t="n">
-        <v>295936</v>
+        <v>102934</v>
       </c>
       <c r="AG9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>0.17958352</v>
+        <v>0.12323393625</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>0.1795835200000001</v>
+        <v>0.1232339362500001</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>0</v>
@@ -3201,17 +5194,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mistralai</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3220,13 +5213,13 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.015</v>
+        <v>0.006</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -3235,40 +5228,40 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-16T03:15:02+00:00</t>
+          <t>2026-09-16T03:31:23+00:00</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.1338576862477163</v>
+        <v>0.1608350962342315</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2022785739193924</v>
+        <v>0.2302580020788956</v>
       </c>
       <c r="L10" t="n">
-        <v>23.2893881252992</v>
+        <v>26.04951109641535</v>
       </c>
       <c r="M10" t="n">
-        <v>12.28128440018327</v>
+        <v>13.75572799407668</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" s="4" t="n">
-        <v>0.8798944126704795</v>
+        <v>0.8816067653276956</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.9474768280123584</v>
+        <v>0.947463768115942</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.6366366366366367</v>
+        <v>0.6589595375722543</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.5857988165680473</v>
+        <v>0.5407166123778501</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.6975</v>
+        <v>0.705</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.65</v>
+        <v>0.6475</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3276,46 +5269,46 @@
         </is>
       </c>
       <c r="W10" t="n">
-        <v>0.738</v>
+        <v>0.796</v>
       </c>
       <c r="X10" t="n">
-        <v>0.737</v>
+        <v>0.76</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.7285750142849275</v>
+        <v>0.7792340968020122</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.712693713084553</v>
+        <v>0.7439524644750251</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>0.7375</v>
+        <v>0.778</v>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>0.7216311867724771</v>
+        <v>0.7614406146917927</v>
       </c>
       <c r="AC10" s="4" t="n">
-        <v>0.763</v>
+        <v>0.832</v>
       </c>
       <c r="AD10" s="5" t="n">
-        <v>1092316</v>
+        <v>1061596</v>
       </c>
       <c r="AE10" s="5" t="n">
-        <v>71698</v>
+        <v>51608</v>
       </c>
       <c r="AF10" s="5" t="n">
-        <v>299392</v>
+        <v>24960</v>
       </c>
       <c r="AG10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AH10" s="3" t="n">
-        <v>0.13418418</v>
+        <v>0.03791827</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>0.1341841799999999</v>
+        <v>0.03791826999999996</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>0</v>
@@ -3324,17 +5317,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>mistralai</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3346,7 +5339,7 @@
         <v>0.2</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.25</v>
+        <v>0.2</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0.02</v>
@@ -3358,40 +5351,40 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-16T03:20:07+00:00</t>
+          <t>2026-09-16T03:10:41+00:00</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.1303590348428198</v>
+        <v>0.1340643496794257</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1872998825564791</v>
+        <v>0.200848621976299</v>
       </c>
       <c r="L11" t="n">
-        <v>23.22067206524886</v>
+        <v>23.15600037313629</v>
       </c>
       <c r="M11" t="n">
-        <v>11.95596092668423</v>
+        <v>12.32917653667287</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" s="4" t="n">
-        <v>0.961978928080623</v>
+        <v>0.8982440342188204</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.9586330935251799</v>
+        <v>0.9363636363636364</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.6149068322981366</v>
+        <v>0.7163461538461539</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.2382978723404255</v>
+        <v>0.683291770573566</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.705</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.5525</v>
+        <v>0.6825</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3399,46 +5392,46 @@
         </is>
       </c>
       <c r="W11" t="n">
-        <v>0.715</v>
+        <v>0.78</v>
       </c>
       <c r="X11" t="n">
-        <v>0.661</v>
+        <v>0.744</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.7079848008862988</v>
+        <v>0.7603515978750895</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.6593342425290085</v>
+        <v>0.7113942857254609</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.762</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>0.6845822094887644</v>
+        <v>0.736163325053324</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>0.718</v>
+        <v>0.824</v>
       </c>
       <c r="AD11" s="5" t="n">
-        <v>1106945</v>
+        <v>1092316</v>
       </c>
       <c r="AE11" s="5" t="n">
-        <v>75745</v>
+        <v>71944</v>
       </c>
       <c r="AF11" s="5" t="n">
-        <v>0</v>
+        <v>295936</v>
       </c>
       <c r="AG11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AH11" s="3" t="n">
-        <v>0.31607025</v>
+        <v>0.17958352</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AJ11" s="3" t="n">
-        <v>0.3160702499999996</v>
+        <v>0.1795835200000001</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>0</v>
@@ -3447,12 +5440,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3469,7 +5462,7 @@
         <v>0.15</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0.015</v>
@@ -3481,37 +5474,37 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-16T03:07:59+00:00</t>
+          <t>2026-09-16T03:15:02+00:00</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.1486748430163934</v>
+        <v>0.1338576862477163</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2158566833442461</v>
+        <v>0.2022785739193924</v>
       </c>
       <c r="L12" t="n">
-        <v>24.85170132045256</v>
+        <v>23.2893881252992</v>
       </c>
       <c r="M12" t="n">
-        <v>12.57729783101797</v>
+        <v>12.28128440018327</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" s="4" t="n">
-        <v>0.9259462424574877</v>
+        <v>0.8798944126704795</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.9627450980392157</v>
+        <v>0.9474768280123584</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.7247956403269755</v>
+        <v>0.6366366366366367</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.6195652173913043</v>
+        <v>0.5857988165680473</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.6975</v>
       </c>
       <c r="U12" s="4" t="n">
         <v>0.65</v>
@@ -3522,46 +5515,46 @@
         </is>
       </c>
       <c r="W12" t="n">
-        <v>0.509</v>
+        <v>0.738</v>
       </c>
       <c r="X12" t="n">
-        <v>0.711</v>
+        <v>0.737</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.5867378280355483</v>
+        <v>0.7285750142849275</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.7031769757373104</v>
+        <v>0.712693713084553</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>0.61</v>
+        <v>0.7375</v>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>0.6504937686437986</v>
+        <v>0.7216311867724771</v>
       </c>
       <c r="AC12" s="4" t="n">
-        <v>0.7</v>
+        <v>0.763</v>
       </c>
       <c r="AD12" s="5" t="n">
-        <v>1107916</v>
+        <v>1092316</v>
       </c>
       <c r="AE12" s="5" t="n">
-        <v>62923</v>
+        <v>71698</v>
       </c>
       <c r="AF12" s="5" t="n">
-        <v>183856</v>
+        <v>299392</v>
       </c>
       <c r="AG12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AH12" s="3" t="n">
-        <v>0.1964076975</v>
+        <v>0.13418418</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AJ12" s="3" t="n">
-        <v>0.1964076975000001</v>
+        <v>0.1341841799999999</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>0</v>
@@ -3570,17 +5563,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mistralai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3589,13 +5582,13 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.1</v>
+        <v>1.25</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -3604,40 +5597,40 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-16T03:17:56+00:00</t>
+          <t>2026-09-16T03:20:07+00:00</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0.1344392234965607</v>
+        <v>0.1303590348428198</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1976921128927562</v>
+        <v>0.1872998825564791</v>
       </c>
       <c r="L13" t="n">
-        <v>23.21465695587321</v>
+        <v>23.22067206524886</v>
       </c>
       <c r="M13" t="n">
-        <v>11.65156743434614</v>
+        <v>11.95596092668423</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" s="4" t="n">
-        <v>0.886284289276808</v>
+        <v>0.961978928080623</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.9119420989143546</v>
+        <v>0.9586330935251799</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.6757493188010899</v>
+        <v>0.6149068322981366</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.5591939546599498</v>
+        <v>0.2382978723404255</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.7025</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.5625</v>
+        <v>0.5525</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3645,46 +5638,46 @@
         </is>
       </c>
       <c r="W13" t="n">
-        <v>0.465</v>
+        <v>0.715</v>
       </c>
       <c r="X13" t="n">
-        <v>0.606</v>
+        <v>0.661</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.5053205391654078</v>
+        <v>0.7079848008862988</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.5671517703461975</v>
+        <v>0.6593342425290085</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>0.5355</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>0.5411026333400099</v>
+        <v>0.6845822094887644</v>
       </c>
       <c r="AC13" s="4" t="n">
-        <v>0.651</v>
+        <v>0.718</v>
       </c>
       <c r="AD13" s="5" t="n">
-        <v>1092316</v>
+        <v>1106945</v>
       </c>
       <c r="AE13" s="5" t="n">
-        <v>69602</v>
+        <v>75745</v>
       </c>
       <c r="AF13" s="5" t="n">
-        <v>318592</v>
+        <v>0</v>
       </c>
       <c r="AG13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AH13" s="3" t="n">
-        <v>0.08751852</v>
+        <v>0.31607025</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AJ13" s="3" t="n">
-        <v>0.08751852</v>
+        <v>0.3160702499999996</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>0</v>
@@ -3693,17 +5686,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>mistralai</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3712,13 +5705,13 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -3727,40 +5720,40 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:30+00:00</t>
+          <t>2026-09-16T03:07:59+00:00</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.1434021604287071</v>
+        <v>0.1486748430163934</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2194519351485593</v>
+        <v>0.2158566833442461</v>
       </c>
       <c r="L14" t="n">
-        <v>24.49324424955361</v>
+        <v>24.85170132045256</v>
       </c>
       <c r="M14" t="n">
-        <v>12.31697458631575</v>
+        <v>12.57729783101797</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" s="4" t="n">
-        <v>0.8991138377641446</v>
+        <v>0.9259462424574877</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.9558232931726908</v>
+        <v>0.9627450980392157</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.7005347593582888</v>
+        <v>0.7247956403269755</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.5421686746987951</v>
+        <v>0.6195652173913043</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.72</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -3768,46 +5761,46 @@
         </is>
       </c>
       <c r="W14" t="n">
-        <v>0.529</v>
+        <v>0.509</v>
       </c>
       <c r="X14" t="n">
-        <v>0.398</v>
+        <v>0.711</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.5140122481389001</v>
+        <v>0.5867378280355483</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.3758955615145875</v>
+        <v>0.7031769757373104</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>0.4635</v>
+        <v>0.61</v>
       </c>
       <c r="AB14" s="4" t="n">
-        <v>0.4473337487719194</v>
+        <v>0.6504937686437986</v>
       </c>
       <c r="AC14" s="4" t="n">
-        <v>0.731</v>
+        <v>0.7</v>
       </c>
       <c r="AD14" s="5" t="n">
-        <v>1108245</v>
+        <v>1107916</v>
       </c>
       <c r="AE14" s="5" t="n">
-        <v>55419</v>
+        <v>62923</v>
       </c>
       <c r="AF14" s="5" t="n">
-        <v>36224</v>
+        <v>183856</v>
       </c>
       <c r="AG14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AH14" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.1964076975</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AJ14" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.1964076975000001</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>0</v>
@@ -3816,32 +5809,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>mistralai</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ABORTED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -3850,57 +5843,87 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:28+00:00</t>
+          <t>2026-09-16T03:17:56+00:00</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
+        <v>0.1344392234965607</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.1976921128927562</v>
+      </c>
       <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
+        <v>23.21465695587321</v>
+      </c>
+      <c r="M15" t="n">
+        <v>11.65156743434614</v>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="4" t="inlineStr"/>
-      <c r="R15" s="4" t="inlineStr"/>
-      <c r="S15" s="4" t="inlineStr"/>
-      <c r="T15" s="4" t="inlineStr"/>
-      <c r="U15" s="4" t="inlineStr"/>
+      <c r="P15" s="4" t="n">
+        <v>0.886284289276808</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>0.9119420989143546</v>
+      </c>
+      <c r="R15" s="4" t="n">
+        <v>0.6757493188010899</v>
+      </c>
+      <c r="S15" s="4" t="n">
+        <v>0.5591939546599498</v>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="U15" s="4" t="n">
+        <v>0.5625</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>NO_RESULTS</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" s="4" t="inlineStr"/>
-      <c r="Z15" s="4" t="inlineStr"/>
-      <c r="AA15" s="4" t="inlineStr"/>
-      <c r="AB15" s="4" t="inlineStr"/>
-      <c r="AC15" s="4" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="Y15" s="4" t="n">
+        <v>0.5053205391654078</v>
+      </c>
+      <c r="Z15" s="4" t="n">
+        <v>0.5671517703461975</v>
+      </c>
+      <c r="AA15" s="4" t="n">
+        <v>0.5355</v>
+      </c>
+      <c r="AB15" s="4" t="n">
+        <v>0.5411026333400099</v>
+      </c>
+      <c r="AC15" s="4" t="n">
+        <v>0.651</v>
+      </c>
       <c r="AD15" s="5" t="n">
-        <v>0</v>
+        <v>1092316</v>
       </c>
       <c r="AE15" s="5" t="n">
-        <v>0</v>
+        <v>69602</v>
       </c>
       <c r="AF15" s="5" t="n">
-        <v>0</v>
+        <v>318592</v>
       </c>
       <c r="AG15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AH15" s="3" t="n">
-        <v>0</v>
+        <v>0.08751852</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" s="3" t="n">
-        <v>0</v>
+        <v>0.08751852</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>0</v>
@@ -3909,32 +5932,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>z-ai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ABORTED</t>
+          <t>COMPLETED</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.3333</v>
+        <v>0.4</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -3943,57 +5966,87 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-16T03:43:30+00:00</t>
+          <t>2026-09-16T03:23:30+00:00</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
+        <v>0.1434021604287071</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.2194519351485593</v>
+      </c>
       <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="inlineStr"/>
+        <v>24.49324424955361</v>
+      </c>
+      <c r="M16" t="n">
+        <v>12.31697458631575</v>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" s="4" t="inlineStr"/>
-      <c r="Q16" s="4" t="inlineStr"/>
-      <c r="R16" s="4" t="inlineStr"/>
-      <c r="S16" s="4" t="inlineStr"/>
-      <c r="T16" s="4" t="inlineStr"/>
-      <c r="U16" s="4" t="inlineStr"/>
+      <c r="P16" s="4" t="n">
+        <v>0.8991138377641446</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>0.9558232931726908</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>0.7005347593582888</v>
+      </c>
+      <c r="S16" s="4" t="n">
+        <v>0.5421686746987951</v>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="U16" s="4" t="n">
+        <v>0.62</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>NO_RESULTS</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" s="4" t="inlineStr"/>
-      <c r="Z16" s="4" t="inlineStr"/>
-      <c r="AA16" s="4" t="inlineStr"/>
-      <c r="AB16" s="4" t="inlineStr"/>
-      <c r="AC16" s="4" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="Y16" s="4" t="n">
+        <v>0.5140122481389001</v>
+      </c>
+      <c r="Z16" s="4" t="n">
+        <v>0.3758955615145875</v>
+      </c>
+      <c r="AA16" s="4" t="n">
+        <v>0.4635</v>
+      </c>
+      <c r="AB16" s="4" t="n">
+        <v>0.4473337487719194</v>
+      </c>
+      <c r="AC16" s="4" t="n">
+        <v>0.731</v>
+      </c>
       <c r="AD16" s="5" t="n">
-        <v>0</v>
+        <v>1108245</v>
       </c>
       <c r="AE16" s="5" t="n">
-        <v>0</v>
+        <v>55419</v>
       </c>
       <c r="AF16" s="5" t="n">
-        <v>0</v>
+        <v>36224</v>
       </c>
       <c r="AG16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AH16" s="3" t="n">
-        <v>0</v>
+        <v>0.1302753</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AJ16" s="3" t="n">
-        <v>0</v>
+        <v>0.1302753</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>0</v>
@@ -4005,13 +6058,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4995,30 +7048,32 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>16</v>
+        <v>200</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0</v>
+        <v>0.1299020365576643</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0</v>
+        <v>0.1672544192884085</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0</v>
+        <v>0.03217330003838188</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0</v>
+        <v>23.01138546667206</v>
       </c>
       <c r="J18" s="4" t="inlineStr"/>
-      <c r="K18" s="4" t="inlineStr"/>
+      <c r="K18" s="4" t="n">
+        <v>0.949200376293509</v>
+      </c>
       <c r="L18" s="4" t="n">
-        <v>0</v>
+        <v>0.3165530602795757</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0</v>
+        <v>126.435</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0</v>
@@ -5027,23 +7082,23 @@
         <v>0</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ko</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -5053,26 +7108,26 @@
         <v>200</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.1303590348428198</v>
+        <v>0.1992896265281343</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.1709290841952356</v>
+        <v>0.2605229540836376</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.03614057893066214</v>
+        <v>0.1061640442440433</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>23.22067206524886</v>
+        <v>11.48522300950568</v>
       </c>
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="n">
-        <v>0.961978928080623</v>
+        <v>0.9549738219895288</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.3145865020042631</v>
+        <v>0.1848632772302493</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>128.1</v>
+        <v>116.72</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0</v>
@@ -5097,7 +7152,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
@@ -5107,26 +7162,26 @@
         <v>200</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.1872998825564791</v>
+        <v>0.1303590348428198</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.2493456350942448</v>
+        <v>0.1709290841952356</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.1065647713569492</v>
+        <v>0.03614057893066214</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>11.95596092668423</v>
+        <v>23.22067206524886</v>
       </c>
       <c r="J20" s="4" t="inlineStr"/>
       <c r="K20" s="4" t="n">
-        <v>0.9586330935251799</v>
+        <v>0.961978928080623</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.2081682001826282</v>
+        <v>0.3145865020042631</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>134.76</v>
+        <v>128.1</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>0</v>
@@ -5141,17 +7196,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ko</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
@@ -5161,26 +7216,26 @@
         <v>200</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.1599680545649344</v>
+        <v>0.1872998825564791</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.2116671860835906</v>
+        <v>0.2493456350942448</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.04944341845697765</v>
+        <v>0.1065647713569492</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>26.76607327189645</v>
+        <v>11.95596092668423</v>
       </c>
       <c r="J21" s="4" t="inlineStr"/>
       <c r="K21" s="4" t="n">
-        <v>0.9235668789808917</v>
+        <v>0.9586330935251799</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.2056149504531175</v>
+        <v>0.2081682001826282</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>82.97</v>
+        <v>134.76</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
@@ -5205,7 +7260,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
@@ -5215,26 +7270,26 @@
         <v>200</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.2296438059429992</v>
+        <v>0.1599680545649344</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.3114530052791114</v>
+        <v>0.2116671860835906</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.1383908316772563</v>
+        <v>0.04944341845697765</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>13.96081188606404</v>
+        <v>26.76607327189645</v>
       </c>
       <c r="J22" s="4" t="inlineStr"/>
       <c r="K22" s="4" t="n">
-        <v>0.9401574803149606</v>
+        <v>0.9235668789808917</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.1394294309478642</v>
+        <v>0.2056149504531175</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>90.59</v>
+        <v>82.97</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -5249,17 +7304,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ko</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -5269,26 +7324,26 @@
         <v>200</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.1416464777859414</v>
+        <v>0.2296438059429992</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.180559850956248</v>
+        <v>0.3114530052791114</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.04159431582022528</v>
+        <v>0.1383908316772563</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>24.38575174114155</v>
+        <v>13.96081188606404</v>
       </c>
       <c r="J23" s="4" t="inlineStr"/>
       <c r="K23" s="4" t="n">
-        <v>0.9091375770020534</v>
+        <v>0.9401574803149606</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.3035461624893713</v>
+        <v>0.1394294309478642</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>123.885</v>
+        <v>90.59</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -5313,7 +7368,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
@@ -5323,26 +7378,26 @@
         <v>200</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.2093037662697218</v>
+        <v>0.1416464777859414</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.2729415283736519</v>
+        <v>0.180559850956248</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.1190768955431999</v>
+        <v>0.04159431582022528</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>12.78420991940304</v>
+        <v>24.38575174114155</v>
       </c>
       <c r="J24" s="4" t="inlineStr"/>
       <c r="K24" s="4" t="n">
-        <v>0.9739027283511269</v>
+        <v>0.9091375770020534</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.1769149869083851</v>
+        <v>0.3035461624893713</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>113.325</v>
+        <v>123.885</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>0</v>
@@ -5357,17 +7412,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ko</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -5377,26 +7432,26 @@
         <v>200</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.1608350962342315</v>
+        <v>0.2093037662697218</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.2085794745422087</v>
+        <v>0.2729415283736519</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.04632105468306493</v>
+        <v>0.1190768955431999</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>26.04951109641535</v>
+        <v>12.78420991940304</v>
       </c>
       <c r="J25" s="4" t="inlineStr"/>
       <c r="K25" s="4" t="n">
-        <v>0.8816067653276956</v>
+        <v>0.9739027283511269</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.2409253679233042</v>
+        <v>0.1769149869083851</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>99.355</v>
+        <v>113.325</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
@@ -5421,7 +7476,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
@@ -5431,26 +7486,26 @@
         <v>200</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.2302580020788956</v>
+        <v>0.1608350962342315</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.3083312001934705</v>
+        <v>0.2085794745422087</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.1348816271187801</v>
+        <v>0.04632105468306493</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>13.75572799407668</v>
+        <v>26.04951109641535</v>
       </c>
       <c r="J26" s="4" t="inlineStr"/>
       <c r="K26" s="4" t="n">
-        <v>0.947463768115942</v>
+        <v>0.8816067653276956</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.1406667786319521</v>
+        <v>0.2409253679233042</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>91.66500000000001</v>
+        <v>99.355</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>0</v>
@@ -5465,17 +7520,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ko</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
@@ -5485,26 +7540,26 @@
         <v>200</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.1621429745937464</v>
+        <v>0.2302580020788956</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.2140816061855588</v>
+        <v>0.3083312001934705</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.04984441933906216</v>
+        <v>0.1348816271187801</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>26.68302009498116</v>
+        <v>13.75572799407668</v>
       </c>
       <c r="J27" s="4" t="inlineStr"/>
       <c r="K27" s="4" t="n">
-        <v>0.8794037940379403</v>
+        <v>0.947463768115942</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.23494993212131</v>
+        <v>0.1406667786319521</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>94.31</v>
+        <v>91.66500000000001</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>0</v>
@@ -5529,7 +7584,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
@@ -5539,26 +7594,26 @@
         <v>200</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.2283869866974114</v>
+        <v>0.1621429745937464</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.3045945744869495</v>
+        <v>0.2140816061855588</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.136835376836795</v>
+        <v>0.04984441933906216</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>14.15140430658347</v>
+        <v>26.68302009498116</v>
       </c>
       <c r="J28" s="4" t="inlineStr"/>
       <c r="K28" s="4" t="n">
-        <v>0.9405594405594405</v>
+        <v>0.8794037940379403</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1476203006498572</v>
+        <v>0.23494993212131</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>95.755</v>
+        <v>94.31</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>0</v>
@@ -5573,62 +7628,172 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>qwen/qwen3.8-flash</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Qwen3.8 Flash</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>0.2283869866974114</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>0.3045945744869495</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>0.136835376836795</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>14.15140430658347</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr"/>
+      <c r="K29" s="4" t="n">
+        <v>0.9405594405594405</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>0.1476203006498572</v>
+      </c>
+      <c r="M29" s="5" t="n">
+        <v>95.755</v>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>z-ai/glm-5.3-flash</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>GLM 5.3 Flash</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="D29" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr"/>
-      <c r="K29" s="4" t="inlineStr"/>
-      <c r="L29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="5" t="n">
-        <v>17</v>
+      <c r="D30" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>0.1442957203978096</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>0.1849635446126243</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0.04312971461647706</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>24.60010668803035</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="n">
+        <v>0.9221978021978022</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>0.3054752814341838</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>124.13</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>0.2059639679861038</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>0.2660039429049016</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>0.1213426022152081</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>13.49752283326942</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="n">
+        <v>0.9633928571428572</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>0.1944783648634142</v>
+      </c>
+      <c r="M31" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P29"/>
+  <autoFilter ref="A1:P31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5640,7 +7805,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -6629,24 +8794,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NO_RESULTS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="4" t="inlineStr"/>
-      <c r="J18" s="4" t="inlineStr"/>
-      <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr"/>
-      <c r="O18" s="5" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0.6775</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0.6774496015002344</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0.6731707317073171</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0.6814814814814814</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>0.6734177215189874</v>
+      </c>
+      <c r="N18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6666,24 +8849,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NO_RESULTS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr"/>
-      <c r="I19" s="4" t="inlineStr"/>
-      <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="4" t="inlineStr"/>
-      <c r="N19" s="4" t="inlineStr"/>
-      <c r="O19" s="5" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0.5059742647058822</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>0.328125</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>0.6838235294117646</v>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7253,24 +9454,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NO_RESULTS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="4" t="inlineStr"/>
-      <c r="I30" s="4" t="inlineStr"/>
-      <c r="J30" s="4" t="inlineStr"/>
-      <c r="K30" s="4" t="inlineStr"/>
-      <c r="L30" s="4" t="inlineStr"/>
-      <c r="M30" s="4" t="inlineStr"/>
-      <c r="N30" s="4" t="inlineStr"/>
-      <c r="O30" s="5" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>0.7275</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>0.7274846710127445</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>0.7309644670050761</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>0.72544080604534</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>0.729528535980149</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7290,24 +9509,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NO_RESULTS</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="4" t="inlineStr"/>
-      <c r="I31" s="4" t="inlineStr"/>
-      <c r="J31" s="4" t="inlineStr"/>
-      <c r="K31" s="4" t="inlineStr"/>
-      <c r="L31" s="4" t="inlineStr"/>
-      <c r="M31" s="4" t="inlineStr"/>
-      <c r="N31" s="4" t="inlineStr"/>
-      <c r="O31" s="5" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>0.6265172735760971</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>0.7258064516129032</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>0.5555555555555557</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M31" s="4" t="n">
+        <v>0.6974789915966386</v>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:O31"/>
@@ -7315,13 +9552,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8239,13 +10476,23 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0.8314865753296514</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>842</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8264,44 +10511,54 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0.8034449936517111</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>815</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>overall</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.715</v>
+        <v>0.8285</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.7079848008862988</v>
+        <v>0.8179267929293625</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>715</v>
+        <v>1657</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
         <v>60</v>
@@ -8320,23 +10577,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.661</v>
+        <v>0.715</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.6593342425290085</v>
+        <v>0.7079848008862988</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>661</v>
+        <v>715</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="I29" s="5" t="n">
         <v>60</v>
@@ -8355,23 +10612,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>overall</t>
+          <t>ko</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.661</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.6845822094887644</v>
+        <v>0.6593342425290085</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>1376</v>
+        <v>661</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="I30" s="5" t="n">
         <v>60</v>
@@ -8380,33 +10637,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>overall</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.868</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.8492172170319239</v>
+        <v>0.6845822094887644</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>868</v>
+        <v>1376</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I31" s="5" t="n">
         <v>60</v>
@@ -8425,20 +10682,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.831</v>
+        <v>0.868</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.8000988567676002</v>
+        <v>0.8492172170319239</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>831</v>
+        <v>868</v>
       </c>
       <c r="H32" s="4" t="n">
         <v>0</v>
@@ -8460,20 +10717,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>overall</t>
+          <t>ko</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.8495</v>
+        <v>0.831</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.8278820044607954</v>
+        <v>0.8000988567676002</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>1699</v>
+        <v>831</v>
       </c>
       <c r="H33" s="4" t="n">
         <v>0</v>
@@ -8485,33 +10742,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>overall</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8495</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.7992131261387427</v>
+        <v>0.8278820044607954</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>809</v>
+        <v>1699</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>60</v>
@@ -8530,23 +10787,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.794</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.7717528819109728</v>
+        <v>0.7992131261387427</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>794</v>
+        <v>809</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I35" s="5" t="n">
         <v>60</v>
@@ -8565,23 +10822,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>overall</t>
+          <t>ko</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.8015</v>
+        <v>0.794</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.7855676169719019</v>
+        <v>0.7717528819109728</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>1603</v>
+        <v>794</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I36" s="5" t="n">
         <v>60</v>
@@ -8590,33 +10847,33 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>overall</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.796</v>
+        <v>0.8015</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.7792340968020122</v>
+        <v>0.7855676169719019</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>796</v>
+        <v>1603</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I37" s="5" t="n">
         <v>60</v>
@@ -8635,23 +10892,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.76</v>
+        <v>0.796</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.7439524644750251</v>
+        <v>0.7792340968020122</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>760</v>
+        <v>796</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="I38" s="5" t="n">
         <v>60</v>
@@ -8670,23 +10927,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>overall</t>
+          <t>ko</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.778</v>
+        <v>0.76</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.7614406146917927</v>
+        <v>0.7439524644750251</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>1556</v>
+        <v>760</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I39" s="5" t="n">
         <v>60</v>
@@ -8695,33 +10952,33 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>overall</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.882</v>
+        <v>0.778</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.8710472576948233</v>
+        <v>0.7614406146917927</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>882</v>
+        <v>1556</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I40" s="5" t="n">
         <v>60</v>
@@ -8740,20 +10997,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.846</v>
+        <v>0.882</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.8354346192098669</v>
+        <v>0.8710472576948233</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>846</v>
+        <v>882</v>
       </c>
       <c r="H41" s="4" t="n">
         <v>0</v>
@@ -8775,20 +11032,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>overall</t>
+          <t>ko</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.864</v>
+        <v>0.846</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.8523414150627505</v>
+        <v>0.8354346192098669</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>1728</v>
+        <v>846</v>
       </c>
       <c r="H42" s="4" t="n">
         <v>0</v>
@@ -8800,27 +11057,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>overall</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr"/>
-      <c r="G43" s="5" t="inlineStr"/>
-      <c r="H43" s="4" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>0.8523414150627505</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>1728</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -8835,31 +11102,111 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>0.846487306452871</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>858</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>ko</t>
         </is>
       </c>
-      <c r="D44" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="4" t="inlineStr"/>
-      <c r="F44" s="4" t="inlineStr"/>
-      <c r="G44" s="5" t="inlineStr"/>
-      <c r="H44" s="4" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr"/>
+      <c r="D45" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>0.7859849948864567</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>797</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>0.8275</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>0.8155753958777252</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>1655</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I44"/>
+  <autoFilter ref="A1:I46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9307,241 +11654,331 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.718</v>
+        <v>0.863</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.612</v>
+        <v>0.833</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>547</v>
+        <v>760</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.547</v>
+        <v>0.76</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.168</v>
+        <v>0.082</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.114</v>
+        <v>0.055</v>
       </c>
       <c r="L10" t="n">
-        <v>171</v>
+        <v>103</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.171</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.895</v>
+        <v>0.718</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.866</v>
+        <v>0.612</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>797</v>
+        <v>547</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.797</v>
+        <v>0.547</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>71</v>
+        <v>168</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.168</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.034</v>
+        <v>0.114</v>
       </c>
       <c r="L11" t="n">
-        <v>98</v>
+        <v>171</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.098</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.865</v>
+        <v>0.895</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.866</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>734</v>
+        <v>797</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.734</v>
+        <v>0.797</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.075</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.06</v>
+        <v>0.034</v>
       </c>
       <c r="L12" t="n">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.131</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.832</v>
+        <v>0.865</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.77</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>694</v>
+        <v>734</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.694</v>
+        <v>0.734</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.102</v>
+        <v>0.075</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.066</v>
+        <v>0.06</v>
       </c>
       <c r="L13" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.138</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D14" s="4" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>694</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="L14" t="n">
+        <v>138</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>0.138</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>qwen/qwen3.8-flash</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Qwen3.8 Flash</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D15" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E15" s="4" t="n">
         <v>0.887</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F15" s="5" t="n">
         <v>819</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>0.819</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H15" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="I15" s="4" t="n">
         <v>0.063</v>
       </c>
-      <c r="J14" s="5" t="n">
+      <c r="J15" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="K14" s="4" t="n">
+      <c r="K15" s="4" t="n">
         <v>0.027</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L15" t="n">
         <v>91</v>
       </c>
-      <c r="M14" s="4" t="n">
+      <c r="M15" s="4" t="n">
         <v>0.091</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>761</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="L16" t="n">
+        <v>106</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0.106</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M14"/>
+  <autoFilter ref="A1:M16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -10341,73 +12778,75 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0</v>
+        <v>2126</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="4" t="inlineStr"/>
+        <v>2018</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.949200376293509</v>
+      </c>
       <c r="G18" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ko</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>2183</v>
+        <v>955</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2100</v>
+        <v>912</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.961978928080623</v>
+        <v>0.9549738219895288</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="K19" s="4" t="n">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>200</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20">
@@ -10423,79 +12862,79 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>1112</v>
+        <v>2183</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1066</v>
+        <v>2100</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.9586330935251799</v>
+        <v>0.961978928080623</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ko</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1413</v>
+        <v>1112</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1305</v>
+        <v>1066</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.9235668789808917</v>
+        <v>0.9586330935251799</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="22">
@@ -10511,79 +12950,79 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>635</v>
+        <v>1413</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>597</v>
+        <v>1305</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.9401574803149606</v>
+        <v>0.9235668789808917</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>181</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ko</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1948</v>
+        <v>635</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1771</v>
+        <v>597</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.9091375770020534</v>
+        <v>0.9401574803149606</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="5" t="n">
-        <v>26</v>
-      </c>
       <c r="K23" s="4" t="n">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>200</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24">
@@ -10599,79 +13038,79 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>843</v>
+        <v>1948</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>821</v>
+        <v>1771</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.9739027283511269</v>
+        <v>0.9091375770020534</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>12</v>
+        <v>140</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>187</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ko</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1419</v>
+        <v>843</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1251</v>
+        <v>821</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.8816067653276956</v>
+        <v>0.9739027283511269</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>154</v>
+        <v>12</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>200</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26">
@@ -10687,79 +13126,79 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>552</v>
+        <v>1419</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>523</v>
+        <v>1251</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.947463768115942</v>
+        <v>0.8816067653276956</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>17</v>
+        <v>154</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>179</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>ko</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>1476</v>
+        <v>552</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1298</v>
+        <v>523</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.8794037940379403</v>
+        <v>0.947463768115942</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="K27" s="4" t="n">
-        <v>159</v>
+        <v>17</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>200</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28">
@@ -10775,86 +13214,176 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ko</t>
+          <t>en</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>572</v>
+        <v>1476</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>538</v>
+        <v>1298</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.9405594405594405</v>
+        <v>0.8794037940379403</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>21</v>
+        <v>159</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>186</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>qwen/qwen3.8-flash</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Qwen3.8 Flash</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>572</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>538</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>0.9405594405594405</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>z-ai/glm-5.3-flash</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>GLM 5.3 Flash</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>en</t>
         </is>
       </c>
-      <c r="D29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v>0</v>
+      <c r="D30" s="5" t="n">
+        <v>2275</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>2098</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>0.9221978021978022</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>1120</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>1079</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>0.9633928571428572</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>197</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L29"/>
+  <autoFilter ref="A1:L31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11544,17 +14073,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:28+00:00</t>
+          <t>2026-09-16T04:40:49+00:00</t>
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>0.08205585</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>0.1433661</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>0.0474705</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0</v>
@@ -11563,22 +14092,22 @@
         <v>0</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>0.27289245</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>0.2728924500000001</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>0.27289245</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>0.2728924500000001</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0</v>
+        <v>0.27289245</v>
       </c>
       <c r="S10" t="b">
         <v>1</v>
@@ -11944,17 +14473,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-16T03:43:30+00:00</t>
+          <t>2026-09-16T04:41:38+00:00</t>
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0</v>
+        <v>0.0828101102</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0</v>
+        <v>0.11700001578</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0</v>
+        <v>0.0149070175</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>0</v>
@@ -11963,801 +14492,29 @@
         <v>0</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0</v>
+        <v>0.21471714348</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0</v>
+        <v>0.2147171434799998</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0</v>
+        <v>0.21471714348</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0</v>
+        <v>0.2147171434799998</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0</v>
+        <v>0.1606481436</v>
       </c>
       <c r="S16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:S16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>display_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>successful_cases</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>prompt_tokens</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>cached_tokens</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>cache_write_tokens</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>completion_tokens</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>reasoning_tokens</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>total_tokens</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>cache_hits</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>cache_misses</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>openrouter_api_calls</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>openrouter_http_attempts</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>deepseek/deepseek-v4-flash-0731</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>DeepSeek V4 Flash 0731</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>1190712</v>
-      </c>
-      <c r="E2" s="5" t="n">
-        <v>369477</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>63519</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>1254231</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="M2" s="5" t="n">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>google/gemini-2.5-flash-lite</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Gemini 2.5 Flash-Lite</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>1097914</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>54986</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>1152900</v>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="M3" s="5" t="n">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>google/gemini-3.1-flash-lite</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Gemini 3.1 Flash-Lite</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>1098022</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>55664</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>1153686</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>83</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>1217</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>1217</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v>1217</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>mistralai/ministral-14b-2512</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ministral 3 14B</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>1092316</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>295936</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>71944</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>1164260</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>mistralai/ministral-3b-2512</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ministral 3 3B</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>1092316</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>318592</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>69602</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>1161918</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>mistralai/ministral-8b-2512</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Ministral 3 8B</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>1092316</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>299392</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>71698</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>1164014</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>mistralai/mistral-small-2603</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Mistral Small 4</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>1107916</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>183856</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>62923</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>1170839</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>openai/gpt-4.1-nano</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>GPT-4.1 Nano</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>1108245</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>36224</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>55419</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>1163664</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>openai/gpt-5-nano</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>GPT-5 Nano</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>openai/gpt-5.4-nano</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>GPT-5.4 Nano</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>1106945</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>75745</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>1182690</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>openai/gpt-5.6-luna</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>GPT-5.6 Luna</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>1106945</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>458921</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>55276</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>1162221</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>1213604</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>102934</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>72595</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>1286199</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>qwen/qwen3.7-flash</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Qwen3.7 Flash</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>1061596</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>24960</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>51608</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>1113204</v>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>qwen/qwen3.8-flash</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Qwen3.8 Flash</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>1061596</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>265984</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>52179</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>1113775</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>z-ai/glm-5.3-flash</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>GLM 5.3 Flash</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:M16"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/results/benchmark_results.xlsx
+++ b/results/benchmark_results.xlsx
@@ -23,17 +23,17 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Legend'!$A$1:$D$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Leaderboard'!$A$1:$AK$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Leaderboard'!$A$1:$AL$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Summarization'!$A$1:$P$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Hallucination'!$A$1:$O$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Classification'!$A$1:$I$46</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'CrossLingual'!$A$1:$M$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Classification'!$A$1:$I$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'CrossLingual'!$A$1:$M$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'ClassificationModes'!$A$1:$K$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'SurfaceFacts'!$A$1:$L$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cost'!$A$1:$S$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Usage'!$A$1:$M$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cost'!$A$1:$S$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Usage'!$A$1:$M$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Judge'!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Runs'!$A$1:$T$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Runs'!$A$1:$T$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -516,7 +516,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T00:38:36+00:00</t>
+          <t>2026-09-17T01:55:51+00:00</t>
         </is>
       </c>
     </row>
@@ -647,11 +647,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -972,89 +972,59 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0.2</v>
-      </c>
+          <t>Qwen2.5 1.5B Instruct (GGUF Q8_0, local)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-16T03:10:41+00:00</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>0.07769180000000001</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0.08999796</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0.01189376</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>0.17958352</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>0.1795835200000001</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>0.17958352</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>0.1795835200000001</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>0.17958352</v>
-      </c>
-      <c r="S5" t="b">
-        <v>1</v>
-      </c>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1063,17 +1033,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-16T03:17:56+00:00</t>
+          <t>2026-09-16T03:10:41+00:00</t>
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.0385285</v>
+        <v>0.07769180000000001</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.0433295</v>
+        <v>0.08999796</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.00566052</v>
+        <v>0.01189376</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -1082,22 +1052,22 @@
         <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>0.08751852</v>
+        <v>0.17958352</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>0.08751852</v>
+        <v>0.1795835200000001</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>0.08751852</v>
+        <v>0.17958352</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.08751852</v>
+        <v>0.1795835200000001</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.08751852</v>
+        <v>0.17958352</v>
       </c>
       <c r="S6" t="b">
         <v>1</v>
@@ -1106,22 +1076,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1130,17 +1100,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-16T03:15:02+00:00</t>
+          <t>2026-09-16T03:17:56+00:00</t>
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.0582456</v>
+        <v>0.0385285</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.06753291</v>
+        <v>0.0433295</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.008405670000000001</v>
+        <v>0.00566052</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
@@ -1149,22 +1119,22 @@
         <v>0</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.13418418</v>
+        <v>0.08751852</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.1341841799999999</v>
+        <v>0.08751852</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.13418418</v>
+        <v>0.08751852</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.1341841799999999</v>
+        <v>0.08751852</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.13418418</v>
+        <v>0.08751852</v>
       </c>
       <c r="S7" t="b">
         <v>1</v>
@@ -1173,12 +1143,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -1188,7 +1158,7 @@
         <v>0.015</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1197,17 +1167,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-16T03:07:59+00:00</t>
+          <t>2026-09-16T03:15:02+00:00</t>
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.0802729125</v>
+        <v>0.0582456</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.0986139</v>
+        <v>0.06753291</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.017520885</v>
+        <v>0.008405670000000001</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1216,46 +1186,46 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.1964076975</v>
+        <v>0.13418418</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.1964076975000001</v>
+        <v>0.1341841799999999</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0.1964076975</v>
+        <v>0.13418418</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.1964076975000001</v>
+        <v>0.1341841799999999</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.17912064</v>
+        <v>0.13418418</v>
       </c>
       <c r="S8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1264,17 +1234,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:30+00:00</t>
+          <t>2026-09-16T03:07:59+00:00</t>
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.0519185</v>
+        <v>0.0802729125</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.067397</v>
+        <v>0.0986139</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.0109598</v>
+        <v>0.017520885</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>0</v>
@@ -1283,43 +1253,43 @@
         <v>0</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.1964076975</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.1964076975000001</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.1964076975</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.1964076975000001</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.1302753</v>
+        <v>0.17912064</v>
       </c>
       <c r="S9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.005</v>
+        <v>0.025</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0.4</v>
@@ -1331,17 +1301,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-16T04:40:49+00:00</t>
+          <t>2026-09-16T03:23:30+00:00</t>
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.08205585</v>
+        <v>0.0519185</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.1433661</v>
+        <v>0.067397</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.0474705</v>
+        <v>0.0109598</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0</v>
@@ -1350,22 +1320,22 @@
         <v>0</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.27289245</v>
+        <v>0.1302753</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.2728924500000001</v>
+        <v>0.1302753</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.27289245</v>
+        <v>0.1302753</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.2728924500000001</v>
+        <v>0.1302753</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.27289245</v>
+        <v>0.1302753</v>
       </c>
       <c r="S10" t="b">
         <v>1</v>
@@ -1374,22 +1344,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1.25</v>
+        <v>0.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1398,17 +1368,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-16T03:20:07+00:00</t>
+          <t>2026-09-16T04:40:49+00:00</t>
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.1453735</v>
+        <v>0.08205585</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.1435934</v>
+        <v>0.1433661</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.02710335</v>
+        <v>0.0474705</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
@@ -1417,22 +1387,22 @@
         <v>0</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.31607025</v>
+        <v>0.27289245</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.3160702499999996</v>
+        <v>0.2728924500000001</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.31607025</v>
+        <v>0.27289245</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.3160702499999996</v>
+        <v>0.2728924500000001</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.3160702500000001</v>
+        <v>0.27289245</v>
       </c>
       <c r="S11" t="b">
         <v>1</v>
@@ -1441,12 +1411,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
@@ -1456,7 +1426,7 @@
         <v>0.02</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1465,17 +1435,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-16T02:59:08+00:00</t>
+          <t>2026-09-16T03:20:07+00:00</t>
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.12600455</v>
+        <v>0.1453735</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.1584021</v>
+        <v>0.1435934</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.0262596</v>
+        <v>0.02710335</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1484,44 +1454,46 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.31066625</v>
+        <v>0.31607025</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.3106662500000003</v>
+        <v>0.3160702499999996</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0.31066625</v>
+        <v>0.31607025</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.3106662500000003</v>
+        <v>0.3160702499999996</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.2877202</v>
+        <v>0.3160702500000001</v>
       </c>
       <c r="S12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.04815</v>
-      </c>
-      <c r="D13" s="3" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0.02</v>
+      </c>
       <c r="E13" s="3" t="n">
-        <v>0.19305</v>
+        <v>1.2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1530,17 +1502,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-16T03:34:40+00:00</t>
+          <t>2026-09-16T02:59:08+00:00</t>
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.04959875775</v>
+        <v>0.12600455</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.06309176505</v>
+        <v>0.1584021</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.01054341345</v>
+        <v>0.0262596</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
@@ -1549,22 +1521,22 @@
         <v>0</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>0.12323393625</v>
+        <v>0.31066625</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.1232339362500001</v>
+        <v>0.3106662500000003</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>0.12323393625</v>
+        <v>0.31066625</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.1232339362500001</v>
+        <v>0.3106662500000003</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.07244949735</v>
+        <v>0.2877202</v>
       </c>
       <c r="S13" t="b">
         <v>0</v>
@@ -1573,22 +1545,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>0.006</v>
-      </c>
+        <v>0.04815</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr"/>
       <c r="E14" s="3" t="n">
-        <v>0.13</v>
+        <v>0.19305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1597,17 +1567,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-16T03:31:23+00:00</t>
+          <t>2026-09-16T03:34:40+00:00</t>
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.01445385</v>
+        <v>0.04959875775</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.01955122</v>
+        <v>0.06309176505</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.0039132</v>
+        <v>0.01054341345</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0</v>
@@ -1616,46 +1586,46 @@
         <v>0</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>0.03791827</v>
+        <v>0.12323393625</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.03791826999999996</v>
+        <v>0.1232339362500001</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.03791827</v>
+        <v>0.12323393625</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.03791826999999996</v>
+        <v>0.1232339362500001</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.03795787999999999</v>
+        <v>0.07244949735</v>
       </c>
       <c r="S14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.016</v>
+        <v>0.006</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.47</v>
+        <v>0.13</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1664,17 +1634,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-16T03:26:19+00:00</t>
+          <t>2026-09-16T03:31:23+00:00</t>
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.06590207000000001</v>
+        <v>0.01445385</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.068078582</v>
+        <v>0.01955122</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.013945102</v>
+        <v>0.0039132</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>0</v>
@@ -1683,22 +1653,22 @@
         <v>0</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.03791827</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.03791826999999996</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.03791827</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.03791826999999996</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.148121674</v>
+        <v>0.03795787999999999</v>
       </c>
       <c r="S15" t="b">
         <v>1</v>
@@ -1707,72 +1677,139 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>qwen/qwen3.8-flash</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Qwen3.8 Flash</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-09-16T03:26:19+00:00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0.06590207000000001</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>0.068078582</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0.013945102</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>0.147925754</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>0.147925754</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>0.147925754</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>0.147925754</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>0.148121674</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>z-ai/glm-5.3-flash</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>GLM 5.3 Flash</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C17" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>0.02</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>0.3333</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>2026-09-16T04:41:38+00:00</t>
         </is>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="H17" s="3" t="n">
         <v>0.0828101102</v>
       </c>
-      <c r="I16" s="3" t="n">
+      <c r="I17" s="3" t="n">
         <v>0.11700001578</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="J17" s="3" t="n">
         <v>0.0149070175</v>
       </c>
-      <c r="K16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="3" t="n">
+      <c r="K17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3" t="n">
         <v>0.21471714348</v>
       </c>
-      <c r="N16" s="3" t="n">
+      <c r="N17" s="3" t="n">
         <v>0.2147171434799998</v>
       </c>
-      <c r="O16" s="3" t="n">
+      <c r="O17" s="3" t="n">
         <v>0.21471714348</v>
       </c>
-      <c r="P16" s="3" t="n">
+      <c r="P17" s="3" t="n">
         <v>0.2147171434799998</v>
       </c>
-      <c r="Q16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="4" t="n">
+      <c r="Q17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="4" t="n">
         <v>0.1606481436</v>
       </c>
-      <c r="S16" t="b">
+      <c r="S17" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S16"/>
+  <autoFilter ref="A1:S17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1783,11 +1820,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -2006,57 +2043,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen2.5 1.5B Instruct (GGUF Q8_0, local)</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1300</v>
+        <v>4000</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1092316</v>
+        <v>1441986</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>295936</v>
+        <v>0</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>71944</v>
+        <v>10903</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>1164260</v>
+        <v>1452889</v>
       </c>
       <c r="J5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>1300</v>
+        <v>2000</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>1300</v>
+        <v>2000</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>1300</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
@@ -2066,19 +2103,19 @@
         <v>1092316</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>318592</v>
+        <v>295936</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>69602</v>
+        <v>71944</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>1161918</v>
+        <v>1164260</v>
       </c>
       <c r="J6" s="5" t="n">
         <v>0</v>
@@ -2096,12 +2133,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
@@ -2111,19 +2148,19 @@
         <v>1092316</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>299392</v>
+        <v>318592</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>71698</v>
+        <v>69602</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>1164014</v>
+        <v>1161918</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>0</v>
@@ -2141,34 +2178,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1107916</v>
+        <v>1092316</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>183856</v>
+        <v>299392</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>62923</v>
+        <v>71698</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>1170839</v>
+        <v>1164014</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>0</v>
@@ -2186,34 +2223,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1108245</v>
+        <v>1107916</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>36224</v>
+        <v>183856</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>55419</v>
+        <v>62923</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>1163664</v>
+        <v>1170839</v>
       </c>
       <c r="J9" s="5" t="n">
         <v>0</v>
@@ -2231,34 +2268,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1106945</v>
+        <v>1108245</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>40320</v>
+        <v>36224</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>548399</v>
+        <v>55419</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>433920</v>
+        <v>0</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>1655344</v>
+        <v>1163664</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>0</v>
@@ -2276,12 +2313,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
@@ -2291,19 +2328,19 @@
         <v>1106945</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>40320</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>75745</v>
+        <v>548399</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0</v>
+        <v>433920</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>1182690</v>
+        <v>1655344</v>
       </c>
       <c r="J11" s="5" t="n">
         <v>0</v>
@@ -2321,12 +2358,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
@@ -2339,16 +2376,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>458921</v>
+        <v>0</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>55276</v>
+        <v>75745</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>1162221</v>
+        <v>1182690</v>
       </c>
       <c r="J12" s="5" t="n">
         <v>0</v>
@@ -2366,34 +2403,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1213604</v>
+        <v>1106945</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>102934</v>
+        <v>0</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0</v>
+        <v>458921</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>72595</v>
+        <v>55276</v>
       </c>
       <c r="H13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>1286199</v>
+        <v>1162221</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>0</v>
@@ -2411,34 +2448,34 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1061596</v>
+        <v>1213604</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>24960</v>
+        <v>102934</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>51608</v>
+        <v>72595</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>1113204</v>
+        <v>1286199</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>0</v>
@@ -2450,18 +2487,18 @@
         <v>1300</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>1307</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -2471,19 +2508,19 @@
         <v>1061596</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>265984</v>
+        <v>24960</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>52179</v>
+        <v>51608</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>1113775</v>
+        <v>1113204</v>
       </c>
       <c r="J15" s="5" t="n">
         <v>0</v>
@@ -2495,40 +2532,40 @@
         <v>1300</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>1314</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1293055</v>
+        <v>1061596</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>104384</v>
+        <v>265984</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>119092</v>
+        <v>52179</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>35855</v>
+        <v>0</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>1412147</v>
+        <v>1113775</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>0</v>
@@ -2540,11 +2577,56 @@
         <v>1300</v>
       </c>
       <c r="M16" s="5" t="n">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
         <v>1300</v>
       </c>
+      <c r="D17" s="5" t="n">
+        <v>1293055</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>104384</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>119092</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>35855</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>1412147</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>1300</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M16"/>
+  <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2580,10 +2662,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
@@ -2950,7 +3032,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2960,17 +3042,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>run-20260916T031043-60c30b6a</t>
+          <t>run-20260917T013544-81d671a6</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:15:02+00:00</t>
+          <t>2026-09-17T01:52:22+00:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-16T03:10:43+00:00</t>
+          <t>2026-09-17T01:35:44+00:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2978,8 +3060,14 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>7d940a780adb2d63730876016bcc16115c9bd8e2</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -2987,7 +3075,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>summarization, hallucination, classification</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2996,7 +3084,7 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>3200</v>
+        <v>2000</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -3030,7 +3118,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3040,17 +3128,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>run-20260916T031757-6f0019bc</t>
+          <t>run-20260916T031043-60c30b6a</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:20:07+00:00</t>
+          <t>2026-09-16T03:15:02+00:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-16T03:17:57+00:00</t>
+          <t>2026-09-16T03:10:43+00:00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3110,7 +3198,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3120,17 +3208,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>run-20260916T031504-7b84cf7d</t>
+          <t>run-20260916T031757-6f0019bc</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:17:56+00:00</t>
+          <t>2026-09-16T03:20:07+00:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-16T03:15:04+00:00</t>
+          <t>2026-09-16T03:17:57+00:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3190,7 +3278,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3200,17 +3288,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>run-20260916T030801-577d0830</t>
+          <t>run-20260916T031504-7b84cf7d</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:10:41+00:00</t>
+          <t>2026-09-16T03:17:56+00:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-16T03:08:01+00:00</t>
+          <t>2026-09-16T03:15:04+00:00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3270,7 +3358,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3280,17 +3368,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>run-20260916T032332-5a24afb2</t>
+          <t>run-20260916T030801-577d0830</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:26:19+00:00</t>
+          <t>2026-09-16T03:10:41+00:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:32+00:00</t>
+          <t>2026-09-16T03:08:01+00:00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3350,7 +3438,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3360,17 +3448,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>run-20260916T044051-1b0d71da</t>
+          <t>run-20260916T032332-5a24afb2</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T04:51:21+00:00</t>
+          <t>2026-09-16T03:26:19+00:00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-16T04:40:51+00:00</t>
+          <t>2026-09-16T03:23:32+00:00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3378,14 +3466,8 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
-      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -3436,7 +3518,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3446,17 +3528,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>run-20260916T032009-aca77564</t>
+          <t>run-20260916T044051-1b0d71da</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:28+00:00</t>
+          <t>2026-09-16T04:51:21+00:00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-16T03:20:09+00:00</t>
+          <t>2026-09-16T04:40:51+00:00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3464,8 +3546,14 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -3516,7 +3604,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3526,17 +3614,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>run-20260916T025909-be4eb782</t>
+          <t>run-20260916T032009-aca77564</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:02:43+00:00</t>
+          <t>2026-09-16T03:23:28+00:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-16T02:59:09+00:00</t>
+          <t>2026-09-16T03:20:09+00:00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3596,7 +3684,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3606,17 +3694,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>run-20260916T033441-93cb685e</t>
+          <t>run-20260916T025909-be4eb782</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:43:30+00:00</t>
+          <t>2026-09-16T03:02:43+00:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-16T03:34:41+00:00</t>
+          <t>2026-09-16T02:59:09+00:00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3676,7 +3764,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3686,17 +3774,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>run-20260916T033125-8730c140</t>
+          <t>run-20260916T033441-93cb685e</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:34:40+00:00</t>
+          <t>2026-09-16T03:43:30+00:00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-16T03:31:25+00:00</t>
+          <t>2026-09-16T03:34:41+00:00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3756,7 +3844,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3766,17 +3854,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>run-20260916T032621-2ec5c283</t>
+          <t>run-20260916T033125-8730c140</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:31:23+00:00</t>
+          <t>2026-09-16T03:34:40+00:00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-16T03:26:21+00:00</t>
+          <t>2026-09-16T03:31:25+00:00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3836,7 +3924,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3846,17 +3934,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>run-20260916T044139-f5eda9f3</t>
+          <t>run-20260916T032621-2ec5c283</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T04:51:13+00:00</t>
+          <t>2026-09-16T03:31:23+00:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-16T04:41:39+00:00</t>
+          <t>2026-09-16T03:26:21+00:00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3864,14 +3952,8 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -3919,8 +4001,94 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>run-20260916T044139-f5eda9f3</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16T04:51:13+00:00</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-09-16T04:41:39+00:00</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3.12.3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>summarization, hallucination, classification</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>en, ko</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>3200</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>cbe6fb9c14d4b2b12e690d6565e05bcf861c5db26cc56aef45e3e3810f67b298</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0135c4f4499e35dcde7855ad6afe33e333ebf2bca519a20b81257dc39150cd62</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>21debf696ed02ef001638142e2864a1bb58be409f88d8c86ad36e067ee609ca5</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>b49d914db700703584e2388f602808314a59c9e088a20f02e670ead58141fa96</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1bebd7a4e6cab622b3a85e6f856e019c9459100085c08ca38ccec107d5e3ec21</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T16"/>
+  <autoFilter ref="A1:T17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5250,46 +5418,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK16"/>
+  <dimension ref="A1:AL17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="27" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
     <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
-    <col width="21" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="20" max="20"/>
     <col width="18" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
     <col width="10" customWidth="1" min="24" max="24"/>
-    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
     <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="21" customWidth="1" min="27" max="27"/>
     <col width="22" customWidth="1" min="28" max="28"/>
-    <col width="19" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="15" customWidth="1" min="31" max="31"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="19" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
     <col width="15" customWidth="1" min="32" max="32"/>
-    <col width="18" customWidth="1" min="33" max="33"/>
-    <col width="21" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
-    <col width="22" customWidth="1" min="36" max="36"/>
-    <col width="25" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="22" customWidth="1" min="37" max="37"/>
+    <col width="25" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5310,170 +5479,175 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>api_provider</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>input_per_million</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>output_per_million</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>cached_input_per_million</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>pricing_source</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>pricing_retrieved_at</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>summary_en</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>summary_ko</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>summary_en_chrf</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>summary_ko_chrf</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>summary_en_bertscore</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>summary_ko_bertscore</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>summary_en_surface_facts</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>summary_ko_surface_facts</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>halu_en_f1</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>halu_ko_f1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>halu_en_accuracy</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>halu_ko_accuracy</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>halu_ko_status</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>cls_en</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>cls_ko</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>cls_en_macro_f1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>cls_ko_macro_f1</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>cls_overall_accuracy</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>cls_overall_macro_f1</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>en_ko_consistency</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>input_tokens</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>output_tokens</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>cached_tokens</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>reasoning_tokens</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>openrouter_cost</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>judge_cost</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>fresh_cost_this_run</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>estimated_cache_savings</t>
         </is>
@@ -5497,108 +5671,113 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="G2" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="H2" s="3" t="n">
         <v>0.025</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>2026-09-16T03:02:43+00:00</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>0.180021324735549</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>0.221024648052918</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>28.32632418475155</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>13.84056050921727</v>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" s="4" t="n">
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" s="4" t="n">
         <v>0.8389154704944178</v>
       </c>
-      <c r="Q2" s="4" t="n">
+      <c r="R2" s="4" t="n">
         <v>0.964349376114082</v>
       </c>
-      <c r="R2" s="4" t="n">
+      <c r="S2" s="4" t="n">
         <v>0.7183462532299741</v>
       </c>
-      <c r="S2" s="4" t="n">
+      <c r="T2" s="4" t="n">
         <v>0.6112759643916914</v>
       </c>
-      <c r="T2" s="4" t="n">
+      <c r="U2" s="4" t="n">
         <v>0.7275</v>
       </c>
-      <c r="U2" s="4" t="n">
+      <c r="V2" s="4" t="n">
         <v>0.6725</v>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>0.891</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>0.87</v>
       </c>
-      <c r="Y2" s="4" t="n">
+      <c r="Z2" s="4" t="n">
         <v>0.8762568261606758</v>
       </c>
-      <c r="Z2" s="4" t="n">
+      <c r="AA2" s="4" t="n">
         <v>0.8425254254032213</v>
       </c>
-      <c r="AA2" s="4" t="n">
+      <c r="AB2" s="4" t="n">
         <v>0.8804999999999999</v>
       </c>
-      <c r="AB2" s="4" t="n">
+      <c r="AC2" s="4" t="n">
         <v>0.8564742197577885</v>
       </c>
-      <c r="AC2" s="4" t="n">
+      <c r="AD2" s="4" t="n">
         <v>0.9330000000000001</v>
       </c>
-      <c r="AD2" s="5" t="n">
+      <c r="AE2" s="5" t="n">
         <v>1098022</v>
       </c>
-      <c r="AE2" s="5" t="n">
+      <c r="AF2" s="5" t="n">
         <v>55664</v>
       </c>
-      <c r="AF2" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="AG2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AH2" s="3" t="n">
+      <c r="AH2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="3" t="n">
         <v>0.3580015</v>
       </c>
-      <c r="AI2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="3" t="n">
         <v>0.3334132499999996</v>
       </c>
-      <c r="AK2" s="3" t="n">
+      <c r="AL2" s="3" t="n">
         <v>0.02458824999999998</v>
       </c>
     </row>
@@ -5620,108 +5799,113 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="G3" s="3" t="n">
         <v>0.47</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="H3" s="3" t="n">
         <v>0.016</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-09-16T03:26:19+00:00</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>0.1621429745937464</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>0.2283869866974114</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>26.68302009498116</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>14.15140430658347</v>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" s="4" t="n">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" s="4" t="n">
         <v>0.8794037940379403</v>
       </c>
-      <c r="Q3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>0.9405594405594405</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="S3" s="4" t="n">
         <v>0.7596899224806202</v>
       </c>
-      <c r="S3" s="4" t="n">
+      <c r="T3" s="4" t="n">
         <v>0.5623003194888179</v>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>0.7675</v>
       </c>
-      <c r="U3" s="4" t="n">
+      <c r="V3" s="4" t="n">
         <v>0.6575</v>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>0.882</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>0.846</v>
       </c>
-      <c r="Y3" s="4" t="n">
+      <c r="Z3" s="4" t="n">
         <v>0.8710472576948233</v>
       </c>
-      <c r="Z3" s="4" t="n">
+      <c r="AA3" s="4" t="n">
         <v>0.8354346192098669</v>
       </c>
-      <c r="AA3" s="4" t="n">
+      <c r="AB3" s="4" t="n">
         <v>0.864</v>
       </c>
-      <c r="AB3" s="4" t="n">
+      <c r="AC3" s="4" t="n">
         <v>0.8523414150627505</v>
       </c>
-      <c r="AC3" s="4" t="n">
+      <c r="AD3" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="AD3" s="5" t="n">
+      <c r="AE3" s="5" t="n">
         <v>1061596</v>
       </c>
-      <c r="AE3" s="5" t="n">
+      <c r="AF3" s="5" t="n">
         <v>52179</v>
       </c>
-      <c r="AF3" s="5" t="n">
+      <c r="AG3" s="5" t="n">
         <v>265984</v>
       </c>
-      <c r="AG3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="3" t="n">
+      <c r="AH3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="3" t="n">
         <v>0.147925754</v>
       </c>
-      <c r="AI3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="3" t="n">
         <v>0.147925754</v>
       </c>
-      <c r="AK3" s="3" t="n">
+      <c r="AL3" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5743,108 +5927,113 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="G4" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="H4" s="3" t="n">
         <v>0.02</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>2026-09-16T02:59:08+00:00</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>0.1599680545649344</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>0.2296438059429992</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>26.76607327189645</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>13.96081188606404</v>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" s="4" t="n">
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" s="4" t="n">
         <v>0.9235668789808917</v>
       </c>
-      <c r="Q4" s="4" t="n">
+      <c r="R4" s="4" t="n">
         <v>0.9401574803149606</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="S4" s="4" t="n">
         <v>0.748129675810474</v>
       </c>
-      <c r="S4" s="4" t="n">
+      <c r="T4" s="4" t="n">
         <v>0.6520547945205479</v>
       </c>
-      <c r="T4" s="4" t="n">
+      <c r="U4" s="4" t="n">
         <v>0.7475000000000001</v>
       </c>
-      <c r="U4" s="4" t="n">
+      <c r="V4" s="4" t="n">
         <v>0.6825</v>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>0.868</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>0.831</v>
       </c>
-      <c r="Y4" s="4" t="n">
+      <c r="Z4" s="4" t="n">
         <v>0.8492172170319239</v>
       </c>
-      <c r="Z4" s="4" t="n">
+      <c r="AA4" s="4" t="n">
         <v>0.8000988567676002</v>
       </c>
-      <c r="AA4" s="4" t="n">
+      <c r="AB4" s="4" t="n">
         <v>0.8495</v>
       </c>
-      <c r="AB4" s="4" t="n">
+      <c r="AC4" s="4" t="n">
         <v>0.8278820044607954</v>
       </c>
-      <c r="AC4" s="4" t="n">
+      <c r="AD4" s="4" t="n">
         <v>0.895</v>
       </c>
-      <c r="AD4" s="5" t="n">
+      <c r="AE4" s="5" t="n">
         <v>1106945</v>
       </c>
-      <c r="AE4" s="5" t="n">
+      <c r="AF4" s="5" t="n">
         <v>55276</v>
       </c>
-      <c r="AF4" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="AG4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AH4" s="3" t="n">
+      <c r="AH4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="3" t="n">
         <v>0.31066625</v>
       </c>
-      <c r="AI4" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="3" t="n">
         <v>0.3106662500000003</v>
       </c>
-      <c r="AK4" s="3" t="n">
+      <c r="AL4" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5866,108 +6055,113 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="G5" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="H5" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>2026-09-16T03:05:27+00:00</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>0.1624008768665497</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>0.2286708213618012</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>25.83220416940711</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>13.80053671434364</v>
       </c>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" s="4" t="n">
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" s="4" t="n">
         <v>0.9100877192982456</v>
       </c>
-      <c r="Q5" s="4" t="n">
+      <c r="R5" s="4" t="n">
         <v>0.9710144927536232</v>
       </c>
-      <c r="R5" s="4" t="n">
+      <c r="S5" s="4" t="n">
         <v>0.6476190476190476</v>
       </c>
-      <c r="S5" s="4" t="n">
+      <c r="T5" s="4" t="n">
         <v>0.5830721003134797</v>
       </c>
-      <c r="T5" s="4" t="n">
+      <c r="U5" s="4" t="n">
         <v>0.7225</v>
       </c>
-      <c r="U5" s="4" t="n">
+      <c r="V5" s="4" t="n">
         <v>0.6675</v>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>0.843</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>0.823</v>
       </c>
-      <c r="Y5" s="4" t="n">
+      <c r="Z5" s="4" t="n">
         <v>0.8340438470244677</v>
       </c>
-      <c r="Z5" s="4" t="n">
+      <c r="AA5" s="4" t="n">
         <v>0.8081048779503196</v>
       </c>
-      <c r="AA5" s="4" t="n">
+      <c r="AB5" s="4" t="n">
         <v>0.833</v>
       </c>
-      <c r="AB5" s="4" t="n">
+      <c r="AC5" s="4" t="n">
         <v>0.8191126626634225</v>
       </c>
-      <c r="AC5" s="4" t="n">
+      <c r="AD5" s="4" t="n">
         <v>0.886</v>
       </c>
-      <c r="AD5" s="5" t="n">
+      <c r="AE5" s="5" t="n">
         <v>1097914</v>
       </c>
-      <c r="AE5" s="5" t="n">
+      <c r="AF5" s="5" t="n">
         <v>54986</v>
       </c>
-      <c r="AF5" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="AG5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" s="3" t="n">
+      <c r="AH5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="3" t="n">
         <v>0.1317858</v>
       </c>
-      <c r="AI5" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="3" t="n">
         <v>0.1317858</v>
       </c>
-      <c r="AK5" s="3" t="n">
+      <c r="AL5" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5989,108 +6183,113 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>0.05</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="G6" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="H6" s="3" t="n">
         <v>0.005</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>2026-09-16T04:40:49+00:00</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>0.1299020365576643</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>0.1992896265281343</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>23.01138546667206</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>11.48522300950568</v>
       </c>
-      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" s="4" t="n">
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" s="4" t="n">
         <v>0.949200376293509</v>
       </c>
-      <c r="Q6" s="4" t="n">
+      <c r="R6" s="4" t="n">
         <v>0.9549738219895288</v>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="S6" s="4" t="n">
         <v>0.6814814814814814</v>
       </c>
-      <c r="S6" s="4" t="n">
+      <c r="T6" s="4" t="n">
         <v>0.328125</v>
       </c>
-      <c r="T6" s="4" t="n">
+      <c r="U6" s="4" t="n">
         <v>0.6775</v>
       </c>
-      <c r="U6" s="4" t="n">
+      <c r="V6" s="4" t="n">
         <v>0.57</v>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>0.842</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>0.8149999999999999</v>
       </c>
-      <c r="Y6" s="4" t="n">
+      <c r="Z6" s="4" t="n">
         <v>0.8314865753296514</v>
       </c>
-      <c r="Z6" s="4" t="n">
+      <c r="AA6" s="4" t="n">
         <v>0.8034449936517111</v>
       </c>
-      <c r="AA6" s="4" t="n">
+      <c r="AB6" s="4" t="n">
         <v>0.8285</v>
       </c>
-      <c r="AB6" s="4" t="n">
+      <c r="AC6" s="4" t="n">
         <v>0.8179267929293625</v>
       </c>
-      <c r="AC6" s="4" t="n">
+      <c r="AD6" s="4" t="n">
         <v>0.863</v>
       </c>
-      <c r="AD6" s="5" t="n">
+      <c r="AE6" s="5" t="n">
         <v>1106945</v>
       </c>
-      <c r="AE6" s="5" t="n">
+      <c r="AF6" s="5" t="n">
         <v>548399</v>
       </c>
-      <c r="AF6" s="5" t="n">
+      <c r="AG6" s="5" t="n">
         <v>40320</v>
       </c>
-      <c r="AG6" s="5" t="n">
+      <c r="AH6" s="5" t="n">
         <v>433920</v>
       </c>
-      <c r="AH6" s="3" t="n">
+      <c r="AI6" s="3" t="n">
         <v>0.27289245</v>
       </c>
-      <c r="AI6" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="3" t="n">
         <v>0.2728924500000001</v>
       </c>
-      <c r="AK6" s="3" t="n">
+      <c r="AL6" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6112,108 +6311,113 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="G7" s="3" t="n">
         <v>0.3333</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="H7" s="3" t="n">
         <v>0.02</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>2026-09-16T04:41:38+00:00</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>0.1442957203978096</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>0.2059639679861038</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>24.60010668803035</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>13.49752283326942</v>
       </c>
-      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" s="4" t="n">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" s="4" t="n">
         <v>0.9221978021978022</v>
       </c>
-      <c r="Q7" s="4" t="n">
+      <c r="R7" s="4" t="n">
         <v>0.9633928571428572</v>
       </c>
-      <c r="R7" s="4" t="n">
+      <c r="S7" s="4" t="n">
         <v>0.72544080604534</v>
       </c>
-      <c r="S7" s="4" t="n">
+      <c r="T7" s="4" t="n">
         <v>0.5555555555555557</v>
       </c>
-      <c r="T7" s="4" t="n">
+      <c r="U7" s="4" t="n">
         <v>0.7275</v>
       </c>
-      <c r="U7" s="4" t="n">
+      <c r="V7" s="4" t="n">
         <v>0.64</v>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>0.858</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>0.797</v>
       </c>
-      <c r="Y7" s="4" t="n">
+      <c r="Z7" s="4" t="n">
         <v>0.846487306452871</v>
       </c>
-      <c r="Z7" s="4" t="n">
+      <c r="AA7" s="4" t="n">
         <v>0.7859849948864567</v>
       </c>
-      <c r="AA7" s="4" t="n">
+      <c r="AB7" s="4" t="n">
         <v>0.8275</v>
       </c>
-      <c r="AB7" s="4" t="n">
+      <c r="AC7" s="4" t="n">
         <v>0.8155753958777252</v>
       </c>
-      <c r="AC7" s="4" t="n">
+      <c r="AD7" s="4" t="n">
         <v>0.867</v>
       </c>
-      <c r="AD7" s="5" t="n">
+      <c r="AE7" s="5" t="n">
         <v>1293055</v>
       </c>
-      <c r="AE7" s="5" t="n">
+      <c r="AF7" s="5" t="n">
         <v>119092</v>
       </c>
-      <c r="AF7" s="5" t="n">
+      <c r="AG7" s="5" t="n">
         <v>104384</v>
       </c>
-      <c r="AG7" s="5" t="n">
+      <c r="AH7" s="5" t="n">
         <v>35855</v>
       </c>
-      <c r="AH7" s="3" t="n">
+      <c r="AI7" s="3" t="n">
         <v>0.21471714348</v>
       </c>
-      <c r="AI7" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="3" t="n">
         <v>0.2147171434799998</v>
       </c>
-      <c r="AK7" s="3" t="n">
+      <c r="AL7" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6235,108 +6439,113 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>0.055</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="G8" s="3" t="n">
         <v>0.11</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="H8" s="3" t="n">
         <v>0.011</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>2026-09-16T03:43:32+00:00</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>0.1602129689146955</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>0.2187402179219718</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>26.38968843606158</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>13.34734148800115</v>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" s="4" t="n">
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" s="4" t="n">
         <v>0.8983156581409857</v>
       </c>
-      <c r="Q8" s="4" t="n">
+      <c r="R8" s="4" t="n">
         <v>0.958904109589041</v>
       </c>
-      <c r="R8" s="4" t="n">
+      <c r="S8" s="4" t="n">
         <v>0.7204030226700252</v>
       </c>
-      <c r="S8" s="4" t="n">
+      <c r="T8" s="4" t="n">
         <v>0.6525821596244131</v>
       </c>
-      <c r="T8" s="4" t="n">
+      <c r="U8" s="4" t="n">
         <v>0.7225</v>
       </c>
-      <c r="U8" s="4" t="n">
+      <c r="V8" s="4" t="n">
         <v>0.63</v>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>0.803</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>0.802</v>
       </c>
-      <c r="Y8" s="4" t="n">
+      <c r="Z8" s="4" t="n">
         <v>0.7737251717218584</v>
       </c>
-      <c r="Z8" s="4" t="n">
+      <c r="AA8" s="4" t="n">
         <v>0.7760490357248214</v>
       </c>
-      <c r="AA8" s="4" t="n">
+      <c r="AB8" s="4" t="n">
         <v>0.8025</v>
       </c>
-      <c r="AB8" s="4" t="n">
+      <c r="AC8" s="4" t="n">
         <v>0.7750244596849166</v>
       </c>
-      <c r="AC8" s="4" t="n">
+      <c r="AD8" s="4" t="n">
         <v>0.851</v>
       </c>
-      <c r="AD8" s="5" t="n">
+      <c r="AE8" s="5" t="n">
         <v>1190712</v>
       </c>
-      <c r="AE8" s="5" t="n">
+      <c r="AF8" s="5" t="n">
         <v>63519</v>
       </c>
-      <c r="AF8" s="5" t="n">
+      <c r="AG8" s="5" t="n">
         <v>369477</v>
       </c>
-      <c r="AG8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="3" t="n">
+      <c r="AH8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3" t="n">
         <v>0.087699192003</v>
       </c>
-      <c r="AI8" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="3" t="n">
         <v>0.08769919200300014</v>
       </c>
-      <c r="AK8" s="3" t="n">
+      <c r="AL8" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6358,106 +6567,111 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>0.04815</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="G9" s="3" t="n">
         <v>0.19305</v>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>2026-09-16T03:34:40+00:00</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>0.1416464777859414</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>0.2093037662697218</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>24.38575174114155</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>12.78420991940304</v>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" s="4" t="n">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" s="4" t="n">
         <v>0.9091375770020534</v>
       </c>
-      <c r="Q9" s="4" t="n">
+      <c r="R9" s="4" t="n">
         <v>0.9739027283511269</v>
       </c>
-      <c r="R9" s="4" t="n">
+      <c r="S9" s="4" t="n">
         <v>0.6089743589743589</v>
       </c>
-      <c r="S9" s="4" t="n">
+      <c r="T9" s="4" t="n">
         <v>0.4191176470588235</v>
       </c>
-      <c r="T9" s="4" t="n">
+      <c r="U9" s="4" t="n">
         <v>0.695</v>
       </c>
-      <c r="U9" s="4" t="n">
+      <c r="V9" s="4" t="n">
         <v>0.605</v>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>0.8090000000000001</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>0.794</v>
       </c>
-      <c r="Y9" s="4" t="n">
+      <c r="Z9" s="4" t="n">
         <v>0.7992131261387427</v>
       </c>
-      <c r="Z9" s="4" t="n">
+      <c r="AA9" s="4" t="n">
         <v>0.7717528819109728</v>
       </c>
-      <c r="AA9" s="4" t="n">
+      <c r="AB9" s="4" t="n">
         <v>0.8015</v>
       </c>
-      <c r="AB9" s="4" t="n">
+      <c r="AC9" s="4" t="n">
         <v>0.7855676169719019</v>
       </c>
-      <c r="AC9" s="4" t="n">
+      <c r="AD9" s="4" t="n">
         <v>0.865</v>
       </c>
-      <c r="AD9" s="5" t="n">
+      <c r="AE9" s="5" t="n">
         <v>1213604</v>
       </c>
-      <c r="AE9" s="5" t="n">
+      <c r="AF9" s="5" t="n">
         <v>72595</v>
       </c>
-      <c r="AF9" s="5" t="n">
+      <c r="AG9" s="5" t="n">
         <v>102934</v>
       </c>
-      <c r="AG9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="3" t="n">
+      <c r="AH9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="3" t="n">
         <v>0.12323393625</v>
       </c>
-      <c r="AI9" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="3" t="n">
         <v>0.1232339362500001</v>
       </c>
-      <c r="AK9" s="3" t="n">
+      <c r="AL9" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6479,108 +6693,113 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>0.03</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="G10" s="3" t="n">
         <v>0.13</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="H10" s="3" t="n">
         <v>0.006</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>2026-09-16T03:31:23+00:00</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>0.1608350962342315</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>0.2302580020788956</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>26.04951109641535</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>13.75572799407668</v>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" s="4" t="n">
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" s="4" t="n">
         <v>0.8816067653276956</v>
       </c>
-      <c r="Q10" s="4" t="n">
+      <c r="R10" s="4" t="n">
         <v>0.947463768115942</v>
       </c>
-      <c r="R10" s="4" t="n">
+      <c r="S10" s="4" t="n">
         <v>0.6589595375722543</v>
       </c>
-      <c r="S10" s="4" t="n">
+      <c r="T10" s="4" t="n">
         <v>0.5407166123778501</v>
       </c>
-      <c r="T10" s="4" t="n">
+      <c r="U10" s="4" t="n">
         <v>0.705</v>
       </c>
-      <c r="U10" s="4" t="n">
+      <c r="V10" s="4" t="n">
         <v>0.6475</v>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>0.796</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>0.76</v>
       </c>
-      <c r="Y10" s="4" t="n">
+      <c r="Z10" s="4" t="n">
         <v>0.7792340968020122</v>
       </c>
-      <c r="Z10" s="4" t="n">
+      <c r="AA10" s="4" t="n">
         <v>0.7439524644750251</v>
       </c>
-      <c r="AA10" s="4" t="n">
+      <c r="AB10" s="4" t="n">
         <v>0.778</v>
       </c>
-      <c r="AB10" s="4" t="n">
+      <c r="AC10" s="4" t="n">
         <v>0.7614406146917927</v>
       </c>
-      <c r="AC10" s="4" t="n">
+      <c r="AD10" s="4" t="n">
         <v>0.832</v>
       </c>
-      <c r="AD10" s="5" t="n">
+      <c r="AE10" s="5" t="n">
         <v>1061596</v>
       </c>
-      <c r="AE10" s="5" t="n">
+      <c r="AF10" s="5" t="n">
         <v>51608</v>
       </c>
-      <c r="AF10" s="5" t="n">
+      <c r="AG10" s="5" t="n">
         <v>24960</v>
       </c>
-      <c r="AG10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="3" t="n">
+      <c r="AH10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="3" t="n">
         <v>0.03791827</v>
       </c>
-      <c r="AI10" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="3" t="n">
         <v>0.03791826999999996</v>
       </c>
-      <c r="AK10" s="3" t="n">
+      <c r="AL10" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6602,108 +6821,113 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>COMPLETED</t>
         </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0.2</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="G11" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H11" s="3" t="n">
         <v>0.02</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>2026-09-16T03:10:41+00:00</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>0.1340643496794257</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>0.200848621976299</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>23.15600037313629</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>12.32917653667287</v>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" s="4" t="n">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" s="4" t="n">
         <v>0.8982440342188204</v>
       </c>
-      <c r="Q11" s="4" t="n">
+      <c r="R11" s="4" t="n">
         <v>0.9363636363636364</v>
       </c>
-      <c r="R11" s="4" t="n">
+      <c r="S11" s="4" t="n">
         <v>0.7163461538461539</v>
       </c>
-      <c r="S11" s="4" t="n">
+      <c r="T11" s="4" t="n">
         <v>0.683291770573566</v>
       </c>
-      <c r="T11" s="4" t="n">
+      <c r="U11" s="4" t="n">
         <v>0.705</v>
       </c>
-      <c r="U11" s="4" t="n">
+      <c r="V11" s="4" t="n">
         <v>0.6825</v>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>0.78</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>0.744</v>
       </c>
-      <c r="Y11" s="4" t="n">
+      <c r="Z11" s="4" t="n">
         <v>0.7603515978750895</v>
       </c>
-      <c r="Z11" s="4" t="n">
+      <c r="AA11" s="4" t="n">
         <v>0.7113942857254609</v>
       </c>
-      <c r="AA11" s="4" t="n">
+      <c r="AB11" s="4" t="n">
         <v>0.762</v>
       </c>
-      <c r="AB11" s="4" t="n">
+      <c r="AC11" s="4" t="n">
         <v>0.736163325053324</v>
       </c>
-      <c r="AC11" s="4" t="n">
+      <c r="AD11" s="4" t="n">
         <v>0.824</v>
       </c>
-      <c r="AD11" s="5" t="n">
+      <c r="AE11" s="5" t="n">
         <v>1092316</v>
       </c>
-      <c r="AE11" s="5" t="n">
+      <c r="AF11" s="5" t="n">
         <v>71944</v>
       </c>
-      <c r="AF11" s="5" t="n">
+      <c r="AG11" s="5" t="n">
         <v>295936</v>
       </c>
-      <c r="AG11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="3" t="n">
+      <c r="AH11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="3" t="n">
         <v>0.17958352</v>
       </c>
-      <c r="AI11" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="3" t="n">
         <v>0.1795835200000001</v>
       </c>
-      <c r="AK11" s="3" t="n">
+      <c r="AL11" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6725,108 +6949,113 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>COMPLETED</t>
         </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>0.15</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0.15</v>
       </c>
       <c r="G12" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H12" s="3" t="n">
         <v>0.015</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>2026-09-16T03:15:02+00:00</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>0.1338576862477163</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>0.2022785739193924</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>23.2893881252992</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>12.28128440018327</v>
       </c>
-      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" s="4" t="n">
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" s="4" t="n">
         <v>0.8798944126704795</v>
       </c>
-      <c r="Q12" s="4" t="n">
+      <c r="R12" s="4" t="n">
         <v>0.9474768280123584</v>
       </c>
-      <c r="R12" s="4" t="n">
+      <c r="S12" s="4" t="n">
         <v>0.6366366366366367</v>
       </c>
-      <c r="S12" s="4" t="n">
+      <c r="T12" s="4" t="n">
         <v>0.5857988165680473</v>
       </c>
-      <c r="T12" s="4" t="n">
+      <c r="U12" s="4" t="n">
         <v>0.6975</v>
       </c>
-      <c r="U12" s="4" t="n">
+      <c r="V12" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>0.738</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>0.737</v>
       </c>
-      <c r="Y12" s="4" t="n">
+      <c r="Z12" s="4" t="n">
         <v>0.7285750142849275</v>
       </c>
-      <c r="Z12" s="4" t="n">
+      <c r="AA12" s="4" t="n">
         <v>0.712693713084553</v>
       </c>
-      <c r="AA12" s="4" t="n">
+      <c r="AB12" s="4" t="n">
         <v>0.7375</v>
       </c>
-      <c r="AB12" s="4" t="n">
+      <c r="AC12" s="4" t="n">
         <v>0.7216311867724771</v>
       </c>
-      <c r="AC12" s="4" t="n">
+      <c r="AD12" s="4" t="n">
         <v>0.763</v>
       </c>
-      <c r="AD12" s="5" t="n">
+      <c r="AE12" s="5" t="n">
         <v>1092316</v>
       </c>
-      <c r="AE12" s="5" t="n">
+      <c r="AF12" s="5" t="n">
         <v>71698</v>
       </c>
-      <c r="AF12" s="5" t="n">
+      <c r="AG12" s="5" t="n">
         <v>299392</v>
       </c>
-      <c r="AG12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="3" t="n">
+      <c r="AH12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="3" t="n">
         <v>0.13418418</v>
       </c>
-      <c r="AI12" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="3" t="n">
         <v>0.1341841799999999</v>
       </c>
-      <c r="AK12" s="3" t="n">
+      <c r="AL12" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6848,108 +7077,113 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="G13" s="3" t="n">
         <v>1.25</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="H13" s="3" t="n">
         <v>0.02</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>2026-09-16T03:20:07+00:00</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>0.1303590348428198</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>0.1872998825564791</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>23.22067206524886</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>11.95596092668423</v>
       </c>
-      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" s="4" t="n">
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" s="4" t="n">
         <v>0.961978928080623</v>
       </c>
-      <c r="Q13" s="4" t="n">
+      <c r="R13" s="4" t="n">
         <v>0.9586330935251799</v>
       </c>
-      <c r="R13" s="4" t="n">
+      <c r="S13" s="4" t="n">
         <v>0.6149068322981366</v>
       </c>
-      <c r="S13" s="4" t="n">
+      <c r="T13" s="4" t="n">
         <v>0.2382978723404255</v>
       </c>
-      <c r="T13" s="4" t="n">
+      <c r="U13" s="4" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="U13" s="4" t="n">
+      <c r="V13" s="4" t="n">
         <v>0.5525</v>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>0.715</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>0.661</v>
       </c>
-      <c r="Y13" s="4" t="n">
+      <c r="Z13" s="4" t="n">
         <v>0.7079848008862988</v>
       </c>
-      <c r="Z13" s="4" t="n">
+      <c r="AA13" s="4" t="n">
         <v>0.6593342425290085</v>
       </c>
-      <c r="AA13" s="4" t="n">
+      <c r="AB13" s="4" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="AB13" s="4" t="n">
+      <c r="AC13" s="4" t="n">
         <v>0.6845822094887644</v>
       </c>
-      <c r="AC13" s="4" t="n">
+      <c r="AD13" s="4" t="n">
         <v>0.718</v>
       </c>
-      <c r="AD13" s="5" t="n">
+      <c r="AE13" s="5" t="n">
         <v>1106945</v>
       </c>
-      <c r="AE13" s="5" t="n">
+      <c r="AF13" s="5" t="n">
         <v>75745</v>
       </c>
-      <c r="AF13" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="AG13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AH13" s="3" t="n">
+      <c r="AH13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3" t="n">
         <v>0.31607025</v>
       </c>
-      <c r="AI13" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3" t="n">
         <v>0.3160702499999996</v>
       </c>
-      <c r="AK13" s="3" t="n">
+      <c r="AL13" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6971,108 +7205,113 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="G14" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="H14" s="3" t="n">
         <v>0.015</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>2026-09-16T03:07:59+00:00</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>0.1486748430163934</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>0.2158566833442461</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>24.85170132045256</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>12.57729783101797</v>
       </c>
-      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" s="4" t="n">
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" s="4" t="n">
         <v>0.9259462424574877</v>
       </c>
-      <c r="Q14" s="4" t="n">
+      <c r="R14" s="4" t="n">
         <v>0.9627450980392157</v>
       </c>
-      <c r="R14" s="4" t="n">
+      <c r="S14" s="4" t="n">
         <v>0.7247956403269755</v>
       </c>
-      <c r="S14" s="4" t="n">
+      <c r="T14" s="4" t="n">
         <v>0.6195652173913043</v>
       </c>
-      <c r="T14" s="4" t="n">
+      <c r="U14" s="4" t="n">
         <v>0.7475000000000001</v>
       </c>
-      <c r="U14" s="4" t="n">
+      <c r="V14" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>0.509</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Y14" t="n">
         <v>0.711</v>
       </c>
-      <c r="Y14" s="4" t="n">
+      <c r="Z14" s="4" t="n">
         <v>0.5867378280355483</v>
       </c>
-      <c r="Z14" s="4" t="n">
+      <c r="AA14" s="4" t="n">
         <v>0.7031769757373104</v>
       </c>
-      <c r="AA14" s="4" t="n">
+      <c r="AB14" s="4" t="n">
         <v>0.61</v>
       </c>
-      <c r="AB14" s="4" t="n">
+      <c r="AC14" s="4" t="n">
         <v>0.6504937686437986</v>
       </c>
-      <c r="AC14" s="4" t="n">
+      <c r="AD14" s="4" t="n">
         <v>0.7</v>
       </c>
-      <c r="AD14" s="5" t="n">
+      <c r="AE14" s="5" t="n">
         <v>1107916</v>
       </c>
-      <c r="AE14" s="5" t="n">
+      <c r="AF14" s="5" t="n">
         <v>62923</v>
       </c>
-      <c r="AF14" s="5" t="n">
+      <c r="AG14" s="5" t="n">
         <v>183856</v>
       </c>
-      <c r="AG14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3" t="n">
+      <c r="AH14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="n">
         <v>0.1964076975</v>
       </c>
-      <c r="AI14" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="n">
         <v>0.1964076975000001</v>
       </c>
-      <c r="AK14" s="3" t="n">
+      <c r="AL14" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7094,236 +7333,336 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>COMPLETED</t>
         </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>0.1</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="G15" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H15" s="3" t="n">
         <v>0.01</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>2026-09-16T03:17:56+00:00</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>0.1344392234965607</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>0.1976921128927562</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>23.21465695587321</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>11.65156743434614</v>
       </c>
-      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" s="4" t="n">
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" s="4" t="n">
         <v>0.886284289276808</v>
       </c>
-      <c r="Q15" s="4" t="n">
+      <c r="R15" s="4" t="n">
         <v>0.9119420989143546</v>
       </c>
-      <c r="R15" s="4" t="n">
+      <c r="S15" s="4" t="n">
         <v>0.6757493188010899</v>
       </c>
-      <c r="S15" s="4" t="n">
+      <c r="T15" s="4" t="n">
         <v>0.5591939546599498</v>
       </c>
-      <c r="T15" s="4" t="n">
+      <c r="U15" s="4" t="n">
         <v>0.7025</v>
       </c>
-      <c r="U15" s="4" t="n">
+      <c r="V15" s="4" t="n">
         <v>0.5625</v>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
         <v>0.465</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Y15" t="n">
         <v>0.606</v>
       </c>
-      <c r="Y15" s="4" t="n">
+      <c r="Z15" s="4" t="n">
         <v>0.5053205391654078</v>
       </c>
-      <c r="Z15" s="4" t="n">
+      <c r="AA15" s="4" t="n">
         <v>0.5671517703461975</v>
       </c>
-      <c r="AA15" s="4" t="n">
+      <c r="AB15" s="4" t="n">
         <v>0.5355</v>
       </c>
-      <c r="AB15" s="4" t="n">
+      <c r="AC15" s="4" t="n">
         <v>0.5411026333400099</v>
       </c>
-      <c r="AC15" s="4" t="n">
+      <c r="AD15" s="4" t="n">
         <v>0.651</v>
       </c>
-      <c r="AD15" s="5" t="n">
+      <c r="AE15" s="5" t="n">
         <v>1092316</v>
       </c>
-      <c r="AE15" s="5" t="n">
+      <c r="AF15" s="5" t="n">
         <v>69602</v>
       </c>
-      <c r="AF15" s="5" t="n">
+      <c r="AG15" s="5" t="n">
         <v>318592</v>
       </c>
-      <c r="AG15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="3" t="n">
+      <c r="AH15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3" t="n">
         <v>0.08751852</v>
       </c>
-      <c r="AI15" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3" t="n">
         <v>0.08751852</v>
       </c>
-      <c r="AK15" s="3" t="n">
+      <c r="AL15" s="3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Qwen2.5 1.5B Instruct (GGUF Q8_0, local)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="E16" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>openrouter</t>
-        </is>
-      </c>
+      <c r="F16" s="3" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:30+00:00</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>0.1434021604287071</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.2194519351485593</v>
-      </c>
-      <c r="L16" t="n">
-        <v>24.49324424955361</v>
-      </c>
-      <c r="M16" t="n">
-        <v>12.31697458631575</v>
-      </c>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" s="4" t="n">
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" s="4" t="inlineStr"/>
+      <c r="R16" s="4" t="inlineStr"/>
+      <c r="S16" s="4" t="inlineStr"/>
+      <c r="T16" s="4" t="inlineStr"/>
+      <c r="U16" s="4" t="inlineStr"/>
+      <c r="V16" s="4" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="Z16" s="4" t="n">
+        <v>0.5462394606984829</v>
+      </c>
+      <c r="AA16" s="4" t="n">
+        <v>0.4240113868989582</v>
+      </c>
+      <c r="AB16" s="4" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="AC16" s="4" t="n">
+        <v>0.4911253511380655</v>
+      </c>
+      <c r="AD16" s="4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AE16" s="5" t="n">
+        <v>1441986</v>
+      </c>
+      <c r="AF16" s="5" t="n">
+        <v>10903</v>
+      </c>
+      <c r="AG16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>openai/gpt-4.1-nano</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GPT-4.1 Nano</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-09-16T03:23:30+00:00</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0.1434021604287071</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.2194519351485593</v>
+      </c>
+      <c r="M17" t="n">
+        <v>24.49324424955361</v>
+      </c>
+      <c r="N17" t="n">
+        <v>12.31697458631575</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" s="4" t="n">
         <v>0.8991138377641446</v>
       </c>
-      <c r="Q16" s="4" t="n">
+      <c r="R17" s="4" t="n">
         <v>0.9558232931726908</v>
       </c>
-      <c r="R16" s="4" t="n">
+      <c r="S17" s="4" t="n">
         <v>0.7005347593582888</v>
       </c>
-      <c r="S16" s="4" t="n">
+      <c r="T17" s="4" t="n">
         <v>0.5421686746987951</v>
       </c>
-      <c r="T16" s="4" t="n">
+      <c r="U17" s="4" t="n">
         <v>0.72</v>
       </c>
-      <c r="U16" s="4" t="n">
+      <c r="V17" s="4" t="n">
         <v>0.62</v>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="W16" t="n">
+      <c r="X17" t="n">
         <v>0.529</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Y17" t="n">
         <v>0.398</v>
       </c>
-      <c r="Y16" s="4" t="n">
+      <c r="Z17" s="4" t="n">
         <v>0.5140122481389001</v>
       </c>
-      <c r="Z16" s="4" t="n">
+      <c r="AA17" s="4" t="n">
         <v>0.3758955615145875</v>
       </c>
-      <c r="AA16" s="4" t="n">
+      <c r="AB17" s="4" t="n">
         <v>0.4635</v>
       </c>
-      <c r="AB16" s="4" t="n">
+      <c r="AC17" s="4" t="n">
         <v>0.4473337487719194</v>
       </c>
-      <c r="AC16" s="4" t="n">
+      <c r="AD17" s="4" t="n">
         <v>0.731</v>
       </c>
-      <c r="AD16" s="5" t="n">
+      <c r="AE17" s="5" t="n">
         <v>1108245</v>
       </c>
-      <c r="AE16" s="5" t="n">
+      <c r="AF17" s="5" t="n">
         <v>55419</v>
       </c>
-      <c r="AF16" s="5" t="n">
+      <c r="AG17" s="5" t="n">
         <v>36224</v>
       </c>
-      <c r="AG16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="3" t="n">
+      <c r="AH17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="3" t="n">
         <v>0.1302753</v>
       </c>
-      <c r="AI16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" s="3" t="n">
+      <c r="AJ17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="3" t="n">
         <v>0.1302753</v>
       </c>
-      <c r="AK16" s="3" t="n">
+      <c r="AL17" s="3" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK16"/>
+  <autoFilter ref="A1:AL17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10828,15 +11167,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -11207,12 +11546,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen2.5 1.5B Instruct (GGUF Q8_0, local)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -11224,13 +11563,13 @@
         <v>1000</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.78</v>
+        <v>0.575</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.7603515978750895</v>
+        <v>0.5462394606984829</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>780</v>
+        <v>575</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>0</v>
@@ -11242,12 +11581,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen2.5 1.5B Instruct (GGUF Q8_0, local)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -11259,13 +11598,13 @@
         <v>1000</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.744</v>
+        <v>0.463</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.7113942857254609</v>
+        <v>0.4240113868989582</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>744</v>
+        <v>463</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>0</v>
@@ -11277,12 +11616,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen2.5 1.5B Instruct (GGUF Q8_0, local)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -11294,13 +11633,13 @@
         <v>2000</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.762</v>
+        <v>0.519</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.736163325053324</v>
+        <v>0.4911253511380655</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1524</v>
+        <v>1038</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>0</v>
@@ -11312,12 +11651,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -11329,16 +11668,16 @@
         <v>1000</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.465</v>
+        <v>0.78</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.5053205391654078</v>
+        <v>0.7603515978750895</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>465</v>
+        <v>780</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.322</v>
+        <v>0</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>60</v>
@@ -11347,12 +11686,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -11364,16 +11703,16 @@
         <v>1000</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.606</v>
+        <v>0.744</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.5671517703461975</v>
+        <v>0.7113942857254609</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>606</v>
+        <v>744</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>60</v>
@@ -11382,12 +11721,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -11399,16 +11738,16 @@
         <v>2000</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.5355</v>
+        <v>0.762</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.5411026333400099</v>
+        <v>0.736163325053324</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1071</v>
+        <v>1524</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.165</v>
+        <v>0</v>
       </c>
       <c r="I16" s="5" t="n">
         <v>60</v>
@@ -11417,12 +11756,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -11434,16 +11773,16 @@
         <v>1000</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.738</v>
+        <v>0.465</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.7285750142849275</v>
+        <v>0.5053205391654078</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>738</v>
+        <v>465</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.042</v>
+        <v>0.322</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>60</v>
@@ -11452,12 +11791,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -11469,16 +11808,16 @@
         <v>1000</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.737</v>
+        <v>0.606</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.712693713084553</v>
+        <v>0.5671517703461975</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>737</v>
+        <v>606</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>60</v>
@@ -11487,12 +11826,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -11504,16 +11843,16 @@
         <v>2000</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.7375</v>
+        <v>0.5355</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.7216311867724771</v>
+        <v>0.5411026333400099</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>1475</v>
+        <v>1071</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.021</v>
+        <v>0.165</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>60</v>
@@ -11522,12 +11861,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -11539,16 +11878,16 @@
         <v>1000</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.509</v>
+        <v>0.738</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.5867378280355483</v>
+        <v>0.7285750142849275</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>509</v>
+        <v>738</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.343</v>
+        <v>0.042</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>60</v>
@@ -11557,12 +11896,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -11574,16 +11913,16 @@
         <v>1000</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.711</v>
+        <v>0.737</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.7031769757373104</v>
+        <v>0.712693713084553</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>711</v>
+        <v>737</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="I21" s="5" t="n">
         <v>60</v>
@@ -11592,12 +11931,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -11609,16 +11948,16 @@
         <v>2000</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.61</v>
+        <v>0.7375</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.6504937686437986</v>
+        <v>0.7216311867724771</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1220</v>
+        <v>1475</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.202</v>
+        <v>0.021</v>
       </c>
       <c r="I22" s="5" t="n">
         <v>60</v>
@@ -11627,12 +11966,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -11644,16 +11983,16 @@
         <v>1000</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.529</v>
+        <v>0.509</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.5140122481389001</v>
+        <v>0.5867378280355483</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>529</v>
+        <v>509</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0</v>
+        <v>0.343</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>60</v>
@@ -11662,12 +12001,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -11679,16 +12018,16 @@
         <v>1000</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.398</v>
+        <v>0.711</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3758955615145875</v>
+        <v>0.7031769757373104</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>398</v>
+        <v>711</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="I24" s="5" t="n">
         <v>60</v>
@@ -11697,12 +12036,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -11714,16 +12053,16 @@
         <v>2000</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.4635</v>
+        <v>0.61</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.4473337487719194</v>
+        <v>0.6504937686437986</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>927</v>
+        <v>1220</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0</v>
+        <v>0.202</v>
       </c>
       <c r="I25" s="5" t="n">
         <v>60</v>
@@ -11732,12 +12071,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -11749,13 +12088,13 @@
         <v>1000</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.842</v>
+        <v>0.529</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.8314865753296514</v>
+        <v>0.5140122481389001</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>842</v>
+        <v>529</v>
       </c>
       <c r="H26" s="4" t="n">
         <v>0</v>
@@ -11767,12 +12106,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -11784,13 +12123,13 @@
         <v>1000</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.398</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.8034449936517111</v>
+        <v>0.3758955615145875</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>815</v>
+        <v>398</v>
       </c>
       <c r="H27" s="4" t="n">
         <v>0</v>
@@ -11802,12 +12141,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -11819,13 +12158,13 @@
         <v>2000</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.8285</v>
+        <v>0.4635</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.8179267929293625</v>
+        <v>0.4473337487719194</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>1657</v>
+        <v>927</v>
       </c>
       <c r="H28" s="4" t="n">
         <v>0</v>
@@ -11837,12 +12176,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -11854,16 +12193,16 @@
         <v>1000</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.715</v>
+        <v>0.842</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.7079848008862988</v>
+        <v>0.8314865753296514</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>715</v>
+        <v>842</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="I29" s="5" t="n">
         <v>60</v>
@@ -11872,12 +12211,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -11889,16 +12228,16 @@
         <v>1000</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.661</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.6593342425290085</v>
+        <v>0.8034449936517111</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>661</v>
+        <v>815</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I30" s="5" t="n">
         <v>60</v>
@@ -11907,12 +12246,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -11924,16 +12263,16 @@
         <v>2000</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.8285</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.6845822094887644</v>
+        <v>0.8179267929293625</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>1376</v>
+        <v>1657</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I31" s="5" t="n">
         <v>60</v>
@@ -11942,12 +12281,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -11959,16 +12298,16 @@
         <v>1000</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.868</v>
+        <v>0.715</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.8492172170319239</v>
+        <v>0.7079848008862988</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>868</v>
+        <v>715</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>60</v>
@@ -11977,12 +12316,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -11994,16 +12333,16 @@
         <v>1000</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.831</v>
+        <v>0.661</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.8000988567676002</v>
+        <v>0.6593342425290085</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>831</v>
+        <v>661</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>60</v>
@@ -12012,12 +12351,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -12029,16 +12368,16 @@
         <v>2000</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.8495</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.8278820044607954</v>
+        <v>0.6845822094887644</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1699</v>
+        <v>1376</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>60</v>
@@ -12047,12 +12386,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -12064,16 +12403,16 @@
         <v>1000</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.868</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.7992131261387427</v>
+        <v>0.8492172170319239</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>809</v>
+        <v>868</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I35" s="5" t="n">
         <v>60</v>
@@ -12082,12 +12421,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -12099,13 +12438,13 @@
         <v>1000</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.794</v>
+        <v>0.831</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.7717528819109728</v>
+        <v>0.8000988567676002</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>794</v>
+        <v>831</v>
       </c>
       <c r="H36" s="4" t="n">
         <v>0</v>
@@ -12117,12 +12456,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -12134,16 +12473,16 @@
         <v>2000</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.8015</v>
+        <v>0.8495</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.7855676169719019</v>
+        <v>0.8278820044607954</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1603</v>
+        <v>1699</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I37" s="5" t="n">
         <v>60</v>
@@ -12152,12 +12491,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -12169,13 +12508,13 @@
         <v>1000</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.796</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.7792340968020122</v>
+        <v>0.7992131261387427</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>796</v>
+        <v>809</v>
       </c>
       <c r="H38" s="4" t="n">
         <v>0.02</v>
@@ -12187,12 +12526,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -12204,16 +12543,16 @@
         <v>1000</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.76</v>
+        <v>0.794</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.7439524644750251</v>
+        <v>0.7717528819109728</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>760</v>
+        <v>794</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I39" s="5" t="n">
         <v>60</v>
@@ -12222,12 +12561,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -12239,16 +12578,16 @@
         <v>2000</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.778</v>
+        <v>0.8015</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.7614406146917927</v>
+        <v>0.7855676169719019</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>1556</v>
+        <v>1603</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="I40" s="5" t="n">
         <v>60</v>
@@ -12257,12 +12596,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -12274,16 +12613,16 @@
         <v>1000</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.882</v>
+        <v>0.796</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.8710472576948233</v>
+        <v>0.7792340968020122</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>882</v>
+        <v>796</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I41" s="5" t="n">
         <v>60</v>
@@ -12292,12 +12631,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -12309,16 +12648,16 @@
         <v>1000</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.846</v>
+        <v>0.76</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.8354346192098669</v>
+        <v>0.7439524644750251</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>846</v>
+        <v>760</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I42" s="5" t="n">
         <v>60</v>
@@ -12327,12 +12666,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -12344,16 +12683,16 @@
         <v>2000</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.864</v>
+        <v>0.778</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.8523414150627505</v>
+        <v>0.7614406146917927</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>1728</v>
+        <v>1556</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I43" s="5" t="n">
         <v>60</v>
@@ -12362,12 +12701,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -12379,13 +12718,13 @@
         <v>1000</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.858</v>
+        <v>0.882</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.846487306452871</v>
+        <v>0.8710472576948233</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>858</v>
+        <v>882</v>
       </c>
       <c r="H44" s="4" t="n">
         <v>0</v>
@@ -12397,12 +12736,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -12414,16 +12753,16 @@
         <v>1000</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.797</v>
+        <v>0.846</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.7859849948864567</v>
+        <v>0.8354346192098669</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>797</v>
+        <v>846</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I45" s="5" t="n">
         <v>60</v>
@@ -12432,12 +12771,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -12449,23 +12788,128 @@
         <v>2000</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.8275</v>
+        <v>0.864</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.8155753958777252</v>
+        <v>0.8523414150627505</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>1655</v>
+        <v>1728</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I46" s="5" t="n">
         <v>60</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>0.846487306452871</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>858</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>0.7859849948864567</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>797</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>0.8275</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>0.8155753958777252</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>1655</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I46"/>
+  <autoFilter ref="A1:I49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12476,11 +12920,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
@@ -12699,545 +13143,590 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen2.5 1.5B Instruct (GGUF Q8_0, local)</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.824</v>
+        <v>0.7</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.768</v>
+        <v>0.541</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>674</v>
+        <v>369</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.674</v>
+        <v>0.369</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>106</v>
+        <v>206</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.106</v>
+        <v>0.206</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.094</v>
       </c>
       <c r="L5" t="n">
-        <v>150</v>
+        <v>331</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.15</v>
+        <v>0.331</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.651</v>
+        <v>0.824</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.43</v>
+        <v>0.768</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>361</v>
+        <v>674</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.361</v>
+        <v>0.674</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.104</v>
+        <v>0.106</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>245</v>
+        <v>70</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.245</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>290</v>
+        <v>150</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.29</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.763</v>
+        <v>0.651</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.695</v>
+        <v>0.43</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>619</v>
+        <v>361</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.619</v>
+        <v>0.361</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.119</v>
+        <v>0.104</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>118</v>
+        <v>245</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.118</v>
+        <v>0.245</v>
       </c>
       <c r="L7" t="n">
-        <v>144</v>
+        <v>290</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.144</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.7</v>
+        <v>0.763</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.519</v>
+        <v>0.695</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>460</v>
+        <v>619</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.46</v>
+        <v>0.619</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.049</v>
+        <v>0.119</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>251</v>
+        <v>118</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.251</v>
+        <v>0.118</v>
       </c>
       <c r="L8" t="n">
-        <v>240</v>
+        <v>144</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.24</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.731</v>
+        <v>0.7</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.505</v>
+        <v>0.519</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>329</v>
+        <v>460</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.329</v>
+        <v>0.46</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>200</v>
+        <v>49</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.2</v>
+        <v>0.049</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>69</v>
+        <v>251</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.251</v>
       </c>
       <c r="L9" t="n">
-        <v>402</v>
+        <v>240</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.402</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.863</v>
+        <v>0.731</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.833</v>
+        <v>0.505</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>760</v>
+        <v>329</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.76</v>
+        <v>0.329</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.082</v>
+        <v>0.2</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.055</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>103</v>
+        <v>402</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.103</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.718</v>
+        <v>0.863</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.612</v>
+        <v>0.833</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>547</v>
+        <v>760</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.547</v>
+        <v>0.76</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.168</v>
+        <v>0.082</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.114</v>
+        <v>0.055</v>
       </c>
       <c r="L11" t="n">
-        <v>171</v>
+        <v>103</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.171</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.895</v>
+        <v>0.718</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.866</v>
+        <v>0.612</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>797</v>
+        <v>547</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.797</v>
+        <v>0.547</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>71</v>
+        <v>168</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.168</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.034</v>
+        <v>0.114</v>
       </c>
       <c r="L12" t="n">
-        <v>98</v>
+        <v>171</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.098</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.865</v>
+        <v>0.895</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.866</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>734</v>
+        <v>797</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.734</v>
+        <v>0.797</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.075</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.06</v>
+        <v>0.034</v>
       </c>
       <c r="L13" t="n">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.131</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.832</v>
+        <v>0.865</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.77</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>694</v>
+        <v>734</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.694</v>
+        <v>0.734</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.102</v>
+        <v>0.075</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.066</v>
+        <v>0.06</v>
       </c>
       <c r="L14" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.138</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.91</v>
+        <v>0.832</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.887</v>
+        <v>0.77</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>819</v>
+        <v>694</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.819</v>
+        <v>0.694</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.063</v>
+        <v>0.102</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.027</v>
+        <v>0.066</v>
       </c>
       <c r="L15" t="n">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.091</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D16" s="4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>819</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="L16" t="n">
+        <v>91</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>0.091</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D17" s="4" t="n">
         <v>0.867</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E17" s="4" t="n">
         <v>0.822</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F17" s="5" t="n">
         <v>761</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>0.761</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="H17" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="I17" s="4" t="n">
         <v>0.097</v>
       </c>
-      <c r="J16" s="5" t="n">
+      <c r="J17" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="K16" s="4" t="n">
+      <c r="K17" s="4" t="n">
         <v>0.036</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L17" t="n">
         <v>106</v>
       </c>
-      <c r="M16" s="4" t="n">
+      <c r="M17" s="4" t="n">
         <v>0.106</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M16"/>
+  <autoFilter ref="A1:M17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results/benchmark_results.xlsx
+++ b/results/benchmark_results.xlsx
@@ -23,17 +23,17 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Legend'!$A$1:$D$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Leaderboard'!$A$1:$AL$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Leaderboard'!$A$1:$AL$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Summarization'!$A$1:$P$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Hallucination'!$A$1:$O$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Classification'!$A$1:$I$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'CrossLingual'!$A$1:$M$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Classification'!$A$1:$I$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'CrossLingual'!$A$1:$M$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'ClassificationModes'!$A$1:$K$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'SurfaceFacts'!$A$1:$L$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cost'!$A$1:$S$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Usage'!$A$1:$M$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cost'!$A$1:$S$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Usage'!$A$1:$M$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Judge'!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Runs'!$A$1:$T$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Runs'!$A$1:$T$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -516,7 +516,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T01:55:51+00:00</t>
+          <t>2026-09-17T03:05:00+00:00</t>
         </is>
       </c>
     </row>
@@ -647,11 +647,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -977,7 +977,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Instruct (GGUF Q8_0, local)</t>
+          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -1009,89 +1009,59 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.2</v>
-      </c>
+          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-16T03:10:41+00:00</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0.07769180000000001</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>0.08999796</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0.01189376</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0.17958352</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>0.1795835200000001</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>0.17958352</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>0.1795835200000001</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>0.17958352</v>
-      </c>
-      <c r="S6" t="b">
-        <v>1</v>
-      </c>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1100,17 +1070,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-16T03:17:56+00:00</t>
+          <t>2026-09-16T03:10:41+00:00</t>
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.0385285</v>
+        <v>0.07769180000000001</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.0433295</v>
+        <v>0.08999796</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.00566052</v>
+        <v>0.01189376</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
@@ -1119,22 +1089,22 @@
         <v>0</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.08751852</v>
+        <v>0.17958352</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.08751852</v>
+        <v>0.1795835200000001</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.08751852</v>
+        <v>0.17958352</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.08751852</v>
+        <v>0.1795835200000001</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.08751852</v>
+        <v>0.17958352</v>
       </c>
       <c r="S7" t="b">
         <v>1</v>
@@ -1143,22 +1113,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1167,17 +1137,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-16T03:15:02+00:00</t>
+          <t>2026-09-16T03:17:56+00:00</t>
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.0582456</v>
+        <v>0.0385285</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.06753291</v>
+        <v>0.0433295</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.008405670000000001</v>
+        <v>0.00566052</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1186,22 +1156,22 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.13418418</v>
+        <v>0.08751852</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.1341841799999999</v>
+        <v>0.08751852</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0.13418418</v>
+        <v>0.08751852</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.1341841799999999</v>
+        <v>0.08751852</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.13418418</v>
+        <v>0.08751852</v>
       </c>
       <c r="S8" t="b">
         <v>1</v>
@@ -1210,12 +1180,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
@@ -1225,7 +1195,7 @@
         <v>0.015</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1234,17 +1204,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-16T03:07:59+00:00</t>
+          <t>2026-09-16T03:15:02+00:00</t>
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.0802729125</v>
+        <v>0.0582456</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.0986139</v>
+        <v>0.06753291</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.017520885</v>
+        <v>0.008405670000000001</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>0</v>
@@ -1253,46 +1223,46 @@
         <v>0</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.1964076975</v>
+        <v>0.13418418</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0.1964076975000001</v>
+        <v>0.1341841799999999</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0.1964076975</v>
+        <v>0.13418418</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0.1964076975000001</v>
+        <v>0.1341841799999999</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.17912064</v>
+        <v>0.13418418</v>
       </c>
       <c r="S9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1301,17 +1271,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:30+00:00</t>
+          <t>2026-09-16T03:07:59+00:00</t>
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.0519185</v>
+        <v>0.0802729125</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.067397</v>
+        <v>0.0986139</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.0109598</v>
+        <v>0.017520885</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0</v>
@@ -1320,43 +1290,43 @@
         <v>0</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.1964076975</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.1964076975000001</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.1964076975</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.1964076975000001</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.1302753</v>
+        <v>0.17912064</v>
       </c>
       <c r="S10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.005</v>
+        <v>0.025</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0.4</v>
@@ -1368,17 +1338,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-16T04:40:49+00:00</t>
+          <t>2026-09-16T03:23:30+00:00</t>
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.08205585</v>
+        <v>0.0519185</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.1433661</v>
+        <v>0.067397</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.0474705</v>
+        <v>0.0109598</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
@@ -1387,22 +1357,22 @@
         <v>0</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.27289245</v>
+        <v>0.1302753</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.2728924500000001</v>
+        <v>0.1302753</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.27289245</v>
+        <v>0.1302753</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.2728924500000001</v>
+        <v>0.1302753</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.27289245</v>
+        <v>0.1302753</v>
       </c>
       <c r="S11" t="b">
         <v>1</v>
@@ -1411,22 +1381,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1.25</v>
+        <v>0.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1435,17 +1405,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-16T03:20:07+00:00</t>
+          <t>2026-09-16T04:40:49+00:00</t>
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.1453735</v>
+        <v>0.08205585</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.1435934</v>
+        <v>0.1433661</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.02710335</v>
+        <v>0.0474705</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1454,22 +1424,22 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.31607025</v>
+        <v>0.27289245</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.3160702499999996</v>
+        <v>0.2728924500000001</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0.31607025</v>
+        <v>0.27289245</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.3160702499999996</v>
+        <v>0.2728924500000001</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.3160702500000001</v>
+        <v>0.27289245</v>
       </c>
       <c r="S12" t="b">
         <v>1</v>
@@ -1478,12 +1448,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -1493,7 +1463,7 @@
         <v>0.02</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1502,17 +1472,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-16T02:59:08+00:00</t>
+          <t>2026-09-16T03:20:07+00:00</t>
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.12600455</v>
+        <v>0.1453735</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.1584021</v>
+        <v>0.1435934</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.0262596</v>
+        <v>0.02710335</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
@@ -1521,44 +1491,46 @@
         <v>0</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>0.31066625</v>
+        <v>0.31607025</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.3106662500000003</v>
+        <v>0.3160702499999996</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>0.31066625</v>
+        <v>0.31607025</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.3106662500000003</v>
+        <v>0.3160702499999996</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.2877202</v>
+        <v>0.3160702500000001</v>
       </c>
       <c r="S13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.04815</v>
-      </c>
-      <c r="D14" s="3" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0.02</v>
+      </c>
       <c r="E14" s="3" t="n">
-        <v>0.19305</v>
+        <v>1.2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1567,17 +1539,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-16T03:34:40+00:00</t>
+          <t>2026-09-16T02:59:08+00:00</t>
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.04959875775</v>
+        <v>0.12600455</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.06309176505</v>
+        <v>0.1584021</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.01054341345</v>
+        <v>0.0262596</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0</v>
@@ -1586,22 +1558,22 @@
         <v>0</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>0.12323393625</v>
+        <v>0.31066625</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.1232339362500001</v>
+        <v>0.3106662500000003</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.12323393625</v>
+        <v>0.31066625</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.1232339362500001</v>
+        <v>0.3106662500000003</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.07244949735</v>
+        <v>0.2877202</v>
       </c>
       <c r="S14" t="b">
         <v>0</v>
@@ -1610,22 +1582,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>0.006</v>
-      </c>
+        <v>0.04815</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr"/>
       <c r="E15" s="3" t="n">
-        <v>0.13</v>
+        <v>0.19305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1634,17 +1604,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-16T03:31:23+00:00</t>
+          <t>2026-09-16T03:34:40+00:00</t>
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.01445385</v>
+        <v>0.04959875775</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.01955122</v>
+        <v>0.06309176505</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.0039132</v>
+        <v>0.01054341345</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>0</v>
@@ -1653,46 +1623,46 @@
         <v>0</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0.03791827</v>
+        <v>0.12323393625</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>0.03791826999999996</v>
+        <v>0.1232339362500001</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>0.03791827</v>
+        <v>0.12323393625</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0.03791826999999996</v>
+        <v>0.1232339362500001</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.03795787999999999</v>
+        <v>0.07244949735</v>
       </c>
       <c r="S15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.016</v>
+        <v>0.006</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.47</v>
+        <v>0.13</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1701,17 +1671,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-16T03:26:19+00:00</t>
+          <t>2026-09-16T03:31:23+00:00</t>
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.06590207000000001</v>
+        <v>0.01445385</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.068078582</v>
+        <v>0.01955122</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.013945102</v>
+        <v>0.0039132</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>0</v>
@@ -1720,22 +1690,22 @@
         <v>0</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.03791827</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.03791826999999996</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.03791827</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.03791826999999996</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.148121674</v>
+        <v>0.03795787999999999</v>
       </c>
       <c r="S16" t="b">
         <v>1</v>
@@ -1744,72 +1714,139 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>qwen/qwen3.8-flash</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Qwen3.8 Flash</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-09-16T03:26:19+00:00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>0.06590207000000001</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>0.068078582</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>0.013945102</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>0.147925754</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>0.147925754</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>0.147925754</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>0.147925754</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>0.148121674</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>z-ai/glm-5.3-flash</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>GLM 5.3 Flash</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C18" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>0.02</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>0.3333</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>2026-09-16T04:41:38+00:00</t>
         </is>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H18" s="3" t="n">
         <v>0.0828101102</v>
       </c>
-      <c r="I17" s="3" t="n">
+      <c r="I18" s="3" t="n">
         <v>0.11700001578</v>
       </c>
-      <c r="J17" s="3" t="n">
+      <c r="J18" s="3" t="n">
         <v>0.0149070175</v>
       </c>
-      <c r="K17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3" t="n">
+      <c r="K18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3" t="n">
         <v>0.21471714348</v>
       </c>
-      <c r="N17" s="3" t="n">
+      <c r="N18" s="3" t="n">
         <v>0.2147171434799998</v>
       </c>
-      <c r="O17" s="3" t="n">
+      <c r="O18" s="3" t="n">
         <v>0.21471714348</v>
       </c>
-      <c r="P17" s="3" t="n">
+      <c r="P18" s="3" t="n">
         <v>0.2147171434799998</v>
       </c>
-      <c r="Q17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="4" t="n">
+      <c r="Q18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="4" t="n">
         <v>0.1606481436</v>
       </c>
-      <c r="S17" t="b">
+      <c r="S18" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S17"/>
+  <autoFilter ref="A1:S18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1820,11 +1857,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -2048,7 +2085,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Instruct (GGUF Q8_0, local)</t>
+          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
@@ -2073,72 +2110,72 @@
         <v>1452889</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1300</v>
+        <v>2000</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>1092316</v>
+        <v>720993</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>295936</v>
+        <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>71944</v>
+        <v>0</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>1164260</v>
+        <v>720993</v>
       </c>
       <c r="J6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>1300</v>
+        <v>2000</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>1300</v>
+        <v>2000</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>1300</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
@@ -2148,19 +2185,19 @@
         <v>1092316</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>318592</v>
+        <v>295936</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>69602</v>
+        <v>71944</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>1161918</v>
+        <v>1164260</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>0</v>
@@ -2178,12 +2215,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
@@ -2193,19 +2230,19 @@
         <v>1092316</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>299392</v>
+        <v>318592</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>71698</v>
+        <v>69602</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>1164014</v>
+        <v>1161918</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>0</v>
@@ -2223,34 +2260,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1107916</v>
+        <v>1092316</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>183856</v>
+        <v>299392</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>62923</v>
+        <v>71698</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>1170839</v>
+        <v>1164014</v>
       </c>
       <c r="J9" s="5" t="n">
         <v>0</v>
@@ -2268,34 +2305,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1108245</v>
+        <v>1107916</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>36224</v>
+        <v>183856</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>55419</v>
+        <v>62923</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>1163664</v>
+        <v>1170839</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>0</v>
@@ -2313,34 +2350,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1106945</v>
+        <v>1108245</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>40320</v>
+        <v>36224</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>548399</v>
+        <v>55419</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>433920</v>
+        <v>0</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>1655344</v>
+        <v>1163664</v>
       </c>
       <c r="J11" s="5" t="n">
         <v>0</v>
@@ -2358,12 +2395,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
@@ -2373,19 +2410,19 @@
         <v>1106945</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0</v>
+        <v>40320</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>75745</v>
+        <v>548399</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0</v>
+        <v>433920</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>1182690</v>
+        <v>1655344</v>
       </c>
       <c r="J12" s="5" t="n">
         <v>0</v>
@@ -2403,12 +2440,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
@@ -2421,16 +2458,16 @@
         <v>0</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>458921</v>
+        <v>0</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>55276</v>
+        <v>75745</v>
       </c>
       <c r="H13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>1162221</v>
+        <v>1182690</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>0</v>
@@ -2448,34 +2485,34 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1213604</v>
+        <v>1106945</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>102934</v>
+        <v>0</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0</v>
+        <v>458921</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>72595</v>
+        <v>55276</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>1286199</v>
+        <v>1162221</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>0</v>
@@ -2493,34 +2530,34 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1061596</v>
+        <v>1213604</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>24960</v>
+        <v>102934</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>51608</v>
+        <v>72595</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>1113204</v>
+        <v>1286199</v>
       </c>
       <c r="J15" s="5" t="n">
         <v>0</v>
@@ -2532,18 +2569,18 @@
         <v>1300</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>1307</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -2553,19 +2590,19 @@
         <v>1061596</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>265984</v>
+        <v>24960</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>52179</v>
+        <v>51608</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>1113775</v>
+        <v>1113204</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>0</v>
@@ -2577,40 +2614,40 @@
         <v>1300</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>1314</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1293055</v>
+        <v>1061596</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>104384</v>
+        <v>265984</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>119092</v>
+        <v>52179</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>35855</v>
+        <v>0</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>1412147</v>
+        <v>1113775</v>
       </c>
       <c r="J17" s="5" t="n">
         <v>0</v>
@@ -2622,11 +2659,56 @@
         <v>1300</v>
       </c>
       <c r="M17" s="5" t="n">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
         <v>1300</v>
       </c>
+      <c r="D18" s="5" t="n">
+        <v>1293055</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>104384</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>119092</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>35855</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>1412147</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>1300</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M17"/>
+  <autoFilter ref="A1:M18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2662,10 +2744,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
@@ -3042,17 +3124,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>run-20260917T013544-81d671a6</t>
+          <t>run-20260917T030240-7b921abc</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T01:52:22+00:00</t>
+          <t>2026-09-17T03:02:41+00:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-17T01:35:44+00:00</t>
+          <t>2026-09-17T03:02:40+00:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3062,7 +3144,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7d940a780adb2d63730876016bcc16115c9bd8e2</t>
+          <t>62bd51cc58aff3b5128149c0e7098fc7bb1caa80</t>
         </is>
       </c>
       <c r="H5" t="b">
@@ -3118,7 +3200,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3128,17 +3210,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>run-20260916T031043-60c30b6a</t>
+          <t>run-20260917T023435-d6148d1a</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:15:02+00:00</t>
+          <t>2026-09-17T03:02:38+00:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-16T03:10:43+00:00</t>
+          <t>2026-09-17T02:34:35+00:00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3146,8 +3228,14 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>62bd51cc58aff3b5128149c0e7098fc7bb1caa80</t>
+        </is>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -3155,7 +3243,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>summarization, hallucination, classification</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3164,7 +3252,7 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>3200</v>
+        <v>2000</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -3198,7 +3286,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3208,17 +3296,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>run-20260916T031757-6f0019bc</t>
+          <t>run-20260916T031043-60c30b6a</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:20:07+00:00</t>
+          <t>2026-09-16T03:15:02+00:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-16T03:17:57+00:00</t>
+          <t>2026-09-16T03:10:43+00:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3278,7 +3366,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3288,17 +3376,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>run-20260916T031504-7b84cf7d</t>
+          <t>run-20260916T031757-6f0019bc</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:17:56+00:00</t>
+          <t>2026-09-16T03:20:07+00:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-16T03:15:04+00:00</t>
+          <t>2026-09-16T03:17:57+00:00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3358,7 +3446,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3368,17 +3456,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>run-20260916T030801-577d0830</t>
+          <t>run-20260916T031504-7b84cf7d</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:10:41+00:00</t>
+          <t>2026-09-16T03:17:56+00:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-16T03:08:01+00:00</t>
+          <t>2026-09-16T03:15:04+00:00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3438,7 +3526,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3448,17 +3536,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>run-20260916T032332-5a24afb2</t>
+          <t>run-20260916T030801-577d0830</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:26:19+00:00</t>
+          <t>2026-09-16T03:10:41+00:00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:32+00:00</t>
+          <t>2026-09-16T03:08:01+00:00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3518,7 +3606,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3528,17 +3616,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>run-20260916T044051-1b0d71da</t>
+          <t>run-20260916T032332-5a24afb2</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T04:51:21+00:00</t>
+          <t>2026-09-16T03:26:19+00:00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-16T04:40:51+00:00</t>
+          <t>2026-09-16T03:23:32+00:00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3546,14 +3634,8 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -3604,7 +3686,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3614,17 +3696,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>run-20260916T032009-aca77564</t>
+          <t>run-20260916T044051-1b0d71da</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:28+00:00</t>
+          <t>2026-09-16T04:51:21+00:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-16T03:20:09+00:00</t>
+          <t>2026-09-16T04:40:51+00:00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3632,8 +3714,14 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
+        </is>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -3684,7 +3772,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3694,17 +3782,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>run-20260916T025909-be4eb782</t>
+          <t>run-20260916T032009-aca77564</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:02:43+00:00</t>
+          <t>2026-09-16T03:23:28+00:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-16T02:59:09+00:00</t>
+          <t>2026-09-16T03:20:09+00:00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3764,7 +3852,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3774,17 +3862,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>run-20260916T033441-93cb685e</t>
+          <t>run-20260916T025909-be4eb782</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:43:30+00:00</t>
+          <t>2026-09-16T03:02:43+00:00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-16T03:34:41+00:00</t>
+          <t>2026-09-16T02:59:09+00:00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3844,7 +3932,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3854,17 +3942,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>run-20260916T033125-8730c140</t>
+          <t>run-20260916T033441-93cb685e</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:34:40+00:00</t>
+          <t>2026-09-16T03:43:30+00:00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-16T03:31:25+00:00</t>
+          <t>2026-09-16T03:34:41+00:00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3924,7 +4012,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3934,17 +4022,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>run-20260916T032621-2ec5c283</t>
+          <t>run-20260916T033125-8730c140</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:31:23+00:00</t>
+          <t>2026-09-16T03:34:40+00:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-16T03:26:21+00:00</t>
+          <t>2026-09-16T03:31:25+00:00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4004,7 +4092,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4014,17 +4102,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>run-20260916T044139-f5eda9f3</t>
+          <t>run-20260916T032621-2ec5c283</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T04:51:13+00:00</t>
+          <t>2026-09-16T03:31:23+00:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-16T04:41:39+00:00</t>
+          <t>2026-09-16T03:26:21+00:00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4032,14 +4120,8 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
-        </is>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -4087,8 +4169,94 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>run-20260916T044139-f5eda9f3</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16T04:51:13+00:00</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-09-16T04:41:39+00:00</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
+        </is>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3.12.3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>summarization, hallucination, classification</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>en, ko</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>3200</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>cbe6fb9c14d4b2b12e690d6565e05bcf861c5db26cc56aef45e3e3810f67b298</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0135c4f4499e35dcde7855ad6afe33e333ebf2bca519a20b81257dc39150cd62</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>21debf696ed02ef001638142e2864a1bb58be409f88d8c86ad36e067ee609ca5</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>b49d914db700703584e2388f602808314a59c9e088a20f02e670ead58141fa96</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1bebd7a4e6cab622b3a85e6f856e019c9459100085c08ca38ccec107d5e3ec21</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T17"/>
+  <autoFilter ref="A1:T18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5418,11 +5586,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL17"/>
+  <dimension ref="A1:AL18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -7451,7 +7619,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Instruct (GGUF Q8_0, local)</t>
+          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -7499,22 +7667,22 @@
         <v>0.575</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.463</v>
+        <v>0.462</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.5462394606984829</v>
+        <v>0.5459294856069367</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>0.4240113868989582</v>
+        <v>0.4217011621299711</v>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>0.519</v>
+        <v>0.5185</v>
       </c>
       <c r="AC16" s="4" t="n">
-        <v>0.4911253511380655</v>
+        <v>0.4882467464725742</v>
       </c>
       <c r="AD16" s="4" t="n">
-        <v>0.7</v>
+        <v>0.713</v>
       </c>
       <c r="AE16" s="5" t="n">
         <v>1441986</v>
@@ -7536,22 +7704,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>local</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7559,110 +7727,200 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>0.025</v>
-      </c>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:30+00:00</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>0.1434021604287071</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.2194519351485593</v>
-      </c>
-      <c r="M17" t="n">
-        <v>24.49324424955361</v>
-      </c>
-      <c r="N17" t="n">
-        <v>12.31697458631575</v>
-      </c>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" s="4" t="n">
+      <c r="Q17" s="4" t="inlineStr"/>
+      <c r="R17" s="4" t="inlineStr"/>
+      <c r="S17" s="4" t="inlineStr"/>
+      <c r="T17" s="4" t="inlineStr"/>
+      <c r="U17" s="4" t="inlineStr"/>
+      <c r="V17" s="4" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="Z17" s="4" t="n">
+        <v>0.5388418311648718</v>
+      </c>
+      <c r="AA17" s="4" t="n">
+        <v>0.4135867824853839</v>
+      </c>
+      <c r="AB17" s="4" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="AC17" s="4" t="n">
+        <v>0.4814069197519245</v>
+      </c>
+      <c r="AD17" s="4" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="AE17" s="5" t="n">
+        <v>720993</v>
+      </c>
+      <c r="AF17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="3" t="inlineStr"/>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>openai/gpt-4.1-nano</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GPT-4.1 Nano</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-09-16T03:23:30+00:00</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0.1434021604287071</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.2194519351485593</v>
+      </c>
+      <c r="M18" t="n">
+        <v>24.49324424955361</v>
+      </c>
+      <c r="N18" t="n">
+        <v>12.31697458631575</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" s="4" t="n">
         <v>0.8991138377641446</v>
       </c>
-      <c r="R17" s="4" t="n">
+      <c r="R18" s="4" t="n">
         <v>0.9558232931726908</v>
       </c>
-      <c r="S17" s="4" t="n">
+      <c r="S18" s="4" t="n">
         <v>0.7005347593582888</v>
       </c>
-      <c r="T17" s="4" t="n">
+      <c r="T18" s="4" t="n">
         <v>0.5421686746987951</v>
       </c>
-      <c r="U17" s="4" t="n">
+      <c r="U18" s="4" t="n">
         <v>0.72</v>
       </c>
-      <c r="V17" s="4" t="n">
+      <c r="V18" s="4" t="n">
         <v>0.62</v>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X17" t="n">
+      <c r="X18" t="n">
         <v>0.529</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Y18" t="n">
         <v>0.398</v>
       </c>
-      <c r="Z17" s="4" t="n">
+      <c r="Z18" s="4" t="n">
         <v>0.5140122481389001</v>
       </c>
-      <c r="AA17" s="4" t="n">
+      <c r="AA18" s="4" t="n">
         <v>0.3758955615145875</v>
       </c>
-      <c r="AB17" s="4" t="n">
+      <c r="AB18" s="4" t="n">
         <v>0.4635</v>
       </c>
-      <c r="AC17" s="4" t="n">
+      <c r="AC18" s="4" t="n">
         <v>0.4473337487719194</v>
       </c>
-      <c r="AD17" s="4" t="n">
+      <c r="AD18" s="4" t="n">
         <v>0.731</v>
       </c>
-      <c r="AE17" s="5" t="n">
+      <c r="AE18" s="5" t="n">
         <v>1108245</v>
       </c>
-      <c r="AF17" s="5" t="n">
+      <c r="AF18" s="5" t="n">
         <v>55419</v>
       </c>
-      <c r="AG17" s="5" t="n">
+      <c r="AG18" s="5" t="n">
         <v>36224</v>
       </c>
-      <c r="AH17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" s="3" t="n">
+      <c r="AH18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="3" t="n">
         <v>0.1302753</v>
       </c>
-      <c r="AJ17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="3" t="n">
+      <c r="AJ18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="3" t="n">
         <v>0.1302753</v>
       </c>
-      <c r="AL17" s="3" t="n">
+      <c r="AL18" s="3" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL17"/>
+  <autoFilter ref="A1:AL18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11167,11 +11425,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -11551,7 +11809,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Instruct (GGUF Q8_0, local)</t>
+          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -11566,7 +11824,7 @@
         <v>0.575</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.5462394606984829</v>
+        <v>0.5459294856069367</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>575</v>
@@ -11586,7 +11844,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Instruct (GGUF Q8_0, local)</t>
+          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -11598,13 +11856,13 @@
         <v>1000</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.463</v>
+        <v>0.462</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.4240113868989582</v>
+        <v>0.4217011621299711</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>0</v>
@@ -11621,7 +11879,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Instruct (GGUF Q8_0, local)</t>
+          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -11633,13 +11891,13 @@
         <v>2000</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.519</v>
+        <v>0.5185</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.4911253511380655</v>
+        <v>0.4882467464725742</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>0</v>
@@ -11651,12 +11909,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -11668,13 +11926,13 @@
         <v>1000</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.78</v>
+        <v>0.573</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.7603515978750895</v>
+        <v>0.5388418311648718</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>780</v>
+        <v>573</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>0</v>
@@ -11686,12 +11944,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -11703,13 +11961,13 @@
         <v>1000</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.744</v>
+        <v>0.457</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.7113942857254609</v>
+        <v>0.4135867824853839</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>744</v>
+        <v>457</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>0</v>
@@ -11721,12 +11979,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -11738,13 +11996,13 @@
         <v>2000</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.762</v>
+        <v>0.515</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.736163325053324</v>
+        <v>0.4814069197519245</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1524</v>
+        <v>1030</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>0</v>
@@ -11756,12 +12014,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -11773,16 +12031,16 @@
         <v>1000</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.465</v>
+        <v>0.78</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.5053205391654078</v>
+        <v>0.7603515978750895</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>465</v>
+        <v>780</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.322</v>
+        <v>0</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>60</v>
@@ -11791,12 +12049,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -11808,16 +12066,16 @@
         <v>1000</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.606</v>
+        <v>0.744</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.5671517703461975</v>
+        <v>0.7113942857254609</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>606</v>
+        <v>744</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>60</v>
@@ -11826,12 +12084,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -11843,16 +12101,16 @@
         <v>2000</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.5355</v>
+        <v>0.762</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.5411026333400099</v>
+        <v>0.736163325053324</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>1071</v>
+        <v>1524</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.165</v>
+        <v>0</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>60</v>
@@ -11861,12 +12119,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -11878,16 +12136,16 @@
         <v>1000</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.738</v>
+        <v>0.465</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.7285750142849275</v>
+        <v>0.5053205391654078</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>738</v>
+        <v>465</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.042</v>
+        <v>0.322</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>60</v>
@@ -11896,12 +12154,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -11913,16 +12171,16 @@
         <v>1000</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.737</v>
+        <v>0.606</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.712693713084553</v>
+        <v>0.5671517703461975</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>737</v>
+        <v>606</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="I21" s="5" t="n">
         <v>60</v>
@@ -11931,12 +12189,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -11948,16 +12206,16 @@
         <v>2000</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.7375</v>
+        <v>0.5355</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.7216311867724771</v>
+        <v>0.5411026333400099</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1475</v>
+        <v>1071</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.021</v>
+        <v>0.165</v>
       </c>
       <c r="I22" s="5" t="n">
         <v>60</v>
@@ -11966,12 +12224,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -11983,16 +12241,16 @@
         <v>1000</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.509</v>
+        <v>0.738</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.5867378280355483</v>
+        <v>0.7285750142849275</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>509</v>
+        <v>738</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.343</v>
+        <v>0.042</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>60</v>
@@ -12001,12 +12259,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -12018,16 +12276,16 @@
         <v>1000</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.711</v>
+        <v>0.737</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.7031769757373104</v>
+        <v>0.712693713084553</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>711</v>
+        <v>737</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="I24" s="5" t="n">
         <v>60</v>
@@ -12036,12 +12294,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -12053,16 +12311,16 @@
         <v>2000</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.61</v>
+        <v>0.7375</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.6504937686437986</v>
+        <v>0.7216311867724771</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1220</v>
+        <v>1475</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.202</v>
+        <v>0.021</v>
       </c>
       <c r="I25" s="5" t="n">
         <v>60</v>
@@ -12071,12 +12329,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -12088,16 +12346,16 @@
         <v>1000</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.529</v>
+        <v>0.509</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.5140122481389001</v>
+        <v>0.5867378280355483</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>529</v>
+        <v>509</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0</v>
+        <v>0.343</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>60</v>
@@ -12106,12 +12364,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -12123,16 +12381,16 @@
         <v>1000</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.398</v>
+        <v>0.711</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.3758955615145875</v>
+        <v>0.7031769757373104</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>398</v>
+        <v>711</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="I27" s="5" t="n">
         <v>60</v>
@@ -12141,12 +12399,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -12158,16 +12416,16 @@
         <v>2000</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.4635</v>
+        <v>0.61</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.4473337487719194</v>
+        <v>0.6504937686437986</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>927</v>
+        <v>1220</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0</v>
+        <v>0.202</v>
       </c>
       <c r="I28" s="5" t="n">
         <v>60</v>
@@ -12176,12 +12434,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -12193,13 +12451,13 @@
         <v>1000</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.842</v>
+        <v>0.529</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.8314865753296514</v>
+        <v>0.5140122481389001</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>842</v>
+        <v>529</v>
       </c>
       <c r="H29" s="4" t="n">
         <v>0</v>
@@ -12211,12 +12469,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -12228,13 +12486,13 @@
         <v>1000</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.398</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.8034449936517111</v>
+        <v>0.3758955615145875</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>815</v>
+        <v>398</v>
       </c>
       <c r="H30" s="4" t="n">
         <v>0</v>
@@ -12246,12 +12504,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -12263,13 +12521,13 @@
         <v>2000</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.8285</v>
+        <v>0.4635</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.8179267929293625</v>
+        <v>0.4473337487719194</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>1657</v>
+        <v>927</v>
       </c>
       <c r="H31" s="4" t="n">
         <v>0</v>
@@ -12281,12 +12539,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -12298,16 +12556,16 @@
         <v>1000</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.715</v>
+        <v>0.842</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.7079848008862988</v>
+        <v>0.8314865753296514</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>715</v>
+        <v>842</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>60</v>
@@ -12316,12 +12574,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -12333,16 +12591,16 @@
         <v>1000</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.661</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.6593342425290085</v>
+        <v>0.8034449936517111</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>661</v>
+        <v>815</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>60</v>
@@ -12351,12 +12609,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -12368,16 +12626,16 @@
         <v>2000</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.8285</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.6845822094887644</v>
+        <v>0.8179267929293625</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1376</v>
+        <v>1657</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>60</v>
@@ -12386,12 +12644,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -12403,16 +12661,16 @@
         <v>1000</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.868</v>
+        <v>0.715</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.8492172170319239</v>
+        <v>0.7079848008862988</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>868</v>
+        <v>715</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="I35" s="5" t="n">
         <v>60</v>
@@ -12421,12 +12679,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -12438,16 +12696,16 @@
         <v>1000</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.831</v>
+        <v>0.661</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.8000988567676002</v>
+        <v>0.6593342425290085</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>831</v>
+        <v>661</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I36" s="5" t="n">
         <v>60</v>
@@ -12456,12 +12714,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -12473,16 +12731,16 @@
         <v>2000</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.8495</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.8278820044607954</v>
+        <v>0.6845822094887644</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1699</v>
+        <v>1376</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I37" s="5" t="n">
         <v>60</v>
@@ -12491,12 +12749,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -12508,16 +12766,16 @@
         <v>1000</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.868</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.7992131261387427</v>
+        <v>0.8492172170319239</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>809</v>
+        <v>868</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I38" s="5" t="n">
         <v>60</v>
@@ -12526,12 +12784,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -12543,13 +12801,13 @@
         <v>1000</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.794</v>
+        <v>0.831</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.7717528819109728</v>
+        <v>0.8000988567676002</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>794</v>
+        <v>831</v>
       </c>
       <c r="H39" s="4" t="n">
         <v>0</v>
@@ -12561,12 +12819,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -12578,16 +12836,16 @@
         <v>2000</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.8015</v>
+        <v>0.8495</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.7855676169719019</v>
+        <v>0.8278820044607954</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>1603</v>
+        <v>1699</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I40" s="5" t="n">
         <v>60</v>
@@ -12596,12 +12854,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -12613,13 +12871,13 @@
         <v>1000</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.796</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.7792340968020122</v>
+        <v>0.7992131261387427</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>796</v>
+        <v>809</v>
       </c>
       <c r="H41" s="4" t="n">
         <v>0.02</v>
@@ -12631,12 +12889,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -12648,16 +12906,16 @@
         <v>1000</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.76</v>
+        <v>0.794</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.7439524644750251</v>
+        <v>0.7717528819109728</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>760</v>
+        <v>794</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I42" s="5" t="n">
         <v>60</v>
@@ -12666,12 +12924,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -12683,16 +12941,16 @@
         <v>2000</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.778</v>
+        <v>0.8015</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.7614406146917927</v>
+        <v>0.7855676169719019</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>1556</v>
+        <v>1603</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="I43" s="5" t="n">
         <v>60</v>
@@ -12701,12 +12959,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -12718,16 +12976,16 @@
         <v>1000</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.882</v>
+        <v>0.796</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.8710472576948233</v>
+        <v>0.7792340968020122</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>882</v>
+        <v>796</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I44" s="5" t="n">
         <v>60</v>
@@ -12736,12 +12994,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -12753,16 +13011,16 @@
         <v>1000</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.846</v>
+        <v>0.76</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.8354346192098669</v>
+        <v>0.7439524644750251</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>846</v>
+        <v>760</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I45" s="5" t="n">
         <v>60</v>
@@ -12771,12 +13029,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -12788,16 +13046,16 @@
         <v>2000</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.864</v>
+        <v>0.778</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.8523414150627505</v>
+        <v>0.7614406146917927</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>1728</v>
+        <v>1556</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I46" s="5" t="n">
         <v>60</v>
@@ -12806,12 +13064,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -12823,13 +13081,13 @@
         <v>1000</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.858</v>
+        <v>0.882</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.846487306452871</v>
+        <v>0.8710472576948233</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>858</v>
+        <v>882</v>
       </c>
       <c r="H47" s="4" t="n">
         <v>0</v>
@@ -12841,12 +13099,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -12858,16 +13116,16 @@
         <v>1000</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.797</v>
+        <v>0.846</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.7859849948864567</v>
+        <v>0.8354346192098669</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>797</v>
+        <v>846</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I48" s="5" t="n">
         <v>60</v>
@@ -12876,12 +13134,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -12893,23 +13151,128 @@
         <v>2000</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.8275</v>
+        <v>0.864</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.8155753958777252</v>
+        <v>0.8523414150627505</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>1655</v>
+        <v>1728</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I49" s="5" t="n">
         <v>60</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>0.846487306452871</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>858</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>0.7859849948864567</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>797</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>0.8275</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>0.8155753958777252</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>1655</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I49"/>
+  <autoFilter ref="A1:I52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12920,11 +13283,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
@@ -13148,585 +13511,630 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Instruct (GGUF Q8_0, local)</t>
+          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.7</v>
+        <v>0.713</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.541</v>
+        <v>0.555</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.369</v>
+        <v>0.375</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.206</v>
+        <v>0.2</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.094</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.331</v>
+        <v>0.338</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.824</v>
+        <v>0.726</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.768</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>674</v>
+        <v>378</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.674</v>
+        <v>0.378</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>106</v>
+        <v>195</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.106</v>
+        <v>0.195</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.079</v>
       </c>
       <c r="L6" t="n">
-        <v>150</v>
+        <v>348</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.15</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.651</v>
+        <v>0.824</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.43</v>
+        <v>0.768</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>361</v>
+        <v>674</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.361</v>
+        <v>0.674</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.104</v>
+        <v>0.106</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>245</v>
+        <v>70</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.245</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>290</v>
+        <v>150</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.29</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.763</v>
+        <v>0.651</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.695</v>
+        <v>0.43</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>619</v>
+        <v>361</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.619</v>
+        <v>0.361</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.119</v>
+        <v>0.104</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>118</v>
+        <v>245</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.118</v>
+        <v>0.245</v>
       </c>
       <c r="L8" t="n">
-        <v>144</v>
+        <v>290</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.144</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.7</v>
+        <v>0.763</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.519</v>
+        <v>0.695</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>460</v>
+        <v>619</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.46</v>
+        <v>0.619</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.049</v>
+        <v>0.119</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>251</v>
+        <v>118</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.251</v>
+        <v>0.118</v>
       </c>
       <c r="L9" t="n">
-        <v>240</v>
+        <v>144</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.24</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.731</v>
+        <v>0.7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.505</v>
+        <v>0.519</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>329</v>
+        <v>460</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.329</v>
+        <v>0.46</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>200</v>
+        <v>49</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2</v>
+        <v>0.049</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>69</v>
+        <v>251</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.251</v>
       </c>
       <c r="L10" t="n">
-        <v>402</v>
+        <v>240</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.402</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.863</v>
+        <v>0.731</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.833</v>
+        <v>0.505</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>760</v>
+        <v>329</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.76</v>
+        <v>0.329</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.082</v>
+        <v>0.2</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.055</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>103</v>
+        <v>402</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.103</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.718</v>
+        <v>0.863</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.612</v>
+        <v>0.833</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>547</v>
+        <v>760</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.547</v>
+        <v>0.76</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.168</v>
+        <v>0.082</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.114</v>
+        <v>0.055</v>
       </c>
       <c r="L12" t="n">
-        <v>171</v>
+        <v>103</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.171</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.895</v>
+        <v>0.718</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.866</v>
+        <v>0.612</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>797</v>
+        <v>547</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.797</v>
+        <v>0.547</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>71</v>
+        <v>168</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.168</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.034</v>
+        <v>0.114</v>
       </c>
       <c r="L13" t="n">
-        <v>98</v>
+        <v>171</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.098</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.865</v>
+        <v>0.895</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.866</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>734</v>
+        <v>797</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.734</v>
+        <v>0.797</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.075</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.06</v>
+        <v>0.034</v>
       </c>
       <c r="L14" t="n">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.131</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.832</v>
+        <v>0.865</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.77</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>694</v>
+        <v>734</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.694</v>
+        <v>0.734</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.102</v>
+        <v>0.075</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.066</v>
+        <v>0.06</v>
       </c>
       <c r="L15" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.138</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.91</v>
+        <v>0.832</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.887</v>
+        <v>0.77</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>819</v>
+        <v>694</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.819</v>
+        <v>0.694</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.063</v>
+        <v>0.102</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.027</v>
+        <v>0.066</v>
       </c>
       <c r="L16" t="n">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.091</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D17" s="4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>819</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="L17" t="n">
+        <v>91</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>0.091</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D18" s="4" t="n">
         <v>0.867</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E18" s="4" t="n">
         <v>0.822</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F18" s="5" t="n">
         <v>761</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>0.761</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="H18" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="I18" s="4" t="n">
         <v>0.097</v>
       </c>
-      <c r="J17" s="5" t="n">
+      <c r="J18" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="K17" s="4" t="n">
+      <c r="K18" s="4" t="n">
         <v>0.036</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L18" t="n">
         <v>106</v>
       </c>
-      <c r="M17" s="4" t="n">
+      <c r="M18" s="4" t="n">
         <v>0.106</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M17"/>
+  <autoFilter ref="A1:M18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results/benchmark_results.xlsx
+++ b/results/benchmark_results.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T03:05:00+00:00</t>
+          <t>2026-09-17T03:39:22+00:00</t>
         </is>
       </c>
     </row>
@@ -2134,10 +2134,10 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>720993</v>
+        <v>1441986</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0</v>
@@ -2152,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>720993</v>
+        <v>1441986</v>
       </c>
       <c r="J6" s="5" t="n">
         <v>0</v>
@@ -3210,17 +3210,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>run-20260917T023435-d6148d1a</t>
+          <t>run-20260917T032017-051fd34b</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T03:02:38+00:00</t>
+          <t>2026-09-17T03:38:23+00:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-17T02:34:35+00:00</t>
+          <t>2026-09-17T03:20:17+00:00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>62bd51cc58aff3b5128149c0e7098fc7bb1caa80</t>
+          <t>c12db6c91e7697f9dafc897de9c531e43921d60d</t>
         </is>
       </c>
       <c r="H6" t="b">
@@ -5615,7 +5615,7 @@
     <col width="10" customWidth="1" min="24" max="24"/>
     <col width="10" customWidth="1" min="25" max="25"/>
     <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="21" customWidth="1" min="27" max="27"/>
+    <col width="20" customWidth="1" min="27" max="27"/>
     <col width="22" customWidth="1" min="28" max="28"/>
     <col width="22" customWidth="1" min="29" max="29"/>
     <col width="19" customWidth="1" min="30" max="30"/>
@@ -7754,28 +7754,28 @@
       <c r="V17" s="4" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="n">
-        <v>0.573</v>
+        <v>0.572</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.5388418311648718</v>
+        <v>0.5383725106907433</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>0.4135867824853839</v>
+        <v>0.4142792208259681</v>
       </c>
       <c r="AB17" s="4" t="n">
         <v>0.515</v>
       </c>
       <c r="AC17" s="4" t="n">
-        <v>0.4814069197519245</v>
+        <v>0.4816940963179205</v>
       </c>
       <c r="AD17" s="4" t="n">
-        <v>0.726</v>
+        <v>0.724</v>
       </c>
       <c r="AE17" s="5" t="n">
-        <v>720993</v>
+        <v>1441986</v>
       </c>
       <c r="AF17" s="5" t="n">
         <v>0</v>
@@ -11433,7 +11433,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -11926,13 +11926,13 @@
         <v>1000</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.573</v>
+        <v>0.572</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.5388418311648718</v>
+        <v>0.5383725106907433</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>0</v>
@@ -11961,13 +11961,13 @@
         <v>1000</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.4135867824853839</v>
+        <v>0.4142792208259681</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>0</v>
@@ -11999,7 +11999,7 @@
         <v>0.515</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.4814069197519245</v>
+        <v>0.4816940963179205</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>1030</v>
@@ -13563,16 +13563,16 @@
         <v>1000</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.726</v>
+        <v>0.724</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.378</v>
+        <v>0.377</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>195</v>
@@ -13581,16 +13581,16 @@
         <v>0.195</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="L6" t="n">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.348</v>
+        <v>0.347</v>
       </c>
     </row>
     <row r="7">

--- a/results/benchmark_results.xlsx
+++ b/results/benchmark_results.xlsx
@@ -475,48 +475,48 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Benchmark</t>
+          <t>Results as of (UTC)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>LLM summarization / hallucination / classification benchmark</t>
+          <t>2026-09-17T03:38:23+00:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Benchmark version</t>
+          <t>Benchmark</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1.0.0</t>
+          <t>LLM summarization / hallucination / classification benchmark</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>API provider</t>
+          <t>Benchmark version</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>OpenRouter (every model, including judges)</t>
+          <t>1.0.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Generated at (UTC)</t>
+          <t>API provider</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T03:39:22+00:00</t>
+          <t>OpenRouter (every model, including judges)</t>
         </is>
       </c>
     </row>

--- a/results/benchmark_results.xlsx
+++ b/results/benchmark_results.xlsx
@@ -475,48 +475,48 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Results as of (UTC)</t>
+          <t>Benchmark</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T03:38:23+00:00</t>
+          <t>LLM summarization / hallucination / classification benchmark</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Benchmark</t>
+          <t>Benchmark version</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>LLM summarization / hallucination / classification benchmark</t>
+          <t>1.0.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Benchmark version</t>
+          <t>API provider</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>1.0.0</t>
+          <t>OpenRouter (every model, including judges)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>API provider</t>
+          <t>Generated at (UTC)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>OpenRouter (every model, including judges)</t>
+          <t>2026-09-17T03:20:16+00:00</t>
         </is>
       </c>
     </row>
@@ -2089,10 +2089,10 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1441986</v>
+        <v>2162979</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
@@ -2101,25 +2101,25 @@
         <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>10903</v>
+        <v>16353</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>1452889</v>
+        <v>2179332</v>
       </c>
       <c r="J5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" s="5" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="6">
@@ -3124,17 +3124,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>run-20260917T030240-7b921abc</t>
+          <t>run-20260917T033825-47cdee59</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T03:02:41+00:00</t>
+          <t>2026-09-17T04:06:41+00:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-17T03:02:40+00:00</t>
+          <t>2026-09-17T03:38:25+00:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>62bd51cc58aff3b5128149c0e7098fc7bb1caa80</t>
+          <t>c12db6c91e7697f9dafc897de9c531e43921d60d</t>
         </is>
       </c>
       <c r="H5" t="b">
@@ -7664,31 +7664,31 @@
       <c r="V16" s="4" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="n">
-        <v>0.575</v>
+        <v>0.578</v>
       </c>
       <c r="Y16" t="n">
         <v>0.462</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.5459294856069367</v>
+        <v>0.5486232650628055</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>0.4217011621299711</v>
+        <v>0.4225847136466017</v>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>0.5185</v>
+        <v>0.52</v>
       </c>
       <c r="AC16" s="4" t="n">
-        <v>0.4882467464725742</v>
+        <v>0.4912105263425375</v>
       </c>
       <c r="AD16" s="4" t="n">
-        <v>0.713</v>
+        <v>0.706</v>
       </c>
       <c r="AE16" s="5" t="n">
-        <v>1441986</v>
+        <v>2162979</v>
       </c>
       <c r="AF16" s="5" t="n">
-        <v>10903</v>
+        <v>16353</v>
       </c>
       <c r="AG16" s="5" t="n">
         <v>0</v>
@@ -11433,7 +11433,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -11821,13 +11821,13 @@
         <v>1000</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.575</v>
+        <v>0.578</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.5459294856069367</v>
+        <v>0.5486232650628055</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>0</v>
@@ -11859,7 +11859,7 @@
         <v>0.462</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.4217011621299711</v>
+        <v>0.4225847136466017</v>
       </c>
       <c r="G12" s="5" t="n">
         <v>462</v>
@@ -11891,13 +11891,13 @@
         <v>2000</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.5185</v>
+        <v>0.52</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.4882467464725742</v>
+        <v>0.4912105263425375</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>0</v>
@@ -13518,34 +13518,34 @@
         <v>1000</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.713</v>
+        <v>0.706</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.555</v>
+        <v>0.546</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.375</v>
+        <v>0.373</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.2</v>
+        <v>0.205</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.089</v>
       </c>
       <c r="L5" t="n">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.338</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="6">

--- a/results/benchmark_results.xlsx
+++ b/results/benchmark_results.xlsx
@@ -23,17 +23,17 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Legend'!$A$1:$D$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Leaderboard'!$A$1:$AL$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Leaderboard'!$A$1:$AL$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Summarization'!$A$1:$P$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Hallucination'!$A$1:$O$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Classification'!$A$1:$I$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'CrossLingual'!$A$1:$M$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Classification'!$A$1:$I$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'CrossLingual'!$A$1:$M$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'ClassificationModes'!$A$1:$K$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'SurfaceFacts'!$A$1:$L$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cost'!$A$1:$S$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Usage'!$A$1:$M$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cost'!$A$1:$S$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Usage'!$A$1:$M$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Judge'!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Runs'!$A$1:$T$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Runs'!$A$1:$T$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,48 +475,48 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Benchmark</t>
+          <t>Results as of (UTC)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>LLM summarization / hallucination / classification benchmark</t>
+          <t>2026-09-17T08:13:45+00:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Benchmark version</t>
+          <t>Benchmark</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1.0.0</t>
+          <t>LLM summarization / hallucination / classification benchmark</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>API provider</t>
+          <t>Benchmark version</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>OpenRouter (every model, including judges)</t>
+          <t>1.0.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Generated at (UTC)</t>
+          <t>API provider</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T03:20:16+00:00</t>
+          <t>OpenRouter (every model, including judges)</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -1046,156 +1046,96 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen3.5-2b-q8-gguf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0.2</v>
-      </c>
+          <t>Qwen3.5 2B (GGUF Q8_0, local)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-16T03:10:41+00:00</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>0.07769180000000001</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>0.08999796</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>0.01189376</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>0.17958352</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>0.1795835200000001</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>0.17958352</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>0.1795835200000001</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="4" t="n">
-        <v>0.17958352</v>
-      </c>
-      <c r="S7" t="b">
-        <v>1</v>
-      </c>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>local/qwen3.5-4b-q4km-gguf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0.1</v>
-      </c>
+          <t>Qwen3.5 4B (GGUF Q4_K_M, local)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-16T03:17:56+00:00</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>0.0385285</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>0.0433295</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>0.00566052</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>0.08751852</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>0.08751852</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>0.08751852</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>0.08751852</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="4" t="n">
-        <v>0.08751852</v>
-      </c>
-      <c r="S8" t="b">
-        <v>1</v>
-      </c>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1204,17 +1144,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-16T03:15:02+00:00</t>
+          <t>2026-09-16T03:10:41+00:00</t>
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.0582456</v>
+        <v>0.07769180000000001</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.06753291</v>
+        <v>0.08999796</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.008405670000000001</v>
+        <v>0.01189376</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>0</v>
@@ -1223,22 +1163,22 @@
         <v>0</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.13418418</v>
+        <v>0.17958352</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0.1341841799999999</v>
+        <v>0.1795835200000001</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0.13418418</v>
+        <v>0.17958352</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0.1341841799999999</v>
+        <v>0.1795835200000001</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.13418418</v>
+        <v>0.17958352</v>
       </c>
       <c r="S9" t="b">
         <v>1</v>
@@ -1247,22 +1187,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1271,17 +1211,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-16T03:07:59+00:00</t>
+          <t>2026-09-16T03:17:56+00:00</t>
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.0802729125</v>
+        <v>0.0385285</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.0986139</v>
+        <v>0.0433295</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.017520885</v>
+        <v>0.00566052</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0</v>
@@ -1290,46 +1230,46 @@
         <v>0</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.1964076975</v>
+        <v>0.08751852</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.1964076975000001</v>
+        <v>0.08751852</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.1964076975</v>
+        <v>0.08751852</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.1964076975000001</v>
+        <v>0.08751852</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.17912064</v>
+        <v>0.08751852</v>
       </c>
       <c r="S10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1338,17 +1278,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:30+00:00</t>
+          <t>2026-09-16T03:15:02+00:00</t>
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.0519185</v>
+        <v>0.0582456</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.067397</v>
+        <v>0.06753291</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.0109598</v>
+        <v>0.008405670000000001</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
@@ -1357,22 +1297,22 @@
         <v>0</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.13418418</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.1341841799999999</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.13418418</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.1341841799999999</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.1302753</v>
+        <v>0.13418418</v>
       </c>
       <c r="S11" t="b">
         <v>1</v>
@@ -1381,22 +1321,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.005</v>
+        <v>0.015</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1405,17 +1345,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-16T04:40:49+00:00</t>
+          <t>2026-09-16T03:07:59+00:00</t>
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.08205585</v>
+        <v>0.0802729125</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.1433661</v>
+        <v>0.0986139</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.0474705</v>
+        <v>0.017520885</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1424,46 +1364,46 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.27289245</v>
+        <v>0.1964076975</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.2728924500000001</v>
+        <v>0.1964076975000001</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0.27289245</v>
+        <v>0.1964076975</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.2728924500000001</v>
+        <v>0.1964076975000001</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.27289245</v>
+        <v>0.17912064</v>
       </c>
       <c r="S12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1.25</v>
+        <v>0.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1472,17 +1412,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-16T03:20:07+00:00</t>
+          <t>2026-09-16T03:23:30+00:00</t>
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.1453735</v>
+        <v>0.0519185</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.1435934</v>
+        <v>0.067397</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02710335</v>
+        <v>0.0109598</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
@@ -1491,22 +1431,22 @@
         <v>0</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>0.31607025</v>
+        <v>0.1302753</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.3160702499999996</v>
+        <v>0.1302753</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>0.31607025</v>
+        <v>0.1302753</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.3160702499999996</v>
+        <v>0.1302753</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.3160702500000001</v>
+        <v>0.1302753</v>
       </c>
       <c r="S13" t="b">
         <v>1</v>
@@ -1515,22 +1455,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1539,17 +1479,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-16T02:59:08+00:00</t>
+          <t>2026-09-16T04:40:49+00:00</t>
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.12600455</v>
+        <v>0.08205585</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.1584021</v>
+        <v>0.1433661</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.0262596</v>
+        <v>0.0474705</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0</v>
@@ -1558,44 +1498,46 @@
         <v>0</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>0.31066625</v>
+        <v>0.27289245</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.3106662500000003</v>
+        <v>0.2728924500000001</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.31066625</v>
+        <v>0.27289245</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.3106662500000003</v>
+        <v>0.2728924500000001</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.2877202</v>
+        <v>0.27289245</v>
       </c>
       <c r="S14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.04815</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0.02</v>
+      </c>
       <c r="E15" s="3" t="n">
-        <v>0.19305</v>
+        <v>1.25</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1604,17 +1546,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-16T03:34:40+00:00</t>
+          <t>2026-09-16T03:20:07+00:00</t>
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.04959875775</v>
+        <v>0.1453735</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.06309176505</v>
+        <v>0.1435934</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.01054341345</v>
+        <v>0.02710335</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>0</v>
@@ -1623,46 +1565,46 @@
         <v>0</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0.12323393625</v>
+        <v>0.31607025</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>0.1232339362500001</v>
+        <v>0.3160702499999996</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>0.12323393625</v>
+        <v>0.31607025</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0.1232339362500001</v>
+        <v>0.3160702499999996</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.07244949735</v>
+        <v>0.3160702500000001</v>
       </c>
       <c r="S15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.03</v>
+        <v>0.2</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.006</v>
+        <v>0.02</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.13</v>
+        <v>1.2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1671,17 +1613,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-16T03:31:23+00:00</t>
+          <t>2026-09-16T02:59:08+00:00</t>
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.01445385</v>
+        <v>0.12600455</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.01955122</v>
+        <v>0.1584021</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.0039132</v>
+        <v>0.0262596</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>0</v>
@@ -1690,46 +1632,44 @@
         <v>0</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.03791827</v>
+        <v>0.31066625</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.03791826999999996</v>
+        <v>0.3106662500000003</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.03791827</v>
+        <v>0.31066625</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.03791826999999996</v>
+        <v>0.3106662500000003</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.03795787999999999</v>
+        <v>0.2877202</v>
       </c>
       <c r="S16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>0.016</v>
-      </c>
+        <v>0.04815</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr"/>
       <c r="E17" s="3" t="n">
-        <v>0.47</v>
+        <v>0.19305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1738,17 +1678,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-16T03:26:19+00:00</t>
+          <t>2026-09-16T03:34:40+00:00</t>
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.06590207000000001</v>
+        <v>0.04959875775</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.068078582</v>
+        <v>0.06309176505</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.013945102</v>
+        <v>0.01054341345</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>0</v>
@@ -1757,96 +1697,230 @@
         <v>0</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.12323393625</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.1232339362500001</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.12323393625</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.1232339362500001</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.148121674</v>
+        <v>0.07244949735</v>
       </c>
       <c r="S17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>qwen/qwen3.7-flash</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Qwen3.7 Flash</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-09-16T03:31:23+00:00</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>0.01445385</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>0.01955122</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0.0039132</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>0.03791827</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>0.03791826999999996</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>0.03791827</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>0.03791826999999996</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>0.03795787999999999</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>qwen/qwen3.8-flash</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Qwen3.8 Flash</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-09-16T03:26:19+00:00</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0.06590207000000001</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>0.068078582</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>0.013945102</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>0.147925754</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>0.147925754</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>0.147925754</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0.147925754</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>0.148121674</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>z-ai/glm-5.3-flash</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>GLM 5.3 Flash</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C20" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>0.02</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>0.3333</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>2026-09-16T04:41:38+00:00</t>
         </is>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="H20" s="3" t="n">
         <v>0.0828101102</v>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="I20" s="3" t="n">
         <v>0.11700001578</v>
       </c>
-      <c r="J18" s="3" t="n">
+      <c r="J20" s="3" t="n">
         <v>0.0149070175</v>
       </c>
-      <c r="K18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3" t="n">
+      <c r="K20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3" t="n">
         <v>0.21471714348</v>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="N20" s="3" t="n">
         <v>0.2147171434799998</v>
       </c>
-      <c r="O18" s="3" t="n">
+      <c r="O20" s="3" t="n">
         <v>0.21471714348</v>
       </c>
-      <c r="P18" s="3" t="n">
+      <c r="P20" s="3" t="n">
         <v>0.2147171434799998</v>
       </c>
-      <c r="Q18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="4" t="n">
+      <c r="Q20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="4" t="n">
         <v>0.1606481436</v>
       </c>
-      <c r="S18" t="b">
+      <c r="S20" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S18"/>
+  <autoFilter ref="A1:S20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1857,7 +1931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -2110,16 +2184,16 @@
         <v>2179332</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2155,117 +2229,117 @@
         <v>1441986</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen3.5-2b-q8-gguf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen3.5 2B (GGUF Q8_0, local)</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1300</v>
+        <v>2000</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1092316</v>
+        <v>721898</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>295936</v>
+        <v>0</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>71944</v>
+        <v>0</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>1164260</v>
+        <v>721898</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>1300</v>
+        <v>2000</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>1300</v>
+        <v>2000</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>1300</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>local/qwen3.5-4b-q4km-gguf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Qwen3.5 4B (GGUF Q4_K_M, local)</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1300</v>
+        <v>2000</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1092316</v>
+        <v>721898</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>318592</v>
+        <v>0</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>69602</v>
+        <v>0</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>1161918</v>
+        <v>721898</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>1300</v>
+        <v>2000</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1300</v>
+        <v>2000</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>1300</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
@@ -2275,19 +2349,19 @@
         <v>1092316</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>299392</v>
+        <v>295936</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>71698</v>
+        <v>71944</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>1164014</v>
+        <v>1164260</v>
       </c>
       <c r="J9" s="5" t="n">
         <v>0</v>
@@ -2305,34 +2379,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1107916</v>
+        <v>1092316</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>183856</v>
+        <v>318592</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>62923</v>
+        <v>69602</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>1170839</v>
+        <v>1161918</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>0</v>
@@ -2350,34 +2424,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1108245</v>
+        <v>1092316</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>36224</v>
+        <v>299392</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>55419</v>
+        <v>71698</v>
       </c>
       <c r="H11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>1163664</v>
+        <v>1164014</v>
       </c>
       <c r="J11" s="5" t="n">
         <v>0</v>
@@ -2395,34 +2469,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1106945</v>
+        <v>1107916</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>40320</v>
+        <v>183856</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>548399</v>
+        <v>62923</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>433920</v>
+        <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>1655344</v>
+        <v>1170839</v>
       </c>
       <c r="J12" s="5" t="n">
         <v>0</v>
@@ -2440,34 +2514,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1106945</v>
+        <v>1108245</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>36224</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>75745</v>
+        <v>55419</v>
       </c>
       <c r="H13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>1182690</v>
+        <v>1163664</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>0</v>
@@ -2485,12 +2559,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
@@ -2500,19 +2574,19 @@
         <v>1106945</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>40320</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>458921</v>
+        <v>0</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>55276</v>
+        <v>548399</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0</v>
+        <v>433920</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>1162221</v>
+        <v>1655344</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>0</v>
@@ -2530,34 +2604,34 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1213604</v>
+        <v>1106945</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>102934</v>
+        <v>0</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>72595</v>
+        <v>75745</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>1286199</v>
+        <v>1182690</v>
       </c>
       <c r="J15" s="5" t="n">
         <v>0</v>
@@ -2575,34 +2649,34 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1061596</v>
+        <v>1106945</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>24960</v>
+        <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0</v>
+        <v>458921</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>51608</v>
+        <v>55276</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>1113204</v>
+        <v>1162221</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>0</v>
@@ -2614,40 +2688,40 @@
         <v>1300</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>1307</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1061596</v>
+        <v>1213604</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>265984</v>
+        <v>102934</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>52179</v>
+        <v>72595</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>1113775</v>
+        <v>1286199</v>
       </c>
       <c r="J17" s="5" t="n">
         <v>0</v>
@@ -2659,40 +2733,40 @@
         <v>1300</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>1314</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>1293055</v>
+        <v>1061596</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>104384</v>
+        <v>24960</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>119092</v>
+        <v>51608</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>35855</v>
+        <v>0</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>1412147</v>
+        <v>1113204</v>
       </c>
       <c r="J18" s="5" t="n">
         <v>0</v>
@@ -2704,11 +2778,101 @@
         <v>1300</v>
       </c>
       <c r="M18" s="5" t="n">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>qwen/qwen3.8-flash</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Qwen3.8 Flash</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
         <v>1300</v>
       </c>
+      <c r="D19" s="5" t="n">
+        <v>1061596</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>265984</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>52179</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>1113775</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>1293055</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>104384</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>119092</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>35855</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>1412147</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>1300</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M18"/>
+  <autoFilter ref="A1:M20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2744,7 +2908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -3124,17 +3288,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>run-20260917T033825-47cdee59</t>
+          <t>run-20260917T044122-e81422e2</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T04:06:41+00:00</t>
+          <t>2026-09-17T04:41:23+00:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-17T03:38:25+00:00</t>
+          <t>2026-09-17T04:41:22+00:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3144,7 +3308,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>c12db6c91e7697f9dafc897de9c531e43921d60d</t>
+          <t>12ce0741fedd9b770a4593296378e383c3ca80b7</t>
         </is>
       </c>
       <c r="H5" t="b">
@@ -3210,17 +3374,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>run-20260917T032017-051fd34b</t>
+          <t>run-20260917T044118-6aa4395f</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T03:38:23+00:00</t>
+          <t>2026-09-17T04:41:20+00:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-17T03:20:17+00:00</t>
+          <t>2026-09-17T04:41:18+00:00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3230,7 +3394,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>c12db6c91e7697f9dafc897de9c531e43921d60d</t>
+          <t>12ce0741fedd9b770a4593296378e383c3ca80b7</t>
         </is>
       </c>
       <c r="H6" t="b">
@@ -3286,7 +3450,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen3.5-2b-q8-gguf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3296,17 +3460,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>run-20260916T031043-60c30b6a</t>
+          <t>run-20260917T044125-67e7e99a</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:15:02+00:00</t>
+          <t>2026-09-17T05:31:28+00:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-16T03:10:43+00:00</t>
+          <t>2026-09-17T04:41:25+00:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3314,8 +3478,14 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>12ce0741fedd9b770a4593296378e383c3ca80b7</t>
+        </is>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -3323,7 +3493,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>summarization, hallucination, classification</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3332,7 +3502,7 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>3200</v>
+        <v>2000</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -3366,7 +3536,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>local/qwen3.5-4b-q4km-gguf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3376,17 +3546,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>run-20260916T031757-6f0019bc</t>
+          <t>run-20260917T053130-4932fffb</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:20:07+00:00</t>
+          <t>2026-09-17T08:13:45+00:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-16T03:17:57+00:00</t>
+          <t>2026-09-17T05:31:30+00:00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3394,8 +3564,14 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>a05631eb2e5769458bfd0e57d53515a08ebf6df1</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -3403,7 +3579,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>summarization, hallucination, classification</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3412,7 +3588,7 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>3200</v>
+        <v>2000</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -3446,7 +3622,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3456,17 +3632,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>run-20260916T031504-7b84cf7d</t>
+          <t>run-20260916T031043-60c30b6a</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:17:56+00:00</t>
+          <t>2026-09-16T03:15:02+00:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-16T03:15:04+00:00</t>
+          <t>2026-09-16T03:10:43+00:00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3526,7 +3702,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3536,17 +3712,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>run-20260916T030801-577d0830</t>
+          <t>run-20260916T031757-6f0019bc</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:10:41+00:00</t>
+          <t>2026-09-16T03:20:07+00:00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-16T03:08:01+00:00</t>
+          <t>2026-09-16T03:17:57+00:00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3606,7 +3782,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3616,17 +3792,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>run-20260916T032332-5a24afb2</t>
+          <t>run-20260916T031504-7b84cf7d</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:26:19+00:00</t>
+          <t>2026-09-16T03:17:56+00:00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:32+00:00</t>
+          <t>2026-09-16T03:15:04+00:00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3686,7 +3862,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3696,17 +3872,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>run-20260916T044051-1b0d71da</t>
+          <t>run-20260916T030801-577d0830</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T04:51:21+00:00</t>
+          <t>2026-09-16T03:10:41+00:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-16T04:40:51+00:00</t>
+          <t>2026-09-16T03:08:01+00:00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3714,14 +3890,8 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -3772,7 +3942,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3782,17 +3952,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>run-20260916T032009-aca77564</t>
+          <t>run-20260916T032332-5a24afb2</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:28+00:00</t>
+          <t>2026-09-16T03:26:19+00:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-16T03:20:09+00:00</t>
+          <t>2026-09-16T03:23:32+00:00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3852,7 +4022,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3862,17 +4032,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>run-20260916T025909-be4eb782</t>
+          <t>run-20260916T044051-1b0d71da</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:02:43+00:00</t>
+          <t>2026-09-16T04:51:21+00:00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-16T02:59:09+00:00</t>
+          <t>2026-09-16T04:40:51+00:00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3880,8 +4050,14 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
+        </is>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -3932,7 +4108,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3942,17 +4118,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>run-20260916T033441-93cb685e</t>
+          <t>run-20260916T032009-aca77564</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:43:30+00:00</t>
+          <t>2026-09-16T03:23:28+00:00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-16T03:34:41+00:00</t>
+          <t>2026-09-16T03:20:09+00:00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4012,7 +4188,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4022,17 +4198,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>run-20260916T033125-8730c140</t>
+          <t>run-20260916T025909-be4eb782</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:34:40+00:00</t>
+          <t>2026-09-16T03:02:43+00:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-16T03:31:25+00:00</t>
+          <t>2026-09-16T02:59:09+00:00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4092,7 +4268,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4102,17 +4278,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>run-20260916T032621-2ec5c283</t>
+          <t>run-20260916T033441-93cb685e</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:31:23+00:00</t>
+          <t>2026-09-16T03:43:30+00:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-16T03:26:21+00:00</t>
+          <t>2026-09-16T03:34:41+00:00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4172,7 +4348,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4182,17 +4358,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>run-20260916T044139-f5eda9f3</t>
+          <t>run-20260916T033125-8730c140</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T04:51:13+00:00</t>
+          <t>2026-09-16T03:34:40+00:00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-09-16T04:41:39+00:00</t>
+          <t>2026-09-16T03:31:25+00:00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -4200,14 +4376,8 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
-        </is>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -4255,8 +4425,174 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>qwen/qwen3.8-flash</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>run-20260916T032621-2ec5c283</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16T03:31:23+00:00</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-09-16T03:26:21+00:00</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3.12.3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>summarization, hallucination, classification</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>en, ko</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>3200</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>cbe6fb9c14d4b2b12e690d6565e05bcf861c5db26cc56aef45e3e3810f67b298</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0135c4f4499e35dcde7855ad6afe33e333ebf2bca519a20b81257dc39150cd62</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>21debf696ed02ef001638142e2864a1bb58be409f88d8c86ad36e067ee609ca5</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>b49d914db700703584e2388f602808314a59c9e088a20f02e670ead58141fa96</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1bebd7a4e6cab622b3a85e6f856e019c9459100085c08ca38ccec107d5e3ec21</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>run-20260916T044139-f5eda9f3</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16T04:51:13+00:00</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-09-16T04:41:39+00:00</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
+        </is>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3.12.3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>summarization, hallucination, classification</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>en, ko</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>3200</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>cbe6fb9c14d4b2b12e690d6565e05bcf861c5db26cc56aef45e3e3810f67b298</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0135c4f4499e35dcde7855ad6afe33e333ebf2bca519a20b81257dc39150cd62</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>21debf696ed02ef001638142e2864a1bb58be409f88d8c86ad36e067ee609ca5</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>b49d914db700703584e2388f602808314a59c9e088a20f02e670ead58141fa96</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1bebd7a4e6cab622b3a85e6f856e019c9459100085c08ca38ccec107d5e3ec21</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T18"/>
+  <autoFilter ref="A1:T20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5586,7 +5922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL18"/>
+  <dimension ref="A1:AL20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -6974,22 +7310,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen3.5-4b-q4km-gguf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen3.5 4B (GGUF Q4_K_M, local)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mistralai</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>local</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -6997,117 +7333,79 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-16T03:10:41+00:00</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>0.1340643496794257</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.200848621976299</v>
-      </c>
-      <c r="M11" t="n">
-        <v>23.15600037313629</v>
-      </c>
-      <c r="N11" t="n">
-        <v>12.32917653667287</v>
-      </c>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" s="4" t="n">
-        <v>0.8982440342188204</v>
-      </c>
-      <c r="R11" s="4" t="n">
-        <v>0.9363636363636364</v>
-      </c>
-      <c r="S11" s="4" t="n">
-        <v>0.7163461538461539</v>
-      </c>
-      <c r="T11" s="4" t="n">
-        <v>0.683291770573566</v>
-      </c>
-      <c r="U11" s="4" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="V11" s="4" t="n">
-        <v>0.6825</v>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="Q11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr"/>
+      <c r="T11" s="4" t="inlineStr"/>
+      <c r="U11" s="4" t="inlineStr"/>
+      <c r="V11" s="4" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.744</v>
+        <v>0.749</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.7603515978750895</v>
+        <v>0.7784520148968087</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>0.7113942857254609</v>
+        <v>0.7246091754455255</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>0.762</v>
+        <v>0.7745</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>0.736163325053324</v>
+        <v>0.7528237438696134</v>
       </c>
       <c r="AD11" s="4" t="n">
-        <v>0.824</v>
+        <v>0.835</v>
       </c>
       <c r="AE11" s="5" t="n">
-        <v>1092316</v>
+        <v>721898</v>
       </c>
       <c r="AF11" s="5" t="n">
-        <v>71944</v>
+        <v>0</v>
       </c>
       <c r="AG11" s="5" t="n">
-        <v>295936</v>
+        <v>0</v>
       </c>
       <c r="AH11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AI11" s="3" t="n">
-        <v>0.17958352</v>
-      </c>
-      <c r="AJ11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="3" t="n">
-        <v>0.1795835200000001</v>
-      </c>
-      <c r="AL11" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7126,13 +7424,13 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -7141,40 +7439,40 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-16T03:15:02+00:00</t>
+          <t>2026-09-16T03:10:41+00:00</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0.1338576862477163</v>
+        <v>0.1340643496794257</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2022785739193924</v>
+        <v>0.200848621976299</v>
       </c>
       <c r="M12" t="n">
-        <v>23.2893881252992</v>
+        <v>23.15600037313629</v>
       </c>
       <c r="N12" t="n">
-        <v>12.28128440018327</v>
+        <v>12.32917653667287</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" s="4" t="n">
-        <v>0.8798944126704795</v>
+        <v>0.8982440342188204</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.9474768280123584</v>
+        <v>0.9363636363636364</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.6366366366366367</v>
+        <v>0.7163461538461539</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.5857988165680473</v>
+        <v>0.683291770573566</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.6975</v>
+        <v>0.705</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.65</v>
+        <v>0.6825</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -7182,46 +7480,46 @@
         </is>
       </c>
       <c r="X12" t="n">
-        <v>0.738</v>
+        <v>0.78</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.737</v>
+        <v>0.744</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.7285750142849275</v>
+        <v>0.7603515978750895</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>0.712693713084553</v>
+        <v>0.7113942857254609</v>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>0.7375</v>
+        <v>0.762</v>
       </c>
       <c r="AC12" s="4" t="n">
-        <v>0.7216311867724771</v>
+        <v>0.736163325053324</v>
       </c>
       <c r="AD12" s="4" t="n">
-        <v>0.763</v>
+        <v>0.824</v>
       </c>
       <c r="AE12" s="5" t="n">
         <v>1092316</v>
       </c>
       <c r="AF12" s="5" t="n">
-        <v>71698</v>
+        <v>71944</v>
       </c>
       <c r="AG12" s="5" t="n">
-        <v>299392</v>
+        <v>295936</v>
       </c>
       <c r="AH12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>0.13418418</v>
+        <v>0.17958352</v>
       </c>
       <c r="AJ12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>0.1341841799999999</v>
+        <v>0.1795835200000001</v>
       </c>
       <c r="AL12" s="3" t="n">
         <v>0</v>
@@ -7230,17 +7528,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>mistralai</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -7254,13 +7552,13 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1.25</v>
+        <v>0.15</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -7269,40 +7567,40 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-16T03:20:07+00:00</t>
+          <t>2026-09-16T03:15:02+00:00</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0.1303590348428198</v>
+        <v>0.1338576862477163</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1872998825564791</v>
+        <v>0.2022785739193924</v>
       </c>
       <c r="M13" t="n">
-        <v>23.22067206524886</v>
+        <v>23.2893881252992</v>
       </c>
       <c r="N13" t="n">
-        <v>11.95596092668423</v>
+        <v>12.28128440018327</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" s="4" t="n">
-        <v>0.961978928080623</v>
+        <v>0.8798944126704795</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.9586330935251799</v>
+        <v>0.9474768280123584</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.6149068322981366</v>
+        <v>0.6366366366366367</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.2382978723404255</v>
+        <v>0.5857988165680473</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6975</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.5525</v>
+        <v>0.65</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -7310,46 +7608,46 @@
         </is>
       </c>
       <c r="X13" t="n">
-        <v>0.715</v>
+        <v>0.738</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.661</v>
+        <v>0.737</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.7079848008862988</v>
+        <v>0.7285750142849275</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>0.6593342425290085</v>
+        <v>0.712693713084553</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.7375</v>
       </c>
       <c r="AC13" s="4" t="n">
-        <v>0.6845822094887644</v>
+        <v>0.7216311867724771</v>
       </c>
       <c r="AD13" s="4" t="n">
-        <v>0.718</v>
+        <v>0.763</v>
       </c>
       <c r="AE13" s="5" t="n">
-        <v>1106945</v>
+        <v>1092316</v>
       </c>
       <c r="AF13" s="5" t="n">
-        <v>75745</v>
+        <v>71698</v>
       </c>
       <c r="AG13" s="5" t="n">
-        <v>0</v>
+        <v>299392</v>
       </c>
       <c r="AH13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>0.31607025</v>
+        <v>0.13418418</v>
       </c>
       <c r="AJ13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>0.3160702499999996</v>
+        <v>0.1341841799999999</v>
       </c>
       <c r="AL13" s="3" t="n">
         <v>0</v>
@@ -7358,17 +7656,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mistralai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -7382,13 +7680,13 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.6</v>
+        <v>1.25</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -7397,40 +7695,40 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-16T03:07:59+00:00</t>
+          <t>2026-09-16T03:20:07+00:00</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.1486748430163934</v>
+        <v>0.1303590348428198</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2158566833442461</v>
+        <v>0.1872998825564791</v>
       </c>
       <c r="M14" t="n">
-        <v>24.85170132045256</v>
+        <v>23.22067206524886</v>
       </c>
       <c r="N14" t="n">
-        <v>12.57729783101797</v>
+        <v>11.95596092668423</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" s="4" t="n">
-        <v>0.9259462424574877</v>
+        <v>0.961978928080623</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.9627450980392157</v>
+        <v>0.9586330935251799</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.7247956403269755</v>
+        <v>0.6149068322981366</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.6195652173913043</v>
+        <v>0.2382978723404255</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.65</v>
+        <v>0.5525</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -7438,46 +7736,46 @@
         </is>
       </c>
       <c r="X14" t="n">
-        <v>0.509</v>
+        <v>0.715</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.711</v>
+        <v>0.661</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.5867378280355483</v>
+        <v>0.7079848008862988</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>0.7031769757373104</v>
+        <v>0.6593342425290085</v>
       </c>
       <c r="AB14" s="4" t="n">
-        <v>0.61</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AC14" s="4" t="n">
-        <v>0.6504937686437986</v>
+        <v>0.6845822094887644</v>
       </c>
       <c r="AD14" s="4" t="n">
-        <v>0.7</v>
+        <v>0.718</v>
       </c>
       <c r="AE14" s="5" t="n">
-        <v>1107916</v>
+        <v>1106945</v>
       </c>
       <c r="AF14" s="5" t="n">
-        <v>62923</v>
+        <v>75745</v>
       </c>
       <c r="AG14" s="5" t="n">
-        <v>183856</v>
+        <v>0</v>
       </c>
       <c r="AH14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>0.1964076975</v>
+        <v>0.31607025</v>
       </c>
       <c r="AJ14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>0.1964076975000001</v>
+        <v>0.3160702499999996</v>
       </c>
       <c r="AL14" s="3" t="n">
         <v>0</v>
@@ -7486,12 +7784,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -7510,13 +7808,13 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -7525,40 +7823,40 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-16T03:17:56+00:00</t>
+          <t>2026-09-16T03:07:59+00:00</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.1344392234965607</v>
+        <v>0.1486748430163934</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1976921128927562</v>
+        <v>0.2158566833442461</v>
       </c>
       <c r="M15" t="n">
-        <v>23.21465695587321</v>
+        <v>24.85170132045256</v>
       </c>
       <c r="N15" t="n">
-        <v>11.65156743434614</v>
+        <v>12.57729783101797</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" s="4" t="n">
-        <v>0.886284289276808</v>
+        <v>0.9259462424574877</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.9119420989143546</v>
+        <v>0.9627450980392157</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.6757493188010899</v>
+        <v>0.7247956403269755</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.5591939546599498</v>
+        <v>0.6195652173913043</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.7025</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.5625</v>
+        <v>0.65</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -7566,46 +7864,46 @@
         </is>
       </c>
       <c r="X15" t="n">
-        <v>0.465</v>
+        <v>0.509</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.606</v>
+        <v>0.711</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.5053205391654078</v>
+        <v>0.5867378280355483</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>0.5671517703461975</v>
+        <v>0.7031769757373104</v>
       </c>
       <c r="AB15" s="4" t="n">
-        <v>0.5355</v>
+        <v>0.61</v>
       </c>
       <c r="AC15" s="4" t="n">
-        <v>0.5411026333400099</v>
+        <v>0.6504937686437986</v>
       </c>
       <c r="AD15" s="4" t="n">
-        <v>0.651</v>
+        <v>0.7</v>
       </c>
       <c r="AE15" s="5" t="n">
-        <v>1092316</v>
+        <v>1107916</v>
       </c>
       <c r="AF15" s="5" t="n">
-        <v>69602</v>
+        <v>62923</v>
       </c>
       <c r="AG15" s="5" t="n">
-        <v>318592</v>
+        <v>183856</v>
       </c>
       <c r="AH15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>0.08751852</v>
+        <v>0.1964076975</v>
       </c>
       <c r="AJ15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>0.08751852</v>
+        <v>0.1964076975000001</v>
       </c>
       <c r="AL15" s="3" t="n">
         <v>0</v>
@@ -7614,12 +7912,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
+          <t>local/qwen3.5-2b-q8-gguf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
+          <t>Qwen3.5 2B (GGUF Q8_0, local)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -7664,31 +7962,31 @@
       <c r="V16" s="4" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="n">
-        <v>0.578</v>
+        <v>0.648</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.462</v>
+        <v>0.517</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.5486232650628055</v>
+        <v>0.6273835935085809</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>0.4225847136466017</v>
+        <v>0.5062609313499989</v>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>0.52</v>
+        <v>0.5825</v>
       </c>
       <c r="AC16" s="4" t="n">
-        <v>0.4912105263425375</v>
+        <v>0.5734975422659654</v>
       </c>
       <c r="AD16" s="4" t="n">
-        <v>0.706</v>
+        <v>0.705</v>
       </c>
       <c r="AE16" s="5" t="n">
-        <v>2162979</v>
+        <v>721898</v>
       </c>
       <c r="AF16" s="5" t="n">
-        <v>16353</v>
+        <v>0</v>
       </c>
       <c r="AG16" s="5" t="n">
         <v>0</v>
@@ -7704,22 +8002,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>mistralai</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7727,89 +8025,127 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>0.01</v>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>config</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>2026-09-16T03:17:56+00:00</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0.1344392234965607</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.1976921128927562</v>
+      </c>
+      <c r="M17" t="n">
+        <v>23.21465695587321</v>
+      </c>
+      <c r="N17" t="n">
+        <v>11.65156743434614</v>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" s="4" t="inlineStr"/>
-      <c r="R17" s="4" t="inlineStr"/>
-      <c r="S17" s="4" t="inlineStr"/>
-      <c r="T17" s="4" t="inlineStr"/>
-      <c r="U17" s="4" t="inlineStr"/>
-      <c r="V17" s="4" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
+      <c r="Q17" s="4" t="n">
+        <v>0.886284289276808</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>0.9119420989143546</v>
+      </c>
+      <c r="S17" s="4" t="n">
+        <v>0.6757493188010899</v>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>0.5591939546599498</v>
+      </c>
+      <c r="U17" s="4" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="X17" t="n">
-        <v>0.572</v>
+        <v>0.465</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.458</v>
+        <v>0.606</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.5383725106907433</v>
+        <v>0.5053205391654078</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>0.4142792208259681</v>
+        <v>0.5671517703461975</v>
       </c>
       <c r="AB17" s="4" t="n">
-        <v>0.515</v>
+        <v>0.5355</v>
       </c>
       <c r="AC17" s="4" t="n">
-        <v>0.4816940963179205</v>
+        <v>0.5411026333400099</v>
       </c>
       <c r="AD17" s="4" t="n">
-        <v>0.724</v>
+        <v>0.651</v>
       </c>
       <c r="AE17" s="5" t="n">
-        <v>1441986</v>
+        <v>1092316</v>
       </c>
       <c r="AF17" s="5" t="n">
-        <v>0</v>
+        <v>69602</v>
       </c>
       <c r="AG17" s="5" t="n">
-        <v>0</v>
+        <v>318592</v>
       </c>
       <c r="AH17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AI17" s="3" t="inlineStr"/>
-      <c r="AJ17" s="3" t="inlineStr"/>
-      <c r="AK17" s="3" t="inlineStr"/>
-      <c r="AL17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="n">
+        <v>0.08751852</v>
+      </c>
+      <c r="AJ17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="3" t="n">
+        <v>0.08751852</v>
+      </c>
+      <c r="AL17" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>local</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7817,110 +8153,290 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>0.025</v>
-      </c>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:30+00:00</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>0.1434021604287071</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.2194519351485593</v>
-      </c>
-      <c r="M18" t="n">
-        <v>24.49324424955361</v>
-      </c>
-      <c r="N18" t="n">
-        <v>12.31697458631575</v>
-      </c>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" s="4" t="n">
+      <c r="Q18" s="4" t="inlineStr"/>
+      <c r="R18" s="4" t="inlineStr"/>
+      <c r="S18" s="4" t="inlineStr"/>
+      <c r="T18" s="4" t="inlineStr"/>
+      <c r="U18" s="4" t="inlineStr"/>
+      <c r="V18" s="4" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="Z18" s="4" t="n">
+        <v>0.5486232650628055</v>
+      </c>
+      <c r="AA18" s="4" t="n">
+        <v>0.4225847136466017</v>
+      </c>
+      <c r="AB18" s="4" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AC18" s="4" t="n">
+        <v>0.4912105263425375</v>
+      </c>
+      <c r="AD18" s="4" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="AE18" s="5" t="n">
+        <v>2162979</v>
+      </c>
+      <c r="AF18" s="5" t="n">
+        <v>16353</v>
+      </c>
+      <c r="AG18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" s="4" t="inlineStr"/>
+      <c r="R19" s="4" t="inlineStr"/>
+      <c r="S19" s="4" t="inlineStr"/>
+      <c r="T19" s="4" t="inlineStr"/>
+      <c r="U19" s="4" t="inlineStr"/>
+      <c r="V19" s="4" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="Z19" s="4" t="n">
+        <v>0.5383725106907433</v>
+      </c>
+      <c r="AA19" s="4" t="n">
+        <v>0.4142792208259681</v>
+      </c>
+      <c r="AB19" s="4" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="AC19" s="4" t="n">
+        <v>0.4816940963179205</v>
+      </c>
+      <c r="AD19" s="4" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="AE19" s="5" t="n">
+        <v>1441986</v>
+      </c>
+      <c r="AF19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>openai/gpt-4.1-nano</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>GPT-4.1 Nano</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-09-16T03:23:30+00:00</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0.1434021604287071</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.2194519351485593</v>
+      </c>
+      <c r="M20" t="n">
+        <v>24.49324424955361</v>
+      </c>
+      <c r="N20" t="n">
+        <v>12.31697458631575</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" s="4" t="n">
         <v>0.8991138377641446</v>
       </c>
-      <c r="R18" s="4" t="n">
+      <c r="R20" s="4" t="n">
         <v>0.9558232931726908</v>
       </c>
-      <c r="S18" s="4" t="n">
+      <c r="S20" s="4" t="n">
         <v>0.7005347593582888</v>
       </c>
-      <c r="T18" s="4" t="n">
+      <c r="T20" s="4" t="n">
         <v>0.5421686746987951</v>
       </c>
-      <c r="U18" s="4" t="n">
+      <c r="U20" s="4" t="n">
         <v>0.72</v>
       </c>
-      <c r="V18" s="4" t="n">
+      <c r="V20" s="4" t="n">
         <v>0.62</v>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="X18" t="n">
+      <c r="X20" t="n">
         <v>0.529</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Y20" t="n">
         <v>0.398</v>
       </c>
-      <c r="Z18" s="4" t="n">
+      <c r="Z20" s="4" t="n">
         <v>0.5140122481389001</v>
       </c>
-      <c r="AA18" s="4" t="n">
+      <c r="AA20" s="4" t="n">
         <v>0.3758955615145875</v>
       </c>
-      <c r="AB18" s="4" t="n">
+      <c r="AB20" s="4" t="n">
         <v>0.4635</v>
       </c>
-      <c r="AC18" s="4" t="n">
+      <c r="AC20" s="4" t="n">
         <v>0.4473337487719194</v>
       </c>
-      <c r="AD18" s="4" t="n">
+      <c r="AD20" s="4" t="n">
         <v>0.731</v>
       </c>
-      <c r="AE18" s="5" t="n">
+      <c r="AE20" s="5" t="n">
         <v>1108245</v>
       </c>
-      <c r="AF18" s="5" t="n">
+      <c r="AF20" s="5" t="n">
         <v>55419</v>
       </c>
-      <c r="AG18" s="5" t="n">
+      <c r="AG20" s="5" t="n">
         <v>36224</v>
       </c>
-      <c r="AH18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" s="3" t="n">
+      <c r="AH20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3" t="n">
         <v>0.1302753</v>
       </c>
-      <c r="AJ18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="3" t="n">
+      <c r="AJ20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3" t="n">
         <v>0.1302753</v>
       </c>
-      <c r="AL18" s="3" t="n">
+      <c r="AL20" s="3" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL18"/>
+  <autoFilter ref="A1:AL20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11425,7 +11941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -12014,12 +12530,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen3.5-2b-q8-gguf</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen3.5 2B (GGUF Q8_0, local)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -12031,13 +12547,13 @@
         <v>1000</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.78</v>
+        <v>0.648</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.7603515978750895</v>
+        <v>0.6273835935085809</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>780</v>
+        <v>648</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>0</v>
@@ -12049,12 +12565,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen3.5-2b-q8-gguf</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen3.5 2B (GGUF Q8_0, local)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -12066,13 +12582,13 @@
         <v>1000</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.744</v>
+        <v>0.517</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.7113942857254609</v>
+        <v>0.5062609313499989</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>744</v>
+        <v>517</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>0</v>
@@ -12084,12 +12600,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen3.5-2b-q8-gguf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen3.5 2B (GGUF Q8_0, local)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -12101,13 +12617,13 @@
         <v>2000</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.762</v>
+        <v>0.5825</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.736163325053324</v>
+        <v>0.5734975422659654</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>1524</v>
+        <v>1165</v>
       </c>
       <c r="H19" s="4" t="n">
         <v>0</v>
@@ -12119,12 +12635,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>local/qwen3.5-4b-q4km-gguf</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Qwen3.5 4B (GGUF Q4_K_M, local)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -12136,16 +12652,16 @@
         <v>1000</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.465</v>
+        <v>0.8</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.5053205391654078</v>
+        <v>0.7784520148968087</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>465</v>
+        <v>800</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.322</v>
+        <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>60</v>
@@ -12154,12 +12670,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>local/qwen3.5-4b-q4km-gguf</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Qwen3.5 4B (GGUF Q4_K_M, local)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -12171,16 +12687,16 @@
         <v>1000</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.606</v>
+        <v>0.749</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.5671517703461975</v>
+        <v>0.7246091754455255</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>606</v>
+        <v>749</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="I21" s="5" t="n">
         <v>60</v>
@@ -12189,12 +12705,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>local/qwen3.5-4b-q4km-gguf</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Qwen3.5 4B (GGUF Q4_K_M, local)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -12206,16 +12722,16 @@
         <v>2000</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.5355</v>
+        <v>0.7745</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.5411026333400099</v>
+        <v>0.7528237438696134</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1071</v>
+        <v>1549</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.165</v>
+        <v>0</v>
       </c>
       <c r="I22" s="5" t="n">
         <v>60</v>
@@ -12224,12 +12740,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -12241,16 +12757,16 @@
         <v>1000</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.738</v>
+        <v>0.78</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.7285750142849275</v>
+        <v>0.7603515978750895</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>738</v>
+        <v>780</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>60</v>
@@ -12259,12 +12775,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -12276,13 +12792,13 @@
         <v>1000</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.737</v>
+        <v>0.744</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.712693713084553</v>
+        <v>0.7113942857254609</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="H24" s="4" t="n">
         <v>0</v>
@@ -12294,12 +12810,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -12311,16 +12827,16 @@
         <v>2000</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.7375</v>
+        <v>0.762</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.7216311867724771</v>
+        <v>0.736163325053324</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1475</v>
+        <v>1524</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="I25" s="5" t="n">
         <v>60</v>
@@ -12329,12 +12845,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -12346,16 +12862,16 @@
         <v>1000</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.509</v>
+        <v>0.465</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.5867378280355483</v>
+        <v>0.5053205391654078</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>509</v>
+        <v>465</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.343</v>
+        <v>0.322</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>60</v>
@@ -12364,12 +12880,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -12381,16 +12897,16 @@
         <v>1000</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.711</v>
+        <v>0.606</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.7031769757373104</v>
+        <v>0.5671517703461975</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>711</v>
+        <v>606</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.061</v>
+        <v>0.008</v>
       </c>
       <c r="I27" s="5" t="n">
         <v>60</v>
@@ -12399,12 +12915,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -12416,16 +12932,16 @@
         <v>2000</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.61</v>
+        <v>0.5355</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.6504937686437986</v>
+        <v>0.5411026333400099</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>1220</v>
+        <v>1071</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.202</v>
+        <v>0.165</v>
       </c>
       <c r="I28" s="5" t="n">
         <v>60</v>
@@ -12434,12 +12950,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -12451,16 +12967,16 @@
         <v>1000</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.529</v>
+        <v>0.738</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.5140122481389001</v>
+        <v>0.7285750142849275</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>529</v>
+        <v>738</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="I29" s="5" t="n">
         <v>60</v>
@@ -12469,12 +12985,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -12486,13 +13002,13 @@
         <v>1000</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.398</v>
+        <v>0.737</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3758955615145875</v>
+        <v>0.712693713084553</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>398</v>
+        <v>737</v>
       </c>
       <c r="H30" s="4" t="n">
         <v>0</v>
@@ -12504,12 +13020,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -12521,16 +13037,16 @@
         <v>2000</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.4635</v>
+        <v>0.7375</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.4473337487719194</v>
+        <v>0.7216311867724771</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>927</v>
+        <v>1475</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="I31" s="5" t="n">
         <v>60</v>
@@ -12539,12 +13055,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -12556,16 +13072,16 @@
         <v>1000</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.842</v>
+        <v>0.509</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.8314865753296514</v>
+        <v>0.5867378280355483</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>842</v>
+        <v>509</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0</v>
+        <v>0.343</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>60</v>
@@ -12574,12 +13090,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -12591,16 +13107,16 @@
         <v>1000</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.711</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.8034449936517111</v>
+        <v>0.7031769757373104</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>815</v>
+        <v>711</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>60</v>
@@ -12609,12 +13125,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -12626,16 +13142,16 @@
         <v>2000</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.8285</v>
+        <v>0.61</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.8179267929293625</v>
+        <v>0.6504937686437986</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1657</v>
+        <v>1220</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0</v>
+        <v>0.202</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>60</v>
@@ -12644,12 +13160,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -12661,16 +13177,16 @@
         <v>1000</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.715</v>
+        <v>0.529</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.7079848008862988</v>
+        <v>0.5140122481389001</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>715</v>
+        <v>529</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="I35" s="5" t="n">
         <v>60</v>
@@ -12679,12 +13195,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -12696,16 +13212,16 @@
         <v>1000</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.661</v>
+        <v>0.398</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.6593342425290085</v>
+        <v>0.3758955615145875</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>661</v>
+        <v>398</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I36" s="5" t="n">
         <v>60</v>
@@ -12714,12 +13230,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -12731,16 +13247,16 @@
         <v>2000</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.4635</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.6845822094887644</v>
+        <v>0.4473337487719194</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1376</v>
+        <v>927</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I37" s="5" t="n">
         <v>60</v>
@@ -12749,12 +13265,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -12766,13 +13282,13 @@
         <v>1000</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.868</v>
+        <v>0.842</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.8492172170319239</v>
+        <v>0.8314865753296514</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>868</v>
+        <v>842</v>
       </c>
       <c r="H38" s="4" t="n">
         <v>0</v>
@@ -12784,12 +13300,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -12801,13 +13317,13 @@
         <v>1000</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.831</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.8000988567676002</v>
+        <v>0.8034449936517111</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>831</v>
+        <v>815</v>
       </c>
       <c r="H39" s="4" t="n">
         <v>0</v>
@@ -12819,12 +13335,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -12836,13 +13352,13 @@
         <v>2000</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.8495</v>
+        <v>0.8285</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.8278820044607954</v>
+        <v>0.8179267929293625</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>1699</v>
+        <v>1657</v>
       </c>
       <c r="H40" s="4" t="n">
         <v>0</v>
@@ -12854,12 +13370,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -12871,16 +13387,16 @@
         <v>1000</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.715</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.7992131261387427</v>
+        <v>0.7079848008862988</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>809</v>
+        <v>715</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="I41" s="5" t="n">
         <v>60</v>
@@ -12889,12 +13405,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -12906,16 +13422,16 @@
         <v>1000</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.794</v>
+        <v>0.661</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.7717528819109728</v>
+        <v>0.6593342425290085</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>794</v>
+        <v>661</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I42" s="5" t="n">
         <v>60</v>
@@ -12924,12 +13440,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -12941,16 +13457,16 @@
         <v>2000</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.8015</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.7855676169719019</v>
+        <v>0.6845822094887644</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>1603</v>
+        <v>1376</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I43" s="5" t="n">
         <v>60</v>
@@ -12959,12 +13475,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -12976,16 +13492,16 @@
         <v>1000</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.796</v>
+        <v>0.868</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.7792340968020122</v>
+        <v>0.8492172170319239</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>796</v>
+        <v>868</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I44" s="5" t="n">
         <v>60</v>
@@ -12994,12 +13510,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -13011,16 +13527,16 @@
         <v>1000</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.76</v>
+        <v>0.831</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.7439524644750251</v>
+        <v>0.8000988567676002</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>760</v>
+        <v>831</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I45" s="5" t="n">
         <v>60</v>
@@ -13029,12 +13545,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -13046,16 +13562,16 @@
         <v>2000</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.778</v>
+        <v>0.8495</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.7614406146917927</v>
+        <v>0.8278820044607954</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>1556</v>
+        <v>1699</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I46" s="5" t="n">
         <v>60</v>
@@ -13064,12 +13580,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -13081,16 +13597,16 @@
         <v>1000</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.882</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.8710472576948233</v>
+        <v>0.7992131261387427</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>882</v>
+        <v>809</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I47" s="5" t="n">
         <v>60</v>
@@ -13099,12 +13615,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -13116,13 +13632,13 @@
         <v>1000</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.846</v>
+        <v>0.794</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.8354346192098669</v>
+        <v>0.7717528819109728</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>846</v>
+        <v>794</v>
       </c>
       <c r="H48" s="4" t="n">
         <v>0</v>
@@ -13134,12 +13650,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -13151,16 +13667,16 @@
         <v>2000</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.864</v>
+        <v>0.8015</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.8523414150627505</v>
+        <v>0.7855676169719019</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>1728</v>
+        <v>1603</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I49" s="5" t="n">
         <v>60</v>
@@ -13169,12 +13685,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -13186,16 +13702,16 @@
         <v>1000</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.858</v>
+        <v>0.796</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.846487306452871</v>
+        <v>0.7792340968020122</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>858</v>
+        <v>796</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I50" s="5" t="n">
         <v>60</v>
@@ -13204,12 +13720,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -13221,16 +13737,16 @@
         <v>1000</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.797</v>
+        <v>0.76</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.7859849948864567</v>
+        <v>0.7439524644750251</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>797</v>
+        <v>760</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="I51" s="5" t="n">
         <v>60</v>
@@ -13239,12 +13755,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -13256,23 +13772,233 @@
         <v>2000</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.8275</v>
+        <v>0.778</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.8155753958777252</v>
+        <v>0.7614406146917927</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>1655</v>
+        <v>1556</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="I52" s="5" t="n">
         <v>60</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>qwen/qwen3.8-flash</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Qwen3.8 Flash</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>0.8710472576948233</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>882</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>qwen/qwen3.8-flash</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Qwen3.8 Flash</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>0.8354346192098669</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>846</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>qwen/qwen3.8-flash</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Qwen3.8 Flash</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>0.8523414150627505</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>1728</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>0.846487306452871</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>858</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>0.7859849948864567</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>797</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>0.8275</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>0.8155753958777252</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>1655</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I52"/>
+  <autoFilter ref="A1:I58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13283,7 +14009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -13596,545 +14322,635 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen3.5-2b-q8-gguf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen3.5 2B (GGUF Q8_0, local)</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.824</v>
+        <v>0.705</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.768</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>674</v>
+        <v>435</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.674</v>
+        <v>0.435</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>106</v>
+        <v>213</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.106</v>
+        <v>0.213</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="L7" t="n">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.15</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>local/qwen3.5-4b-q4km-gguf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Qwen3.5 4B (GGUF Q4_K_M, local)</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.651</v>
+        <v>0.835</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.43</v>
+        <v>0.776</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>361</v>
+        <v>692</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.361</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.104</v>
+        <v>0.108</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>245</v>
+        <v>57</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.245</v>
+        <v>0.057</v>
       </c>
       <c r="L8" t="n">
-        <v>290</v>
+        <v>143</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.29</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.763</v>
+        <v>0.824</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.695</v>
+        <v>0.768</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>619</v>
+        <v>674</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.619</v>
+        <v>0.674</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.119</v>
+        <v>0.106</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.118</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.144</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.7</v>
+        <v>0.651</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.519</v>
+        <v>0.43</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>460</v>
+        <v>361</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.46</v>
+        <v>0.361</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.049</v>
+        <v>0.104</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.251</v>
+        <v>0.245</v>
       </c>
       <c r="L10" t="n">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.731</v>
+        <v>0.763</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.505</v>
+        <v>0.695</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>329</v>
+        <v>619</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.329</v>
+        <v>0.619</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>200</v>
+        <v>119</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.2</v>
+        <v>0.119</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>69</v>
+        <v>118</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.118</v>
       </c>
       <c r="L11" t="n">
-        <v>402</v>
+        <v>144</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.402</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.863</v>
+        <v>0.7</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.833</v>
+        <v>0.519</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>760</v>
+        <v>460</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.76</v>
+        <v>0.46</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.082</v>
+        <v>0.049</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>55</v>
+        <v>251</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.055</v>
+        <v>0.251</v>
       </c>
       <c r="L12" t="n">
-        <v>103</v>
+        <v>240</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.103</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.718</v>
+        <v>0.731</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.612</v>
+        <v>0.505</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>547</v>
+        <v>329</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.547</v>
+        <v>0.329</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.168</v>
+        <v>0.2</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.114</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>171</v>
+        <v>402</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.171</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.895</v>
+        <v>0.863</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.866</v>
+        <v>0.833</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>797</v>
+        <v>760</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.797</v>
+        <v>0.76</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.082</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.034</v>
+        <v>0.055</v>
       </c>
       <c r="L14" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.098</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.865</v>
+        <v>0.718</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.612</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>734</v>
+        <v>547</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.734</v>
+        <v>0.547</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>75</v>
+        <v>168</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.075</v>
+        <v>0.168</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.06</v>
+        <v>0.114</v>
       </c>
       <c r="L15" t="n">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.131</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.832</v>
+        <v>0.895</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.77</v>
+        <v>0.866</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>694</v>
+        <v>797</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.694</v>
+        <v>0.797</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.102</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.066</v>
+        <v>0.034</v>
       </c>
       <c r="L16" t="n">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.138</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.91</v>
+        <v>0.865</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.887</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>819</v>
+        <v>734</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.819</v>
+        <v>0.734</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.063</v>
+        <v>0.075</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.027</v>
+        <v>0.06</v>
       </c>
       <c r="L17" t="n">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.091</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D18" s="4" t="n">
+        <v>0.832</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>694</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="L18" t="n">
+        <v>138</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>0.138</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>qwen/qwen3.8-flash</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Qwen3.8 Flash</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>819</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="L19" t="n">
+        <v>91</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>0.091</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D20" s="4" t="n">
         <v>0.867</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E20" s="4" t="n">
         <v>0.822</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F20" s="5" t="n">
         <v>761</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>0.761</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="H20" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="I18" s="4" t="n">
+      <c r="I20" s="4" t="n">
         <v>0.097</v>
       </c>
-      <c r="J18" s="5" t="n">
+      <c r="J20" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="K18" s="4" t="n">
+      <c r="K20" s="4" t="n">
         <v>0.036</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L20" t="n">
         <v>106</v>
       </c>
-      <c r="M18" s="4" t="n">
+      <c r="M20" s="4" t="n">
         <v>0.106</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M18"/>
+  <autoFilter ref="A1:M20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results/benchmark_results.xlsx
+++ b/results/benchmark_results.xlsx
@@ -23,17 +23,17 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Legend'!$A$1:$D$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Leaderboard'!$A$1:$AL$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Leaderboard'!$A$1:$AL$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Summarization'!$A$1:$P$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Hallucination'!$A$1:$O$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Classification'!$A$1:$I$58</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'CrossLingual'!$A$1:$M$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Classification'!$A$1:$I$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'CrossLingual'!$A$1:$M$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'ClassificationModes'!$A$1:$K$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'SurfaceFacts'!$A$1:$L$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cost'!$A$1:$S$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Usage'!$A$1:$M$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cost'!$A$1:$S$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Usage'!$A$1:$M$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Judge'!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Runs'!$A$1:$T$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Runs'!$A$1:$T$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -480,7 +480,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17T08:13:45+00:00</t>
+          <t>2026-09-21T00:15:42+00:00</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -972,12 +972,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
+          <t>local/laya-multilingual</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
+          <t>Laya Multilingual (mmBERT-base decision head, local)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -1009,12 +1009,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
+          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -1046,12 +1046,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>local/qwen3.5-2b-q8-gguf</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Qwen3.5 2B (GGUF Q8_0, local)</t>
+          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -1083,12 +1083,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>local/qwen3.5-4b-q4km-gguf</t>
+          <t>local/qwen3.5-2b-q8-gguf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Qwen3.5 4B (GGUF Q4_K_M, local)</t>
+          <t>Qwen3.5 2B (GGUF Q8_0, local)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
@@ -1120,89 +1120,59 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen3.5-4b-q4km-gguf</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0.2</v>
-      </c>
+          <t>Qwen3.5 4B (GGUF Q4_K_M, local)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-16T03:10:41+00:00</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>0.07769180000000001</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>0.08999796</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>0.01189376</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>0.17958352</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>0.1795835200000001</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>0.17958352</v>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>0.1795835200000001</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>0.17958352</v>
-      </c>
-      <c r="S9" t="b">
-        <v>1</v>
-      </c>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1211,17 +1181,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-16T03:17:56+00:00</t>
+          <t>2026-09-16T03:10:41+00:00</t>
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.0385285</v>
+        <v>0.07769180000000001</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.0433295</v>
+        <v>0.08999796</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.00566052</v>
+        <v>0.01189376</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0</v>
@@ -1230,22 +1200,22 @@
         <v>0</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.08751852</v>
+        <v>0.17958352</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.08751852</v>
+        <v>0.1795835200000001</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.08751852</v>
+        <v>0.17958352</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.08751852</v>
+        <v>0.1795835200000001</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.08751852</v>
+        <v>0.17958352</v>
       </c>
       <c r="S10" t="b">
         <v>1</v>
@@ -1254,22 +1224,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1278,17 +1248,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-16T03:15:02+00:00</t>
+          <t>2026-09-16T03:17:56+00:00</t>
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.0582456</v>
+        <v>0.0385285</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.06753291</v>
+        <v>0.0433295</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.008405670000000001</v>
+        <v>0.00566052</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
@@ -1297,22 +1267,22 @@
         <v>0</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.13418418</v>
+        <v>0.08751852</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.1341841799999999</v>
+        <v>0.08751852</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.13418418</v>
+        <v>0.08751852</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.1341841799999999</v>
+        <v>0.08751852</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.13418418</v>
+        <v>0.08751852</v>
       </c>
       <c r="S11" t="b">
         <v>1</v>
@@ -1321,12 +1291,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
@@ -1336,7 +1306,7 @@
         <v>0.015</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1345,17 +1315,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-16T03:07:59+00:00</t>
+          <t>2026-09-16T03:15:02+00:00</t>
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.0802729125</v>
+        <v>0.0582456</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.0986139</v>
+        <v>0.06753291</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.017520885</v>
+        <v>0.008405670000000001</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1364,46 +1334,46 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.1964076975</v>
+        <v>0.13418418</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.1964076975000001</v>
+        <v>0.1341841799999999</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0.1964076975</v>
+        <v>0.13418418</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.1964076975000001</v>
+        <v>0.1341841799999999</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.17912064</v>
+        <v>0.13418418</v>
       </c>
       <c r="S12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1412,17 +1382,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:30+00:00</t>
+          <t>2026-09-16T03:07:59+00:00</t>
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.0519185</v>
+        <v>0.0802729125</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.067397</v>
+        <v>0.0986139</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.0109598</v>
+        <v>0.017520885</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
@@ -1431,43 +1401,43 @@
         <v>0</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.1964076975</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.1964076975000001</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.1964076975</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.1964076975000001</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.1302753</v>
+        <v>0.17912064</v>
       </c>
       <c r="S13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.005</v>
+        <v>0.025</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>0.4</v>
@@ -1479,17 +1449,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-16T04:40:49+00:00</t>
+          <t>2026-09-16T03:23:30+00:00</t>
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.08205585</v>
+        <v>0.0519185</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.1433661</v>
+        <v>0.067397</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.0474705</v>
+        <v>0.0109598</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0</v>
@@ -1498,22 +1468,22 @@
         <v>0</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>0.27289245</v>
+        <v>0.1302753</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.2728924500000001</v>
+        <v>0.1302753</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.27289245</v>
+        <v>0.1302753</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.2728924500000001</v>
+        <v>0.1302753</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.27289245</v>
+        <v>0.1302753</v>
       </c>
       <c r="S14" t="b">
         <v>1</v>
@@ -1522,22 +1492,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1.25</v>
+        <v>0.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1546,17 +1516,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-16T03:20:07+00:00</t>
+          <t>2026-09-16T04:40:49+00:00</t>
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.1453735</v>
+        <v>0.08205585</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.1435934</v>
+        <v>0.1433661</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02710335</v>
+        <v>0.0474705</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>0</v>
@@ -1565,22 +1535,22 @@
         <v>0</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0.31607025</v>
+        <v>0.27289245</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>0.3160702499999996</v>
+        <v>0.2728924500000001</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>0.31607025</v>
+        <v>0.27289245</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0.3160702499999996</v>
+        <v>0.2728924500000001</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.3160702500000001</v>
+        <v>0.27289245</v>
       </c>
       <c r="S15" t="b">
         <v>1</v>
@@ -1589,12 +1559,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
@@ -1604,7 +1574,7 @@
         <v>0.02</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1613,17 +1583,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-16T02:59:08+00:00</t>
+          <t>2026-09-16T03:20:07+00:00</t>
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.12600455</v>
+        <v>0.1453735</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.1584021</v>
+        <v>0.1435934</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.0262596</v>
+        <v>0.02710335</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>0</v>
@@ -1632,44 +1602,46 @@
         <v>0</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.31066625</v>
+        <v>0.31607025</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.3106662500000003</v>
+        <v>0.3160702499999996</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.31066625</v>
+        <v>0.31607025</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.3106662500000003</v>
+        <v>0.3160702499999996</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.2877202</v>
+        <v>0.3160702500000001</v>
       </c>
       <c r="S16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.04815</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0.02</v>
+      </c>
       <c r="E17" s="3" t="n">
-        <v>0.19305</v>
+        <v>1.2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1678,17 +1650,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-16T03:34:40+00:00</t>
+          <t>2026-09-16T02:59:08+00:00</t>
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.04959875775</v>
+        <v>0.12600455</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.06309176505</v>
+        <v>0.1584021</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.01054341345</v>
+        <v>0.0262596</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>0</v>
@@ -1697,22 +1669,22 @@
         <v>0</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0.12323393625</v>
+        <v>0.31066625</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.1232339362500001</v>
+        <v>0.3106662500000003</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>0.12323393625</v>
+        <v>0.31066625</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.1232339362500001</v>
+        <v>0.3106662500000003</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.07244949735</v>
+        <v>0.2877202</v>
       </c>
       <c r="S17" t="b">
         <v>0</v>
@@ -1721,22 +1693,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>0.006</v>
-      </c>
+        <v>0.04815</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr"/>
       <c r="E18" s="3" t="n">
-        <v>0.13</v>
+        <v>0.19305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1745,17 +1715,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-16T03:31:23+00:00</t>
+          <t>2026-09-16T03:34:40+00:00</t>
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.01445385</v>
+        <v>0.04959875775</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.01955122</v>
+        <v>0.06309176505</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.0039132</v>
+        <v>0.01054341345</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
@@ -1764,46 +1734,46 @@
         <v>0</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0.03791827</v>
+        <v>0.12323393625</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.03791826999999996</v>
+        <v>0.1232339362500001</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>0.03791827</v>
+        <v>0.12323393625</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>0.03791826999999996</v>
+        <v>0.1232339362500001</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.03795787999999999</v>
+        <v>0.07244949735</v>
       </c>
       <c r="S18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.016</v>
+        <v>0.006</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.47</v>
+        <v>0.13</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1812,17 +1782,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-16T03:26:19+00:00</t>
+          <t>2026-09-16T03:31:23+00:00</t>
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.06590207000000001</v>
+        <v>0.01445385</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.068078582</v>
+        <v>0.01955122</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.013945102</v>
+        <v>0.0039132</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>0</v>
@@ -1831,22 +1801,22 @@
         <v>0</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.03791827</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.03791826999999996</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.03791827</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.03791826999999996</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.148121674</v>
+        <v>0.03795787999999999</v>
       </c>
       <c r="S19" t="b">
         <v>1</v>
@@ -1855,72 +1825,139 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>qwen/qwen3.8-flash</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Qwen3.8 Flash</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-09-16T03:26:19+00:00</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>0.06590207000000001</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0.068078582</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0.013945102</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>0.147925754</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>0.147925754</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>0.147925754</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.147925754</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>0.148121674</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>z-ai/glm-5.3-flash</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>GLM 5.3 Flash</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C21" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>0.02</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>0.3333</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>2026-09-16T04:41:38+00:00</t>
         </is>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H21" s="3" t="n">
         <v>0.0828101102</v>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I21" s="3" t="n">
         <v>0.11700001578</v>
       </c>
-      <c r="J20" s="3" t="n">
+      <c r="J21" s="3" t="n">
         <v>0.0149070175</v>
       </c>
-      <c r="K20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3" t="n">
+      <c r="K21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3" t="n">
         <v>0.21471714348</v>
       </c>
-      <c r="N20" s="3" t="n">
+      <c r="N21" s="3" t="n">
         <v>0.2147171434799998</v>
       </c>
-      <c r="O20" s="3" t="n">
+      <c r="O21" s="3" t="n">
         <v>0.21471714348</v>
       </c>
-      <c r="P20" s="3" t="n">
+      <c r="P21" s="3" t="n">
         <v>0.2147171434799998</v>
       </c>
-      <c r="Q20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="4" t="n">
+      <c r="Q21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="4" t="n">
         <v>0.1606481436</v>
       </c>
-      <c r="S20" t="b">
+      <c r="S21" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S20"/>
+  <autoFilter ref="A1:S21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1931,7 +1968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -2154,19 +2191,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
+          <t>local/laya-multilingual</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
+          <t>Laya Multilingual (mmBERT-base decision head, local)</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>2162979</v>
+        <v>544388</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>0</v>
@@ -2175,43 +2212,43 @@
         <v>0</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>16353</v>
+        <v>0</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>2179332</v>
+        <v>544388</v>
       </c>
       <c r="J5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" s="5" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
+          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>1441986</v>
+        <v>2162979</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0</v>
@@ -2220,13 +2257,13 @@
         <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0</v>
+        <v>16353</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>1441986</v>
+        <v>2179332</v>
       </c>
       <c r="J6" s="5" t="n">
         <v>2000</v>
@@ -2244,57 +2281,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>local/qwen3.5-2b-q8-gguf</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Qwen3.5 2B (GGUF Q8_0, local)</t>
+          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1441986</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>1441986</v>
+      </c>
+      <c r="J7" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="D7" s="5" t="n">
-        <v>721898</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>721898</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" s="5" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>local/qwen3.5-4b-q4km-gguf</t>
+          <t>local/qwen3.5-2b-q8-gguf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Qwen3.5 4B (GGUF Q4_K_M, local)</t>
+          <t>Qwen3.5 2B (GGUF Q8_0, local)</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
@@ -2334,57 +2371,57 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen3.5-4b-q4km-gguf</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen3.5 4B (GGUF Q4_K_M, local)</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1300</v>
+        <v>2000</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1092316</v>
+        <v>721898</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>295936</v>
+        <v>0</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>71944</v>
+        <v>0</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>1164260</v>
+        <v>721898</v>
       </c>
       <c r="J9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>1300</v>
+        <v>2000</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>1300</v>
+        <v>2000</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>1300</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
@@ -2394,19 +2431,19 @@
         <v>1092316</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>318592</v>
+        <v>295936</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>69602</v>
+        <v>71944</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>1161918</v>
+        <v>1164260</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>0</v>
@@ -2424,12 +2461,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
@@ -2439,19 +2476,19 @@
         <v>1092316</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>299392</v>
+        <v>318592</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>71698</v>
+        <v>69602</v>
       </c>
       <c r="H11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>1164014</v>
+        <v>1161918</v>
       </c>
       <c r="J11" s="5" t="n">
         <v>0</v>
@@ -2469,34 +2506,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1107916</v>
+        <v>1092316</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>183856</v>
+        <v>299392</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>62923</v>
+        <v>71698</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>1170839</v>
+        <v>1164014</v>
       </c>
       <c r="J12" s="5" t="n">
         <v>0</v>
@@ -2514,34 +2551,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1108245</v>
+        <v>1107916</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>36224</v>
+        <v>183856</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>55419</v>
+        <v>62923</v>
       </c>
       <c r="H13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>1163664</v>
+        <v>1170839</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>0</v>
@@ -2559,34 +2596,34 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1106945</v>
+        <v>1108245</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>40320</v>
+        <v>36224</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>548399</v>
+        <v>55419</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>433920</v>
+        <v>0</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>1655344</v>
+        <v>1163664</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>0</v>
@@ -2604,12 +2641,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -2619,19 +2656,19 @@
         <v>1106945</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0</v>
+        <v>40320</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>75745</v>
+        <v>548399</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0</v>
+        <v>433920</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>1182690</v>
+        <v>1655344</v>
       </c>
       <c r="J15" s="5" t="n">
         <v>0</v>
@@ -2649,12 +2686,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -2667,16 +2704,16 @@
         <v>0</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>458921</v>
+        <v>0</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>55276</v>
+        <v>75745</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>1162221</v>
+        <v>1182690</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>0</v>
@@ -2694,34 +2731,34 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1213604</v>
+        <v>1106945</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>102934</v>
+        <v>0</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0</v>
+        <v>458921</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>72595</v>
+        <v>55276</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>1286199</v>
+        <v>1162221</v>
       </c>
       <c r="J17" s="5" t="n">
         <v>0</v>
@@ -2739,34 +2776,34 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>1061596</v>
+        <v>1213604</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>24960</v>
+        <v>102934</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>51608</v>
+        <v>72595</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>1113204</v>
+        <v>1286199</v>
       </c>
       <c r="J18" s="5" t="n">
         <v>0</v>
@@ -2778,18 +2815,18 @@
         <v>1300</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>1307</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -2799,19 +2836,19 @@
         <v>1061596</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>265984</v>
+        <v>24960</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>52179</v>
+        <v>51608</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>1113775</v>
+        <v>1113204</v>
       </c>
       <c r="J19" s="5" t="n">
         <v>0</v>
@@ -2823,40 +2860,40 @@
         <v>1300</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>1314</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>1293055</v>
+        <v>1061596</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>104384</v>
+        <v>265984</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>119092</v>
+        <v>52179</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>35855</v>
+        <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>1412147</v>
+        <v>1113775</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>0</v>
@@ -2868,11 +2905,56 @@
         <v>1300</v>
       </c>
       <c r="M20" s="5" t="n">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
         <v>1300</v>
       </c>
+      <c r="D21" s="5" t="n">
+        <v>1293055</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>104384</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>119092</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>35855</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>1412147</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M21" s="5" t="n">
+        <v>1300</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M20"/>
+  <autoFilter ref="A1:M21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2908,7 +2990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -3278,7 +3360,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
+          <t>local/laya-multilingual</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3288,17 +3370,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>run-20260917T044122-e81422e2</t>
+          <t>run-20260921T000602-fd53c8c9</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T04:41:23+00:00</t>
+          <t>2026-09-21T00:15:42+00:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-17T04:41:22+00:00</t>
+          <t>2026-09-21T00:06:02+00:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3308,7 +3390,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>12ce0741fedd9b770a4593296378e383c3ca80b7</t>
+          <t>ad6a92fc3526efc27ceaa68d9e793b56fda72b88</t>
         </is>
       </c>
       <c r="H5" t="b">
@@ -3364,7 +3446,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3374,17 +3456,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>run-20260917T044118-6aa4395f</t>
+          <t>run-20260917T044122-e81422e2</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T04:41:20+00:00</t>
+          <t>2026-09-17T04:41:23+00:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-17T04:41:18+00:00</t>
+          <t>2026-09-17T04:41:22+00:00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3450,7 +3532,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>local/qwen3.5-2b-q8-gguf</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3460,17 +3542,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>run-20260917T044125-67e7e99a</t>
+          <t>run-20260917T044118-6aa4395f</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T05:31:28+00:00</t>
+          <t>2026-09-17T04:41:20+00:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-17T04:41:25+00:00</t>
+          <t>2026-09-17T04:41:18+00:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3536,7 +3618,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>local/qwen3.5-4b-q4km-gguf</t>
+          <t>local/qwen3.5-2b-q8-gguf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3546,17 +3628,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>run-20260917T053130-4932fffb</t>
+          <t>run-20260917T044125-67e7e99a</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17T08:13:45+00:00</t>
+          <t>2026-09-17T05:31:28+00:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-17T05:31:30+00:00</t>
+          <t>2026-09-17T04:41:25+00:00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3566,7 +3648,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>a05631eb2e5769458bfd0e57d53515a08ebf6df1</t>
+          <t>12ce0741fedd9b770a4593296378e383c3ca80b7</t>
         </is>
       </c>
       <c r="H8" t="b">
@@ -3622,7 +3704,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen3.5-4b-q4km-gguf</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3632,17 +3714,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>run-20260916T031043-60c30b6a</t>
+          <t>run-20260917T053130-4932fffb</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:15:02+00:00</t>
+          <t>2026-09-17T08:13:45+00:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-16T03:10:43+00:00</t>
+          <t>2026-09-17T05:31:30+00:00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3650,8 +3732,14 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>a05631eb2e5769458bfd0e57d53515a08ebf6df1</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -3659,7 +3747,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>summarization, hallucination, classification</t>
+          <t>classification</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3668,7 +3756,7 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>3200</v>
+        <v>2000</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3702,7 +3790,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3712,17 +3800,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>run-20260916T031757-6f0019bc</t>
+          <t>run-20260916T031043-60c30b6a</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:20:07+00:00</t>
+          <t>2026-09-16T03:15:02+00:00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-16T03:17:57+00:00</t>
+          <t>2026-09-16T03:10:43+00:00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -3782,7 +3870,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3792,17 +3880,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>run-20260916T031504-7b84cf7d</t>
+          <t>run-20260916T031757-6f0019bc</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:17:56+00:00</t>
+          <t>2026-09-16T03:20:07+00:00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-16T03:15:04+00:00</t>
+          <t>2026-09-16T03:17:57+00:00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3862,7 +3950,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3872,17 +3960,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>run-20260916T030801-577d0830</t>
+          <t>run-20260916T031504-7b84cf7d</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:10:41+00:00</t>
+          <t>2026-09-16T03:17:56+00:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-16T03:08:01+00:00</t>
+          <t>2026-09-16T03:15:04+00:00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3942,7 +4030,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3952,17 +4040,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>run-20260916T032332-5a24afb2</t>
+          <t>run-20260916T030801-577d0830</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:26:19+00:00</t>
+          <t>2026-09-16T03:10:41+00:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:32+00:00</t>
+          <t>2026-09-16T03:08:01+00:00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4022,7 +4110,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4032,17 +4120,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>run-20260916T044051-1b0d71da</t>
+          <t>run-20260916T032332-5a24afb2</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T04:51:21+00:00</t>
+          <t>2026-09-16T03:26:19+00:00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-16T04:40:51+00:00</t>
+          <t>2026-09-16T03:23:32+00:00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4050,14 +4138,8 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
-        </is>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -4108,7 +4190,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4118,17 +4200,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>run-20260916T032009-aca77564</t>
+          <t>run-20260916T044051-1b0d71da</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:28+00:00</t>
+          <t>2026-09-16T04:51:21+00:00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-16T03:20:09+00:00</t>
+          <t>2026-09-16T04:40:51+00:00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4136,8 +4218,14 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
+        </is>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -4188,7 +4276,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4198,17 +4286,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>run-20260916T025909-be4eb782</t>
+          <t>run-20260916T032009-aca77564</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:02:43+00:00</t>
+          <t>2026-09-16T03:23:28+00:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-16T02:59:09+00:00</t>
+          <t>2026-09-16T03:20:09+00:00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4268,7 +4356,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4278,17 +4366,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>run-20260916T033441-93cb685e</t>
+          <t>run-20260916T025909-be4eb782</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:43:30+00:00</t>
+          <t>2026-09-16T03:02:43+00:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-16T03:34:41+00:00</t>
+          <t>2026-09-16T02:59:09+00:00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4348,7 +4436,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4358,17 +4446,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>run-20260916T033125-8730c140</t>
+          <t>run-20260916T033441-93cb685e</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:34:40+00:00</t>
+          <t>2026-09-16T03:43:30+00:00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-09-16T03:31:25+00:00</t>
+          <t>2026-09-16T03:34:41+00:00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -4428,7 +4516,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4438,17 +4526,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>run-20260916T032621-2ec5c283</t>
+          <t>run-20260916T033125-8730c140</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:31:23+00:00</t>
+          <t>2026-09-16T03:34:40+00:00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-09-16T03:26:21+00:00</t>
+          <t>2026-09-16T03:31:25+00:00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4508,7 +4596,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4518,17 +4606,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>run-20260916T044139-f5eda9f3</t>
+          <t>run-20260916T032621-2ec5c283</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T04:51:13+00:00</t>
+          <t>2026-09-16T03:31:23+00:00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-09-16T04:41:39+00:00</t>
+          <t>2026-09-16T03:26:21+00:00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4536,14 +4624,8 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
-        </is>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
-      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -4591,8 +4673,94 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>run-20260916T044139-f5eda9f3</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16T04:51:13+00:00</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-09-16T04:41:39+00:00</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
+        </is>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3.12.3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>summarization, hallucination, classification</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>en, ko</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>3200</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>cbe6fb9c14d4b2b12e690d6565e05bcf861c5db26cc56aef45e3e3810f67b298</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0135c4f4499e35dcde7855ad6afe33e333ebf2bca519a20b81257dc39150cd62</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>21debf696ed02ef001638142e2864a1bb58be409f88d8c86ad36e067ee609ca5</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>b49d914db700703584e2388f602808314a59c9e088a20f02e670ead58141fa96</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1bebd7a4e6cab622b3a85e6f856e019c9459100085c08ca38ccec107d5e3ec21</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T20"/>
+  <autoFilter ref="A1:T21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5922,12 +6090,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL20"/>
+  <dimension ref="A1:AL21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
     <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
@@ -5951,7 +6119,7 @@
     <col width="10" customWidth="1" min="24" max="24"/>
     <col width="10" customWidth="1" min="25" max="25"/>
     <col width="20" customWidth="1" min="26" max="26"/>
-    <col width="20" customWidth="1" min="27" max="27"/>
+    <col width="21" customWidth="1" min="27" max="27"/>
     <col width="22" customWidth="1" min="28" max="28"/>
     <col width="22" customWidth="1" min="29" max="29"/>
     <col width="19" customWidth="1" min="30" max="30"/>
@@ -8435,8 +8603,98 @@
         <v>0</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>local/laya-multilingual</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Laya Multilingual (mmBERT-base decision head, local)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>convaiinnovations</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" s="4" t="inlineStr"/>
+      <c r="R21" s="4" t="inlineStr"/>
+      <c r="S21" s="4" t="inlineStr"/>
+      <c r="T21" s="4" t="inlineStr"/>
+      <c r="U21" s="4" t="inlineStr"/>
+      <c r="V21" s="4" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="Z21" s="4" t="n">
+        <v>0.3312729217590112</v>
+      </c>
+      <c r="AA21" s="4" t="n">
+        <v>0.2508535938503552</v>
+      </c>
+      <c r="AB21" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AC21" s="4" t="n">
+        <v>0.2939712093714177</v>
+      </c>
+      <c r="AD21" s="4" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="AE21" s="5" t="n">
+        <v>544388</v>
+      </c>
+      <c r="AF21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="3" t="inlineStr"/>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL20"/>
+  <autoFilter ref="A1:AL21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11941,7 +12199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -12320,12 +12578,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
+          <t>local/laya-multilingual</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
+          <t>Laya Multilingual (mmBERT-base decision head, local)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -12337,13 +12595,13 @@
         <v>1000</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.578</v>
+        <v>0.398</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.5486232650628055</v>
+        <v>0.3312729217590112</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>578</v>
+        <v>398</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>0</v>
@@ -12355,12 +12613,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
+          <t>local/laya-multilingual</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
+          <t>Laya Multilingual (mmBERT-base decision head, local)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -12372,13 +12630,13 @@
         <v>1000</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.462</v>
+        <v>0.302</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.4225847136466017</v>
+        <v>0.2508535938503552</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>462</v>
+        <v>302</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>0</v>
@@ -12390,12 +12648,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
+          <t>local/laya-multilingual</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
+          <t>Laya Multilingual (mmBERT-base decision head, local)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -12407,13 +12665,13 @@
         <v>2000</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.52</v>
+        <v>0.35</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.4912105263425375</v>
+        <v>0.2939712093714177</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1040</v>
+        <v>700</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>0</v>
@@ -12425,12 +12683,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
+          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -12442,13 +12700,13 @@
         <v>1000</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.572</v>
+        <v>0.578</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.5383725106907433</v>
+        <v>0.5486232650628055</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>0</v>
@@ -12460,12 +12718,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
+          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -12477,13 +12735,13 @@
         <v>1000</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.458</v>
+        <v>0.462</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.4142792208259681</v>
+        <v>0.4225847136466017</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>0</v>
@@ -12495,12 +12753,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
+          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -12512,13 +12770,13 @@
         <v>2000</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.515</v>
+        <v>0.52</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.4816940963179205</v>
+        <v>0.4912105263425375</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1030</v>
+        <v>1040</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>0</v>
@@ -12530,12 +12788,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>local/qwen3.5-2b-q8-gguf</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qwen3.5 2B (GGUF Q8_0, local)</t>
+          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -12547,13 +12805,13 @@
         <v>1000</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.648</v>
+        <v>0.572</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.6273835935085809</v>
+        <v>0.5383725106907433</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>648</v>
+        <v>572</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>0</v>
@@ -12565,12 +12823,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>local/qwen3.5-2b-q8-gguf</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Qwen3.5 2B (GGUF Q8_0, local)</t>
+          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -12582,13 +12840,13 @@
         <v>1000</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.517</v>
+        <v>0.458</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.5062609313499989</v>
+        <v>0.4142792208259681</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>517</v>
+        <v>458</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>0</v>
@@ -12600,12 +12858,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>local/qwen3.5-2b-q8-gguf</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Qwen3.5 2B (GGUF Q8_0, local)</t>
+          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -12617,13 +12875,13 @@
         <v>2000</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.5825</v>
+        <v>0.515</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.5734975422659654</v>
+        <v>0.4816940963179205</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>1165</v>
+        <v>1030</v>
       </c>
       <c r="H19" s="4" t="n">
         <v>0</v>
@@ -12635,12 +12893,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>local/qwen3.5-4b-q4km-gguf</t>
+          <t>local/qwen3.5-2b-q8-gguf</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Qwen3.5 4B (GGUF Q4_K_M, local)</t>
+          <t>Qwen3.5 2B (GGUF Q8_0, local)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -12652,13 +12910,13 @@
         <v>1000</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.8</v>
+        <v>0.648</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.7784520148968087</v>
+        <v>0.6273835935085809</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>800</v>
+        <v>648</v>
       </c>
       <c r="H20" s="4" t="n">
         <v>0</v>
@@ -12670,12 +12928,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>local/qwen3.5-4b-q4km-gguf</t>
+          <t>local/qwen3.5-2b-q8-gguf</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Qwen3.5 4B (GGUF Q4_K_M, local)</t>
+          <t>Qwen3.5 2B (GGUF Q8_0, local)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -12687,13 +12945,13 @@
         <v>1000</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.749</v>
+        <v>0.517</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.7246091754455255</v>
+        <v>0.5062609313499989</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>749</v>
+        <v>517</v>
       </c>
       <c r="H21" s="4" t="n">
         <v>0</v>
@@ -12705,12 +12963,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>local/qwen3.5-4b-q4km-gguf</t>
+          <t>local/qwen3.5-2b-q8-gguf</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Qwen3.5 4B (GGUF Q4_K_M, local)</t>
+          <t>Qwen3.5 2B (GGUF Q8_0, local)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -12722,13 +12980,13 @@
         <v>2000</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.7745</v>
+        <v>0.5825</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.7528237438696134</v>
+        <v>0.5734975422659654</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1549</v>
+        <v>1165</v>
       </c>
       <c r="H22" s="4" t="n">
         <v>0</v>
@@ -12740,12 +12998,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen3.5-4b-q4km-gguf</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen3.5 4B (GGUF Q4_K_M, local)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -12757,13 +13015,13 @@
         <v>1000</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.7603515978750895</v>
+        <v>0.7784520148968087</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>780</v>
+        <v>800</v>
       </c>
       <c r="H23" s="4" t="n">
         <v>0</v>
@@ -12775,12 +13033,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen3.5-4b-q4km-gguf</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen3.5 4B (GGUF Q4_K_M, local)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -12792,13 +13050,13 @@
         <v>1000</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.744</v>
+        <v>0.749</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.7113942857254609</v>
+        <v>0.7246091754455255</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="H24" s="4" t="n">
         <v>0</v>
@@ -12810,12 +13068,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen3.5-4b-q4km-gguf</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen3.5 4B (GGUF Q4_K_M, local)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -12827,13 +13085,13 @@
         <v>2000</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.762</v>
+        <v>0.7745</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.736163325053324</v>
+        <v>0.7528237438696134</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1524</v>
+        <v>1549</v>
       </c>
       <c r="H25" s="4" t="n">
         <v>0</v>
@@ -12845,12 +13103,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -12862,16 +13120,16 @@
         <v>1000</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.465</v>
+        <v>0.78</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.5053205391654078</v>
+        <v>0.7603515978750895</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>465</v>
+        <v>780</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.322</v>
+        <v>0</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>60</v>
@@ -12880,12 +13138,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -12897,16 +13155,16 @@
         <v>1000</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.606</v>
+        <v>0.744</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.5671517703461975</v>
+        <v>0.7113942857254609</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>606</v>
+        <v>744</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="I27" s="5" t="n">
         <v>60</v>
@@ -12915,12 +13173,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -12932,16 +13190,16 @@
         <v>2000</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.5355</v>
+        <v>0.762</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.5411026333400099</v>
+        <v>0.736163325053324</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>1071</v>
+        <v>1524</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.165</v>
+        <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
         <v>60</v>
@@ -12950,12 +13208,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -12967,16 +13225,16 @@
         <v>1000</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.738</v>
+        <v>0.465</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.7285750142849275</v>
+        <v>0.5053205391654078</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>738</v>
+        <v>465</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.042</v>
+        <v>0.322</v>
       </c>
       <c r="I29" s="5" t="n">
         <v>60</v>
@@ -12985,12 +13243,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -13002,16 +13260,16 @@
         <v>1000</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.737</v>
+        <v>0.606</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.712693713084553</v>
+        <v>0.5671517703461975</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>737</v>
+        <v>606</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="I30" s="5" t="n">
         <v>60</v>
@@ -13020,12 +13278,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -13037,16 +13295,16 @@
         <v>2000</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.7375</v>
+        <v>0.5355</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.7216311867724771</v>
+        <v>0.5411026333400099</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>1475</v>
+        <v>1071</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.021</v>
+        <v>0.165</v>
       </c>
       <c r="I31" s="5" t="n">
         <v>60</v>
@@ -13055,12 +13313,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -13072,16 +13330,16 @@
         <v>1000</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.509</v>
+        <v>0.738</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.5867378280355483</v>
+        <v>0.7285750142849275</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>509</v>
+        <v>738</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.343</v>
+        <v>0.042</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>60</v>
@@ -13090,12 +13348,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -13107,16 +13365,16 @@
         <v>1000</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.711</v>
+        <v>0.737</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.7031769757373104</v>
+        <v>0.712693713084553</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>711</v>
+        <v>737</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>60</v>
@@ -13125,12 +13383,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -13142,16 +13400,16 @@
         <v>2000</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.61</v>
+        <v>0.7375</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.6504937686437986</v>
+        <v>0.7216311867724771</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1220</v>
+        <v>1475</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.202</v>
+        <v>0.021</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>60</v>
@@ -13160,12 +13418,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -13177,16 +13435,16 @@
         <v>1000</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.529</v>
+        <v>0.509</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.5140122481389001</v>
+        <v>0.5867378280355483</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>529</v>
+        <v>509</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0</v>
+        <v>0.343</v>
       </c>
       <c r="I35" s="5" t="n">
         <v>60</v>
@@ -13195,12 +13453,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -13212,16 +13470,16 @@
         <v>1000</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.398</v>
+        <v>0.711</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.3758955615145875</v>
+        <v>0.7031769757373104</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>398</v>
+        <v>711</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="I36" s="5" t="n">
         <v>60</v>
@@ -13230,12 +13488,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -13247,16 +13505,16 @@
         <v>2000</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.4635</v>
+        <v>0.61</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.4473337487719194</v>
+        <v>0.6504937686437986</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>927</v>
+        <v>1220</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0</v>
+        <v>0.202</v>
       </c>
       <c r="I37" s="5" t="n">
         <v>60</v>
@@ -13265,12 +13523,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -13282,13 +13540,13 @@
         <v>1000</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.842</v>
+        <v>0.529</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.8314865753296514</v>
+        <v>0.5140122481389001</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>842</v>
+        <v>529</v>
       </c>
       <c r="H38" s="4" t="n">
         <v>0</v>
@@ -13300,12 +13558,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -13317,13 +13575,13 @@
         <v>1000</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.398</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.8034449936517111</v>
+        <v>0.3758955615145875</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>815</v>
+        <v>398</v>
       </c>
       <c r="H39" s="4" t="n">
         <v>0</v>
@@ -13335,12 +13593,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -13352,13 +13610,13 @@
         <v>2000</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.8285</v>
+        <v>0.4635</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.8179267929293625</v>
+        <v>0.4473337487719194</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>1657</v>
+        <v>927</v>
       </c>
       <c r="H40" s="4" t="n">
         <v>0</v>
@@ -13370,12 +13628,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -13387,16 +13645,16 @@
         <v>1000</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.715</v>
+        <v>0.842</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.7079848008862988</v>
+        <v>0.8314865753296514</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>715</v>
+        <v>842</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="I41" s="5" t="n">
         <v>60</v>
@@ -13405,12 +13663,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -13422,16 +13680,16 @@
         <v>1000</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.661</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.6593342425290085</v>
+        <v>0.8034449936517111</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>661</v>
+        <v>815</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I42" s="5" t="n">
         <v>60</v>
@@ -13440,12 +13698,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -13457,16 +13715,16 @@
         <v>2000</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.8285</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.6845822094887644</v>
+        <v>0.8179267929293625</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>1376</v>
+        <v>1657</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I43" s="5" t="n">
         <v>60</v>
@@ -13475,12 +13733,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -13492,16 +13750,16 @@
         <v>1000</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.868</v>
+        <v>0.715</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.8492172170319239</v>
+        <v>0.7079848008862988</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>868</v>
+        <v>715</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="I44" s="5" t="n">
         <v>60</v>
@@ -13510,12 +13768,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -13527,16 +13785,16 @@
         <v>1000</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.831</v>
+        <v>0.661</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.8000988567676002</v>
+        <v>0.6593342425290085</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>831</v>
+        <v>661</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I45" s="5" t="n">
         <v>60</v>
@@ -13545,12 +13803,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -13562,16 +13820,16 @@
         <v>2000</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.8495</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.8278820044607954</v>
+        <v>0.6845822094887644</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>1699</v>
+        <v>1376</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I46" s="5" t="n">
         <v>60</v>
@@ -13580,12 +13838,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -13597,16 +13855,16 @@
         <v>1000</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.868</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.7992131261387427</v>
+        <v>0.8492172170319239</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>809</v>
+        <v>868</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I47" s="5" t="n">
         <v>60</v>
@@ -13615,12 +13873,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -13632,13 +13890,13 @@
         <v>1000</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.794</v>
+        <v>0.831</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.7717528819109728</v>
+        <v>0.8000988567676002</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>794</v>
+        <v>831</v>
       </c>
       <c r="H48" s="4" t="n">
         <v>0</v>
@@ -13650,12 +13908,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -13667,16 +13925,16 @@
         <v>2000</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.8015</v>
+        <v>0.8495</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.7855676169719019</v>
+        <v>0.8278820044607954</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>1603</v>
+        <v>1699</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I49" s="5" t="n">
         <v>60</v>
@@ -13685,12 +13943,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -13702,13 +13960,13 @@
         <v>1000</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.796</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.7792340968020122</v>
+        <v>0.7992131261387427</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>796</v>
+        <v>809</v>
       </c>
       <c r="H50" s="4" t="n">
         <v>0.02</v>
@@ -13720,12 +13978,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -13737,16 +13995,16 @@
         <v>1000</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.76</v>
+        <v>0.794</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.7439524644750251</v>
+        <v>0.7717528819109728</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>760</v>
+        <v>794</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I51" s="5" t="n">
         <v>60</v>
@@ -13755,12 +14013,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -13772,16 +14030,16 @@
         <v>2000</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.778</v>
+        <v>0.8015</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.7614406146917927</v>
+        <v>0.7855676169719019</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>1556</v>
+        <v>1603</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="I52" s="5" t="n">
         <v>60</v>
@@ -13790,12 +14048,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -13807,16 +14065,16 @@
         <v>1000</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.882</v>
+        <v>0.796</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.8710472576948233</v>
+        <v>0.7792340968020122</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>882</v>
+        <v>796</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I53" s="5" t="n">
         <v>60</v>
@@ -13825,12 +14083,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -13842,16 +14100,16 @@
         <v>1000</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.846</v>
+        <v>0.76</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>0.8354346192098669</v>
+        <v>0.7439524644750251</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>846</v>
+        <v>760</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I54" s="5" t="n">
         <v>60</v>
@@ -13860,12 +14118,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -13877,16 +14135,16 @@
         <v>2000</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0.864</v>
+        <v>0.778</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>0.8523414150627505</v>
+        <v>0.7614406146917927</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>1728</v>
+        <v>1556</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I55" s="5" t="n">
         <v>60</v>
@@ -13895,12 +14153,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -13912,13 +14170,13 @@
         <v>1000</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.858</v>
+        <v>0.882</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>0.846487306452871</v>
+        <v>0.8710472576948233</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>858</v>
+        <v>882</v>
       </c>
       <c r="H56" s="4" t="n">
         <v>0</v>
@@ -13930,12 +14188,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -13947,16 +14205,16 @@
         <v>1000</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.797</v>
+        <v>0.846</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>0.7859849948864567</v>
+        <v>0.8354346192098669</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>797</v>
+        <v>846</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I57" s="5" t="n">
         <v>60</v>
@@ -13965,12 +14223,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -13982,23 +14240,128 @@
         <v>2000</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0.8275</v>
+        <v>0.864</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>0.8155753958777252</v>
+        <v>0.8523414150627505</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>1655</v>
+        <v>1728</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I58" s="5" t="n">
         <v>60</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>0.846487306452871</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>858</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>0.7859849948864567</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>797</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>0.8275</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>0.8155753958777252</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>1655</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I58"/>
+  <autoFilter ref="A1:I61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14009,7 +14372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -14232,725 +14595,770 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
+          <t>local/laya-multilingual</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
+          <t>Laya Multilingual (mmBERT-base decision head, local)</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.706</v>
+        <v>0.794</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.546</v>
+        <v>0.423</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>373</v>
+        <v>247</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.373</v>
+        <v>0.247</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>205</v>
+        <v>151</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.205</v>
+        <v>0.151</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.089</v>
+        <v>0.055</v>
       </c>
       <c r="L5" t="n">
-        <v>333</v>
+        <v>547</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.333</v>
+        <v>0.547</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
+          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
         </is>
       </c>
       <c r="C6" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.724</v>
+        <v>0.706</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.546</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.377</v>
+        <v>0.373</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.195</v>
+        <v>0.205</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.081</v>
+        <v>0.089</v>
       </c>
       <c r="L6" t="n">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.347</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>local/qwen3.5-2b-q8-gguf</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Qwen3.5 2B (GGUF Q8_0, local)</t>
+          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.705</v>
+        <v>0.724</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>435</v>
+        <v>377</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.435</v>
+        <v>0.377</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.213</v>
+        <v>0.195</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.082</v>
+        <v>0.081</v>
       </c>
       <c r="L7" t="n">
-        <v>270</v>
+        <v>347</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.27</v>
+        <v>0.347</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>local/qwen3.5-4b-q4km-gguf</t>
+          <t>local/qwen3.5-2b-q8-gguf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Qwen3.5 4B (GGUF Q4_K_M, local)</t>
+          <t>Qwen3.5 2B (GGUF Q8_0, local)</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.835</v>
+        <v>0.705</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.776</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>692</v>
+        <v>435</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.435</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>108</v>
+        <v>213</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.108</v>
+        <v>0.213</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.057</v>
+        <v>0.082</v>
       </c>
       <c r="L8" t="n">
-        <v>143</v>
+        <v>270</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.143</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen3.5-4b-q4km-gguf</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen3.5 4B (GGUF Q4_K_M, local)</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.824</v>
+        <v>0.835</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.768</v>
+        <v>0.776</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>674</v>
+        <v>692</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.674</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.106</v>
+        <v>0.108</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.057</v>
       </c>
       <c r="L9" t="n">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.15</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C10" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.651</v>
+        <v>0.824</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.43</v>
+        <v>0.768</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>361</v>
+        <v>674</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.361</v>
+        <v>0.674</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.104</v>
+        <v>0.106</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>245</v>
+        <v>70</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.245</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>290</v>
+        <v>150</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.29</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.763</v>
+        <v>0.651</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.695</v>
+        <v>0.43</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>619</v>
+        <v>361</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.619</v>
+        <v>0.361</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.119</v>
+        <v>0.104</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>118</v>
+        <v>245</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.118</v>
+        <v>0.245</v>
       </c>
       <c r="L11" t="n">
-        <v>144</v>
+        <v>290</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.144</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.7</v>
+        <v>0.763</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.519</v>
+        <v>0.695</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>460</v>
+        <v>619</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.46</v>
+        <v>0.619</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.049</v>
+        <v>0.119</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>251</v>
+        <v>118</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.251</v>
+        <v>0.118</v>
       </c>
       <c r="L12" t="n">
-        <v>240</v>
+        <v>144</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.24</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.731</v>
+        <v>0.7</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.505</v>
+        <v>0.519</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>329</v>
+        <v>460</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.329</v>
+        <v>0.46</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>200</v>
+        <v>49</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.2</v>
+        <v>0.049</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>69</v>
+        <v>251</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.251</v>
       </c>
       <c r="L13" t="n">
-        <v>402</v>
+        <v>240</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.402</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.863</v>
+        <v>0.731</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.833</v>
+        <v>0.505</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>760</v>
+        <v>329</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.76</v>
+        <v>0.329</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.082</v>
+        <v>0.2</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.055</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>103</v>
+        <v>402</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.103</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.718</v>
+        <v>0.863</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.612</v>
+        <v>0.833</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>547</v>
+        <v>760</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.547</v>
+        <v>0.76</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.168</v>
+        <v>0.082</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.114</v>
+        <v>0.055</v>
       </c>
       <c r="L15" t="n">
-        <v>171</v>
+        <v>103</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.171</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.895</v>
+        <v>0.718</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.866</v>
+        <v>0.612</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>797</v>
+        <v>547</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.797</v>
+        <v>0.547</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>71</v>
+        <v>168</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.168</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.034</v>
+        <v>0.114</v>
       </c>
       <c r="L16" t="n">
-        <v>98</v>
+        <v>171</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.098</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.865</v>
+        <v>0.895</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.866</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>734</v>
+        <v>797</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.734</v>
+        <v>0.797</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.075</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.06</v>
+        <v>0.034</v>
       </c>
       <c r="L17" t="n">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.131</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.832</v>
+        <v>0.865</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.77</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>694</v>
+        <v>734</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.694</v>
+        <v>0.734</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.102</v>
+        <v>0.075</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.066</v>
+        <v>0.06</v>
       </c>
       <c r="L18" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.138</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.91</v>
+        <v>0.832</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.887</v>
+        <v>0.77</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>819</v>
+        <v>694</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.819</v>
+        <v>0.694</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.063</v>
+        <v>0.102</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.027</v>
+        <v>0.066</v>
       </c>
       <c r="L19" t="n">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.091</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D20" s="4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>819</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="L20" t="n">
+        <v>91</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>0.091</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D21" s="4" t="n">
         <v>0.867</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E21" s="4" t="n">
         <v>0.822</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F21" s="5" t="n">
         <v>761</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>0.761</v>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="H21" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="I20" s="4" t="n">
+      <c r="I21" s="4" t="n">
         <v>0.097</v>
       </c>
-      <c r="J20" s="5" t="n">
+      <c r="J21" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="K20" s="4" t="n">
+      <c r="K21" s="4" t="n">
         <v>0.036</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>106</v>
       </c>
-      <c r="M20" s="4" t="n">
+      <c r="M21" s="4" t="n">
         <v>0.106</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M20"/>
+  <autoFilter ref="A1:M21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results/benchmark_results.xlsx
+++ b/results/benchmark_results.xlsx
@@ -23,17 +23,17 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Legend'!$A$1:$D$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Leaderboard'!$A$1:$AL$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Leaderboard'!$A$1:$AL$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Summarization'!$A$1:$P$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Hallucination'!$A$1:$O$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Classification'!$A$1:$I$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'CrossLingual'!$A$1:$M$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Hallucination'!$A$1:$O$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Classification'!$A$1:$I$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'CrossLingual'!$A$1:$M$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'ClassificationModes'!$A$1:$K$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'SurfaceFacts'!$A$1:$L$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cost'!$A$1:$S$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Usage'!$A$1:$M$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cost'!$A$1:$S$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Usage'!$A$1:$M$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Judge'!$A$1:$A$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Runs'!$A$1:$T$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Runs'!$A$1:$T$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -480,7 +480,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09T22:57:20+00:00</t>
+          <t>2026-10-10T15:03:33+00:00</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -1224,22 +1224,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>microsoft/microsoft-decision-1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Microsoft Decision 1</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>0.02</v>
-      </c>
+        <v>0.042</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr"/>
       <c r="E11" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1248,17 +1246,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-16T03:10:41+00:00</t>
+          <t>2026-10-10T14:59:42+00:00</t>
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.07769180000000001</v>
+        <v>0</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.08999796</v>
+        <v>0.027402312</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.01189376</v>
+        <v>0.040912746</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
@@ -1267,22 +1265,22 @@
         <v>0</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.17958352</v>
+        <v>0.068315058</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.1795835200000001</v>
+        <v>0.06831505800000011</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.17958352</v>
+        <v>0.068315058</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.1795835200000001</v>
+        <v>0.06831505800000011</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.17958352</v>
+        <v>0.06831505800000001</v>
       </c>
       <c r="S11" t="b">
         <v>1</v>
@@ -1291,22 +1289,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1315,17 +1313,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-16T03:17:56+00:00</t>
+          <t>2026-09-16T03:10:41+00:00</t>
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.0385285</v>
+        <v>0.07769180000000001</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.0433295</v>
+        <v>0.08999796</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.00566052</v>
+        <v>0.01189376</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1334,22 +1332,22 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0.08751852</v>
+        <v>0.17958352</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.08751852</v>
+        <v>0.1795835200000001</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0.08751852</v>
+        <v>0.17958352</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.08751852</v>
+        <v>0.1795835200000001</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.08751852</v>
+        <v>0.17958352</v>
       </c>
       <c r="S12" t="b">
         <v>1</v>
@@ -1358,22 +1356,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1382,17 +1380,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-16T03:15:02+00:00</t>
+          <t>2026-09-16T03:17:56+00:00</t>
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.0582456</v>
+        <v>0.0385285</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.06753291</v>
+        <v>0.0433295</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.008405670000000001</v>
+        <v>0.00566052</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
@@ -1401,22 +1399,22 @@
         <v>0</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>0.13418418</v>
+        <v>0.08751852</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.1341841799999999</v>
+        <v>0.08751852</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>0.13418418</v>
+        <v>0.08751852</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.1341841799999999</v>
+        <v>0.08751852</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.13418418</v>
+        <v>0.08751852</v>
       </c>
       <c r="S13" t="b">
         <v>1</v>
@@ -1425,12 +1423,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
@@ -1440,7 +1438,7 @@
         <v>0.015</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.6</v>
+        <v>0.15</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1449,17 +1447,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-16T03:07:59+00:00</t>
+          <t>2026-09-16T03:15:02+00:00</t>
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.0802729125</v>
+        <v>0.0582456</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.0986139</v>
+        <v>0.06753291</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.017520885</v>
+        <v>0.008405670000000001</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0</v>
@@ -1468,46 +1466,46 @@
         <v>0</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>0.1964076975</v>
+        <v>0.13418418</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.1964076975000001</v>
+        <v>0.1341841799999999</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>0.1964076975</v>
+        <v>0.13418418</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.1964076975000001</v>
+        <v>0.1341841799999999</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.17912064</v>
+        <v>0.13418418</v>
       </c>
       <c r="S14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1516,17 +1514,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:30+00:00</t>
+          <t>2026-09-16T03:07:59+00:00</t>
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.0519185</v>
+        <v>0.0802729125</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.067397</v>
+        <v>0.0986139</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.0109598</v>
+        <v>0.017520885</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>0</v>
@@ -1535,43 +1533,43 @@
         <v>0</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.1964076975</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.1964076975000001</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.1964076975</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0.1302753</v>
+        <v>0.1964076975000001</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.1302753</v>
+        <v>0.17912064</v>
       </c>
       <c r="S15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.005</v>
+        <v>0.025</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0.4</v>
@@ -1583,17 +1581,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-16T04:40:49+00:00</t>
+          <t>2026-09-16T03:23:30+00:00</t>
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.08205585</v>
+        <v>0.0519185</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.1433661</v>
+        <v>0.067397</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.0474705</v>
+        <v>0.0109598</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>0</v>
@@ -1602,22 +1600,22 @@
         <v>0</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.27289245</v>
+        <v>0.1302753</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.2728924500000001</v>
+        <v>0.1302753</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.27289245</v>
+        <v>0.1302753</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.2728924500000001</v>
+        <v>0.1302753</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.27289245</v>
+        <v>0.1302753</v>
       </c>
       <c r="S16" t="b">
         <v>1</v>
@@ -1626,22 +1624,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1.25</v>
+        <v>0.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1650,17 +1648,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-16T03:20:07+00:00</t>
+          <t>2026-09-16T04:40:49+00:00</t>
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.1453735</v>
+        <v>0.08205585</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.1435934</v>
+        <v>0.1433661</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02710335</v>
+        <v>0.0474705</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>0</v>
@@ -1669,22 +1667,22 @@
         <v>0</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0.31607025</v>
+        <v>0.27289245</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.3160702499999996</v>
+        <v>0.2728924500000001</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>0.31607025</v>
+        <v>0.27289245</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.3160702499999996</v>
+        <v>0.2728924500000001</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.3160702500000001</v>
+        <v>0.27289245</v>
       </c>
       <c r="S17" t="b">
         <v>1</v>
@@ -1693,12 +1691,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -1708,7 +1706,7 @@
         <v>0.02</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1717,17 +1715,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-16T02:59:08+00:00</t>
+          <t>2026-09-16T03:20:07+00:00</t>
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.12600455</v>
+        <v>0.1453735</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.1584021</v>
+        <v>0.1435934</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.0262596</v>
+        <v>0.02710335</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
@@ -1736,46 +1734,46 @@
         <v>0</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0.31066625</v>
+        <v>0.31607025</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.3106662500000003</v>
+        <v>0.3160702499999996</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>0.31066625</v>
+        <v>0.31607025</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>0.3106662500000003</v>
+        <v>0.3160702499999996</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.2877202</v>
+        <v>0.3160702500000001</v>
       </c>
       <c r="S18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>openai/gpt-6-luna</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GPT-6 Luna</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1784,17 +1782,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-09T22:51:13+00:00</t>
+          <t>2026-09-16T02:59:08+00:00</t>
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.04079803</v>
+        <v>0.12600455</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.057590645</v>
+        <v>0.1584021</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.0120998</v>
+        <v>0.0262596</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>0</v>
@@ -1803,22 +1801,22 @@
         <v>0</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>0.110488475</v>
+        <v>0.31066625</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>0.1104884750000001</v>
+        <v>0.3106662500000003</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>0.110488475</v>
+        <v>0.31066625</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>0.1104884750000001</v>
+        <v>0.3106662500000003</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.1080722</v>
+        <v>0.2877202</v>
       </c>
       <c r="S19" t="b">
         <v>0</v>
@@ -1827,20 +1825,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-6-luna</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-6 Luna</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.04815</v>
-      </c>
-      <c r="D20" s="3" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0.01</v>
+      </c>
       <c r="E20" s="3" t="n">
-        <v>0.19305</v>
+        <v>0.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1849,17 +1849,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-16T03:34:40+00:00</t>
+          <t>2026-10-09T22:51:13+00:00</t>
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.04959875775</v>
+        <v>0.04079803</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.06309176505</v>
+        <v>0.057590645</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01054341345</v>
+        <v>0.0120998</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0</v>
@@ -1868,22 +1868,22 @@
         <v>0</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.12323393625</v>
+        <v>0.110488475</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.1232339362500001</v>
+        <v>0.1104884750000001</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.12323393625</v>
+        <v>0.110488475</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.1232339362500001</v>
+        <v>0.1104884750000001</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.07244949735</v>
+        <v>0.1080722</v>
       </c>
       <c r="S20" t="b">
         <v>0</v>
@@ -1892,22 +1892,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>0.006</v>
-      </c>
+        <v>0.04815</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="n">
-        <v>0.13</v>
+        <v>0.19305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1916,17 +1914,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-16T03:31:23+00:00</t>
+          <t>2026-09-16T03:34:40+00:00</t>
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.01445385</v>
+        <v>0.04959875775</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.01955122</v>
+        <v>0.06309176505</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.0039132</v>
+        <v>0.01054341345</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
@@ -1935,46 +1933,46 @@
         <v>0</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>0.03791827</v>
+        <v>0.12323393625</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0.03791826999999996</v>
+        <v>0.1232339362500001</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>0.03791827</v>
+        <v>0.12323393625</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0.03791826999999996</v>
+        <v>0.1232339362500001</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.03795787999999999</v>
+        <v>0.07244949735</v>
       </c>
       <c r="S21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.016</v>
+        <v>0.006</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>0.47</v>
+        <v>0.13</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1983,17 +1981,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-16T03:26:19+00:00</t>
+          <t>2026-09-16T03:31:23+00:00</t>
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.06590207000000001</v>
+        <v>0.01445385</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.068078582</v>
+        <v>0.01955122</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.013945102</v>
+        <v>0.0039132</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
@@ -2002,22 +2000,22 @@
         <v>0</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.03791827</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.03791826999999996</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.03791827</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.03791826999999996</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.148121674</v>
+        <v>0.03795787999999999</v>
       </c>
       <c r="S22" t="b">
         <v>1</v>
@@ -2026,72 +2024,139 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>qwen/qwen3.8-flash</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Qwen3.8 Flash</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>openrouter</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-09-16T03:26:19+00:00</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>0.06590207000000001</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>0.068078582</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>0.013945102</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>0.147925754</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>0.147925754</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>0.147925754</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.147925754</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>0.148121674</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>z-ai/glm-5.3-flash</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>GLM 5.3 Flash</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C24" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>0.02</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>0.3333</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>openrouter</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>2026-09-16T04:41:38+00:00</t>
         </is>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="H24" s="3" t="n">
         <v>0.0828101102</v>
       </c>
-      <c r="I23" s="3" t="n">
+      <c r="I24" s="3" t="n">
         <v>0.11700001578</v>
       </c>
-      <c r="J23" s="3" t="n">
+      <c r="J24" s="3" t="n">
         <v>0.0149070175</v>
       </c>
-      <c r="K23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="3" t="n">
+      <c r="K24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="n">
         <v>0.21471714348</v>
       </c>
-      <c r="N23" s="3" t="n">
+      <c r="N24" s="3" t="n">
         <v>0.2147171434799998</v>
       </c>
-      <c r="O23" s="3" t="n">
+      <c r="O24" s="3" t="n">
         <v>0.21471714348</v>
       </c>
-      <c r="P23" s="3" t="n">
+      <c r="P24" s="3" t="n">
         <v>0.2147171434799998</v>
       </c>
-      <c r="Q23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="4" t="n">
+      <c r="Q24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="4" t="n">
         <v>0.1606481436</v>
       </c>
-      <c r="S23" t="b">
+      <c r="S24" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S23"/>
+  <autoFilter ref="A1:S24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2102,7 +2167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -2595,57 +2660,57 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>microsoft/microsoft-decision-1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Microsoft Decision 1</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1300</v>
+        <v>2800</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>1092316</v>
+        <v>1626549</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>295936</v>
+        <v>0</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>71944</v>
+        <v>2800</v>
       </c>
       <c r="H11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>1164260</v>
+        <v>1629349</v>
       </c>
       <c r="J11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>1300</v>
+        <v>2800</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>1300</v>
+        <v>2800</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>1300</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
@@ -2655,19 +2720,19 @@
         <v>1092316</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>318592</v>
+        <v>295936</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>69602</v>
+        <v>71944</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>1161918</v>
+        <v>1164260</v>
       </c>
       <c r="J12" s="5" t="n">
         <v>0</v>
@@ -2685,12 +2750,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
@@ -2700,19 +2765,19 @@
         <v>1092316</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>299392</v>
+        <v>318592</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>71698</v>
+        <v>69602</v>
       </c>
       <c r="H13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>1164014</v>
+        <v>1161918</v>
       </c>
       <c r="J13" s="5" t="n">
         <v>0</v>
@@ -2730,34 +2795,34 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1107916</v>
+        <v>1092316</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>183856</v>
+        <v>299392</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>62923</v>
+        <v>71698</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>1170839</v>
+        <v>1164014</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>0</v>
@@ -2775,34 +2840,34 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1108245</v>
+        <v>1107916</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>36224</v>
+        <v>183856</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>55419</v>
+        <v>62923</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>1163664</v>
+        <v>1170839</v>
       </c>
       <c r="J15" s="5" t="n">
         <v>0</v>
@@ -2820,34 +2885,34 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1106945</v>
+        <v>1108245</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>40320</v>
+        <v>36224</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>548399</v>
+        <v>55419</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>433920</v>
+        <v>0</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>1655344</v>
+        <v>1163664</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>0</v>
@@ -2865,12 +2930,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
@@ -2880,19 +2945,19 @@
         <v>1106945</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0</v>
+        <v>40320</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>75745</v>
+        <v>548399</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0</v>
+        <v>433920</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>1182690</v>
+        <v>1655344</v>
       </c>
       <c r="J17" s="5" t="n">
         <v>0</v>
@@ -2910,12 +2975,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
@@ -2928,16 +2993,16 @@
         <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>458921</v>
+        <v>0</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>55276</v>
+        <v>75745</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>1162221</v>
+        <v>1182690</v>
       </c>
       <c r="J18" s="5" t="n">
         <v>0</v>
@@ -2955,12 +3020,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>openai/gpt-6-luna</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GPT-6 Luna</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -2970,19 +3035,19 @@
         <v>1106945</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>362270</v>
+        <v>0</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>96651</v>
+        <v>458921</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>59964</v>
+        <v>55276</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>1166909</v>
+        <v>1162221</v>
       </c>
       <c r="J19" s="5" t="n">
         <v>0</v>
@@ -3000,34 +3065,34 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-6-luna</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-6 Luna</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>1213604</v>
+        <v>1106945</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>102934</v>
+        <v>362270</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0</v>
+        <v>96651</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>72595</v>
+        <v>59964</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>1286199</v>
+        <v>1166909</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>0</v>
@@ -3045,34 +3110,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1061596</v>
+        <v>1213604</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>24960</v>
+        <v>102934</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>51608</v>
+        <v>72595</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>1113204</v>
+        <v>1286199</v>
       </c>
       <c r="J21" s="5" t="n">
         <v>0</v>
@@ -3084,18 +3149,18 @@
         <v>1300</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>1307</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -3105,19 +3170,19 @@
         <v>1061596</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>265984</v>
+        <v>24960</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>52179</v>
+        <v>51608</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>1113775</v>
+        <v>1113204</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>0</v>
@@ -3129,40 +3194,40 @@
         <v>1300</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>1314</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>1300</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1293055</v>
+        <v>1061596</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>104384</v>
+        <v>265984</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>119092</v>
+        <v>52179</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>35855</v>
+        <v>0</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>1412147</v>
+        <v>1113775</v>
       </c>
       <c r="J23" s="5" t="n">
         <v>0</v>
@@ -3174,11 +3239,56 @@
         <v>1300</v>
       </c>
       <c r="M23" s="5" t="n">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
         <v>1300</v>
       </c>
+      <c r="D24" s="5" t="n">
+        <v>1293055</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>104384</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>119092</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>35855</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>1412147</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>1300</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M23"/>
+  <autoFilter ref="A1:M24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3214,7 +3324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T23"/>
+  <dimension ref="A1:T24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -3235,7 +3345,7 @@
     <col width="46" customWidth="1" min="16" max="16"/>
     <col width="46" customWidth="1" min="17" max="17"/>
     <col width="46" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="46" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
@@ -4100,7 +4210,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>microsoft/microsoft-decision-1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4110,17 +4220,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>run-20260916T031043-60c30b6a</t>
+          <t>run-20261010T145945-08959870</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:15:02+00:00</t>
+          <t>2026-10-10T15:03:33+00:00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-16T03:10:43+00:00</t>
+          <t>2026-10-10T14:59:45+00:00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4128,8 +4238,14 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>31ace82a3b536d621fd8d80b791759bd37c913b3</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -4137,7 +4253,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>summarization, hallucination, classification</t>
+          <t>hallucination, classification</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4146,7 +4262,7 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>3200</v>
+        <v>2800</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -4174,13 +4290,17 @@
           <t>1bebd7a4e6cab622b3a85e6f856e019c9459100085c08ca38ccec107d5e3ec21</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>summarization: decision models choose among fixed options and cannot generate a summary</t>
+        </is>
+      </c>
       <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4190,17 +4310,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>run-20260916T031757-6f0019bc</t>
+          <t>run-20260916T031043-60c30b6a</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:20:07+00:00</t>
+          <t>2026-09-16T03:15:02+00:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-16T03:17:57+00:00</t>
+          <t>2026-09-16T03:10:43+00:00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -4260,7 +4380,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4270,17 +4390,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>run-20260916T031504-7b84cf7d</t>
+          <t>run-20260916T031757-6f0019bc</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:17:56+00:00</t>
+          <t>2026-09-16T03:20:07+00:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-16T03:15:04+00:00</t>
+          <t>2026-09-16T03:17:57+00:00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4340,7 +4460,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4350,17 +4470,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>run-20260916T030801-577d0830</t>
+          <t>run-20260916T031504-7b84cf7d</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:10:41+00:00</t>
+          <t>2026-09-16T03:17:56+00:00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-16T03:08:01+00:00</t>
+          <t>2026-09-16T03:15:04+00:00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4420,7 +4540,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4430,17 +4550,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>run-20260916T032332-5a24afb2</t>
+          <t>run-20260916T030801-577d0830</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:26:19+00:00</t>
+          <t>2026-09-16T03:10:41+00:00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:32+00:00</t>
+          <t>2026-09-16T03:08:01+00:00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4500,7 +4620,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4510,17 +4630,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>run-20260916T044051-1b0d71da</t>
+          <t>run-20260916T032332-5a24afb2</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T04:51:21+00:00</t>
+          <t>2026-09-16T03:26:19+00:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-16T04:40:51+00:00</t>
+          <t>2026-09-16T03:23:32+00:00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4528,14 +4648,8 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -4586,7 +4700,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4596,17 +4710,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>run-20260916T032009-aca77564</t>
+          <t>run-20260916T044051-1b0d71da</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:28+00:00</t>
+          <t>2026-09-16T04:51:21+00:00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-16T03:20:09+00:00</t>
+          <t>2026-09-16T04:40:51+00:00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -4614,8 +4728,14 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -4666,7 +4786,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4676,17 +4796,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>run-20260916T025909-be4eb782</t>
+          <t>run-20260916T032009-aca77564</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:02:43+00:00</t>
+          <t>2026-09-16T03:23:28+00:00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-09-16T02:59:09+00:00</t>
+          <t>2026-09-16T03:20:09+00:00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -4746,7 +4866,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>openai/gpt-6-luna</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4756,17 +4876,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>run-20261009T225115-ca0eb33f</t>
+          <t>run-20260916T025909-be4eb782</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T22:55:12+00:00</t>
+          <t>2026-09-16T03:02:43+00:00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-09T22:51:15+00:00</t>
+          <t>2026-09-16T02:59:09+00:00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4774,14 +4894,8 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>083c5f3ae0934563cc67c44ddbedac9fad21a483</t>
-        </is>
-      </c>
-      <c r="H19" t="b">
-        <v>1</v>
-      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -4832,7 +4946,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-6-luna</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4842,17 +4956,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>run-20260916T033441-93cb685e</t>
+          <t>run-20261009T225115-ca0eb33f</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:43:30+00:00</t>
+          <t>2026-10-09T22:55:12+00:00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-09-16T03:34:41+00:00</t>
+          <t>2026-10-09T22:51:15+00:00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4860,8 +4974,14 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>083c5f3ae0934563cc67c44ddbedac9fad21a483</t>
+        </is>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -4912,7 +5032,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4922,17 +5042,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>run-20260916T033125-8730c140</t>
+          <t>run-20260916T033441-93cb685e</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:34:40+00:00</t>
+          <t>2026-09-16T03:43:30+00:00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-09-16T03:31:25+00:00</t>
+          <t>2026-09-16T03:34:41+00:00</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4992,7 +5112,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5002,17 +5122,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>run-20260916T032621-2ec5c283</t>
+          <t>run-20260916T033125-8730c140</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T03:31:23+00:00</t>
+          <t>2026-09-16T03:34:40+00:00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-09-16T03:26:21+00:00</t>
+          <t>2026-09-16T03:31:25+00:00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -5072,7 +5192,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5082,17 +5202,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>run-20260916T044139-f5eda9f3</t>
+          <t>run-20260916T032621-2ec5c283</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16T04:51:13+00:00</t>
+          <t>2026-09-16T03:31:23+00:00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-09-16T04:41:39+00:00</t>
+          <t>2026-09-16T03:26:21+00:00</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -5100,14 +5220,8 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
-        </is>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
-      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>3.12.3</t>
@@ -5155,8 +5269,94 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>run-20260916T044139-f5eda9f3</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16T04:51:13+00:00</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-09-16T04:41:39+00:00</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>8d709c8d679a9226e30d04c8bb8a4757529688a6</t>
+        </is>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3.12.3</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>summarization, hallucination, classification</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>en, ko</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>3200</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>cbe6fb9c14d4b2b12e690d6565e05bcf861c5db26cc56aef45e3e3810f67b298</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0135c4f4499e35dcde7855ad6afe33e333ebf2bca519a20b81257dc39150cd62</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>21debf696ed02ef001638142e2864a1bb58be409f88d8c86ad36e067ee609ca5</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>b49d914db700703584e2388f602808314a59c9e088a20f02e670ead58141fa96</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1bebd7a4e6cab622b3a85e6f856e019c9459100085c08ca38ccec107d5e3ec21</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T23"/>
+  <autoFilter ref="A1:T24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6486,7 +6686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL23"/>
+  <dimension ref="A1:AL24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -6724,17 +6924,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>google/gemini-3.1-flash-lite</t>
+          <t>microsoft/microsoft-decision-1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Flash-Lite</t>
+          <t>Microsoft Decision 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>microsoft</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -6748,14 +6948,12 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.25</v>
+        <v>0.042</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>0.025</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>openrouter</t>
@@ -6763,40 +6961,28 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-16T03:02:43+00:00</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>0.180021324735549</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.221024648052918</v>
-      </c>
-      <c r="M2" t="n">
-        <v>28.32632418475155</v>
-      </c>
-      <c r="N2" t="n">
-        <v>13.84056050921727</v>
-      </c>
+          <t>2026-10-10T14:59:42+00:00</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" s="4" t="n">
-        <v>0.8389154704944178</v>
-      </c>
-      <c r="R2" s="4" t="n">
-        <v>0.964349376114082</v>
-      </c>
+      <c r="Q2" s="4" t="inlineStr"/>
+      <c r="R2" s="4" t="inlineStr"/>
       <c r="S2" s="4" t="n">
-        <v>0.7183462532299741</v>
+        <v>0.7463414634146341</v>
       </c>
       <c r="T2" s="4" t="n">
-        <v>0.6112759643916914</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.7275</v>
+        <v>0.74</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.6725</v>
+        <v>0.65</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -6804,31 +6990,31 @@
         </is>
       </c>
       <c r="X2" t="n">
-        <v>0.891</v>
+        <v>0.92</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.87</v>
+        <v>0.887</v>
       </c>
       <c r="Z2" s="4" t="n">
-        <v>0.8762568261606758</v>
+        <v>0.9079095915191101</v>
       </c>
       <c r="AA2" s="4" t="n">
-        <v>0.8425254254032213</v>
+        <v>0.8758736466373309</v>
       </c>
       <c r="AB2" s="4" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.9035</v>
       </c>
       <c r="AC2" s="4" t="n">
-        <v>0.8564742197577885</v>
+        <v>0.8919585061895788</v>
       </c>
       <c r="AD2" s="4" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.927</v>
       </c>
       <c r="AE2" s="5" t="n">
-        <v>1098022</v>
+        <v>1626549</v>
       </c>
       <c r="AF2" s="5" t="n">
-        <v>55664</v>
+        <v>2800</v>
       </c>
       <c r="AG2" s="5" t="n">
         <v>0</v>
@@ -6837,32 +7023,32 @@
         <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>0.3580015</v>
+        <v>0.068315058</v>
       </c>
       <c r="AJ2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>0.3334132499999996</v>
+        <v>0.06831505800000011</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>0.02458824999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>google/gemini-3.1-flash-lite</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Gemini 3.1 Flash-Lite</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>google</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -6876,13 +7062,13 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.47</v>
+        <v>1.5</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.016</v>
+        <v>0.025</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -6891,40 +7077,40 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-16T03:26:19+00:00</t>
+          <t>2026-09-16T03:02:43+00:00</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.1621429745937464</v>
+        <v>0.180021324735549</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2283869866974114</v>
+        <v>0.221024648052918</v>
       </c>
       <c r="M3" t="n">
-        <v>26.68302009498116</v>
+        <v>28.32632418475155</v>
       </c>
       <c r="N3" t="n">
-        <v>14.15140430658347</v>
+        <v>13.84056050921727</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" s="4" t="n">
-        <v>0.8794037940379403</v>
+        <v>0.8389154704944178</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>0.9405594405594405</v>
+        <v>0.964349376114082</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.7596899224806202</v>
+        <v>0.7183462532299741</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>0.5623003194888179</v>
+        <v>0.6112759643916914</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.7675</v>
+        <v>0.7275</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.6575</v>
+        <v>0.6725</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -6932,65 +7118,65 @@
         </is>
       </c>
       <c r="X3" t="n">
-        <v>0.882</v>
+        <v>0.891</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.846</v>
+        <v>0.87</v>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>0.8710472576948233</v>
+        <v>0.8762568261606758</v>
       </c>
       <c r="AA3" s="4" t="n">
-        <v>0.8354346192098669</v>
+        <v>0.8425254254032213</v>
       </c>
       <c r="AB3" s="4" t="n">
-        <v>0.864</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="AC3" s="4" t="n">
-        <v>0.8523414150627505</v>
+        <v>0.8564742197577885</v>
       </c>
       <c r="AD3" s="4" t="n">
-        <v>0.91</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="AE3" s="5" t="n">
-        <v>1061596</v>
+        <v>1098022</v>
       </c>
       <c r="AF3" s="5" t="n">
-        <v>52179</v>
+        <v>55664</v>
       </c>
       <c r="AG3" s="5" t="n">
-        <v>265984</v>
+        <v>0</v>
       </c>
       <c r="AH3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.3580015</v>
       </c>
       <c r="AJ3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>0.147925754</v>
+        <v>0.3334132499999996</v>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>0</v>
+        <v>0.02458824999999998</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>openai/gpt-6-luna</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GPT-6 Luna</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -7004,13 +7190,13 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -7019,40 +7205,40 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-10-09T22:51:13+00:00</t>
+          <t>2026-09-16T03:26:19+00:00</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.1527476518884819</v>
+        <v>0.1621429745937464</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2171848590521927</v>
+        <v>0.2283869866974114</v>
       </c>
       <c r="M4" t="n">
-        <v>25.93513909592676</v>
+        <v>26.68302009498116</v>
       </c>
       <c r="N4" t="n">
-        <v>12.83087534440352</v>
+        <v>14.15140430658347</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" s="4" t="n">
-        <v>0.925974025974026</v>
+        <v>0.8794037940379403</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>0.9517241379310345</v>
+        <v>0.9405594405594405</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.7272727272727272</v>
+        <v>0.7596899224806202</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>0.6174142480211081</v>
+        <v>0.5623003194888179</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>0.7</v>
+        <v>0.7675</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.6375</v>
+        <v>0.6575</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -7060,46 +7246,46 @@
         </is>
       </c>
       <c r="X4" t="n">
-        <v>0.863</v>
+        <v>0.882</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.839</v>
+        <v>0.846</v>
       </c>
       <c r="Z4" s="4" t="n">
-        <v>0.8453007221886907</v>
+        <v>0.8710472576948233</v>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>0.8091186705197505</v>
+        <v>0.8354346192098669</v>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>0.851</v>
+        <v>0.864</v>
       </c>
       <c r="AC4" s="4" t="n">
-        <v>0.829884804655604</v>
+        <v>0.8523414150627505</v>
       </c>
       <c r="AD4" s="4" t="n">
-        <v>0.902</v>
+        <v>0.91</v>
       </c>
       <c r="AE4" s="5" t="n">
-        <v>1106945</v>
+        <v>1061596</v>
       </c>
       <c r="AF4" s="5" t="n">
-        <v>59964</v>
+        <v>52179</v>
       </c>
       <c r="AG4" s="5" t="n">
-        <v>362270</v>
+        <v>265984</v>
       </c>
       <c r="AH4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>0.110488475</v>
+        <v>0.147925754</v>
       </c>
       <c r="AJ4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>0.1104884750000001</v>
+        <v>0.147925754</v>
       </c>
       <c r="AL4" s="3" t="n">
         <v>0</v>
@@ -7108,12 +7294,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-6-luna</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-6 Luna</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -7132,13 +7318,13 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -7147,40 +7333,40 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-16T02:59:08+00:00</t>
+          <t>2026-10-09T22:51:13+00:00</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.1599680545649344</v>
+        <v>0.1527476518884819</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2296438059429992</v>
+        <v>0.2171848590521927</v>
       </c>
       <c r="M5" t="n">
-        <v>26.76607327189645</v>
+        <v>25.93513909592676</v>
       </c>
       <c r="N5" t="n">
-        <v>13.96081188606404</v>
+        <v>12.83087534440352</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" s="4" t="n">
-        <v>0.9235668789808917</v>
+        <v>0.925974025974026</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0.9401574803149606</v>
+        <v>0.9517241379310345</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.748129675810474</v>
+        <v>0.7272727272727272</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>0.6520547945205479</v>
+        <v>0.6174142480211081</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>0.6825</v>
+        <v>0.6375</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -7188,46 +7374,46 @@
         </is>
       </c>
       <c r="X5" t="n">
-        <v>0.868</v>
+        <v>0.863</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.831</v>
+        <v>0.839</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>0.8492172170319239</v>
+        <v>0.8453007221886907</v>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>0.8000988567676002</v>
+        <v>0.8091186705197505</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>0.8495</v>
+        <v>0.851</v>
       </c>
       <c r="AC5" s="4" t="n">
-        <v>0.8278820044607954</v>
+        <v>0.829884804655604</v>
       </c>
       <c r="AD5" s="4" t="n">
-        <v>0.895</v>
+        <v>0.902</v>
       </c>
       <c r="AE5" s="5" t="n">
         <v>1106945</v>
       </c>
       <c r="AF5" s="5" t="n">
-        <v>55276</v>
+        <v>59964</v>
       </c>
       <c r="AG5" s="5" t="n">
-        <v>0</v>
+        <v>362270</v>
       </c>
       <c r="AH5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>0.31066625</v>
+        <v>0.110488475</v>
       </c>
       <c r="AJ5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>0.3106662500000003</v>
+        <v>0.1104884750000001</v>
       </c>
       <c r="AL5" s="3" t="n">
         <v>0</v>
@@ -7236,17 +7422,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>google/gemini-2.5-flash-lite</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gemini 2.5 Flash-Lite</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7260,13 +7446,13 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -7275,40 +7461,40 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-16T03:05:27+00:00</t>
+          <t>2026-09-16T02:59:08+00:00</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.1624008768665497</v>
+        <v>0.1599680545649344</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2286708213618012</v>
+        <v>0.2296438059429992</v>
       </c>
       <c r="M6" t="n">
-        <v>25.83220416940711</v>
+        <v>26.76607327189645</v>
       </c>
       <c r="N6" t="n">
-        <v>13.80053671434364</v>
+        <v>13.96081188606404</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" s="4" t="n">
-        <v>0.9100877192982456</v>
+        <v>0.9235668789808917</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.9710144927536232</v>
+        <v>0.9401574803149606</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.6476190476190476</v>
+        <v>0.748129675810474</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.5830721003134797</v>
+        <v>0.6520547945205479</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.7225</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.6675</v>
+        <v>0.6825</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -7316,31 +7502,31 @@
         </is>
       </c>
       <c r="X6" t="n">
-        <v>0.843</v>
+        <v>0.868</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.823</v>
+        <v>0.831</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.8340438470244677</v>
+        <v>0.8492172170319239</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>0.8081048779503196</v>
+        <v>0.8000988567676002</v>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>0.833</v>
+        <v>0.8495</v>
       </c>
       <c r="AC6" s="4" t="n">
-        <v>0.8191126626634225</v>
+        <v>0.8278820044607954</v>
       </c>
       <c r="AD6" s="4" t="n">
-        <v>0.886</v>
+        <v>0.895</v>
       </c>
       <c r="AE6" s="5" t="n">
-        <v>1097914</v>
+        <v>1106945</v>
       </c>
       <c r="AF6" s="5" t="n">
-        <v>54986</v>
+        <v>55276</v>
       </c>
       <c r="AG6" s="5" t="n">
         <v>0</v>
@@ -7349,13 +7535,13 @@
         <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>0.1317858</v>
+        <v>0.31066625</v>
       </c>
       <c r="AJ6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>0.1317858</v>
+        <v>0.3106662500000003</v>
       </c>
       <c r="AL6" s="3" t="n">
         <v>0</v>
@@ -7364,17 +7550,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>google/gemini-2.5-flash-lite</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>Gemini 2.5 Flash-Lite</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>google</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -7388,13 +7574,13 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -7403,40 +7589,40 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-16T04:40:49+00:00</t>
+          <t>2026-09-16T03:05:27+00:00</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.1299020365576643</v>
+        <v>0.1624008768665497</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1992896265281343</v>
+        <v>0.2286708213618012</v>
       </c>
       <c r="M7" t="n">
-        <v>23.01138546667206</v>
+        <v>25.83220416940711</v>
       </c>
       <c r="N7" t="n">
-        <v>11.48522300950568</v>
+        <v>13.80053671434364</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" s="4" t="n">
-        <v>0.949200376293509</v>
+        <v>0.9100877192982456</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.9549738219895288</v>
+        <v>0.9710144927536232</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.6814814814814814</v>
+        <v>0.6476190476190476</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.328125</v>
+        <v>0.5830721003134797</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.6775</v>
+        <v>0.7225</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.57</v>
+        <v>0.6675</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -7444,46 +7630,46 @@
         </is>
       </c>
       <c r="X7" t="n">
-        <v>0.842</v>
+        <v>0.843</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.823</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.8314865753296514</v>
+        <v>0.8340438470244677</v>
       </c>
       <c r="AA7" s="4" t="n">
-        <v>0.8034449936517111</v>
+        <v>0.8081048779503196</v>
       </c>
       <c r="AB7" s="4" t="n">
-        <v>0.8285</v>
+        <v>0.833</v>
       </c>
       <c r="AC7" s="4" t="n">
-        <v>0.8179267929293625</v>
+        <v>0.8191126626634225</v>
       </c>
       <c r="AD7" s="4" t="n">
-        <v>0.863</v>
+        <v>0.886</v>
       </c>
       <c r="AE7" s="5" t="n">
-        <v>1106945</v>
+        <v>1097914</v>
       </c>
       <c r="AF7" s="5" t="n">
-        <v>548399</v>
+        <v>54986</v>
       </c>
       <c r="AG7" s="5" t="n">
-        <v>40320</v>
+        <v>0</v>
       </c>
       <c r="AH7" s="5" t="n">
-        <v>433920</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>0.27289245</v>
+        <v>0.1317858</v>
       </c>
       <c r="AJ7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>0.2728924500000001</v>
+        <v>0.1317858</v>
       </c>
       <c r="AL7" s="3" t="n">
         <v>0</v>
@@ -7492,17 +7678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>z-ai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7516,13 +7702,13 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.3333</v>
+        <v>0.4</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -7531,40 +7717,40 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-16T04:41:38+00:00</t>
+          <t>2026-09-16T04:40:49+00:00</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.1442957203978096</v>
+        <v>0.1299020365576643</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2059639679861038</v>
+        <v>0.1992896265281343</v>
       </c>
       <c r="M8" t="n">
-        <v>24.60010668803035</v>
+        <v>23.01138546667206</v>
       </c>
       <c r="N8" t="n">
-        <v>13.49752283326942</v>
+        <v>11.48522300950568</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" s="4" t="n">
-        <v>0.9221978021978022</v>
+        <v>0.949200376293509</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.9633928571428572</v>
+        <v>0.9549738219895288</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.72544080604534</v>
+        <v>0.6814814814814814</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.5555555555555557</v>
+        <v>0.328125</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.7275</v>
+        <v>0.6775</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -7572,46 +7758,46 @@
         </is>
       </c>
       <c r="X8" t="n">
-        <v>0.858</v>
+        <v>0.842</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.797</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>0.846487306452871</v>
+        <v>0.8314865753296514</v>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>0.7859849948864567</v>
+        <v>0.8034449936517111</v>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>0.8275</v>
+        <v>0.8285</v>
       </c>
       <c r="AC8" s="4" t="n">
-        <v>0.8155753958777252</v>
+        <v>0.8179267929293625</v>
       </c>
       <c r="AD8" s="4" t="n">
-        <v>0.867</v>
+        <v>0.863</v>
       </c>
       <c r="AE8" s="5" t="n">
-        <v>1293055</v>
+        <v>1106945</v>
       </c>
       <c r="AF8" s="5" t="n">
-        <v>119092</v>
+        <v>548399</v>
       </c>
       <c r="AG8" s="5" t="n">
-        <v>104384</v>
+        <v>40320</v>
       </c>
       <c r="AH8" s="5" t="n">
-        <v>35855</v>
+        <v>433920</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>0.21471714348</v>
+        <v>0.27289245</v>
       </c>
       <c r="AJ8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>0.2147171434799998</v>
+        <v>0.2728924500000001</v>
       </c>
       <c r="AL8" s="3" t="n">
         <v>0</v>
@@ -7620,17 +7806,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>deepseek/deepseek-v4-flash-0731</t>
+          <t>z-ai/glm-5.3-flash</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Flash 0731</t>
+          <t>GLM 5.3 Flash</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>deepseek</t>
+          <t>z-ai</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7644,13 +7830,13 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.055</v>
+        <v>0.1</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.11</v>
+        <v>0.3333</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.011</v>
+        <v>0.02</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -7659,40 +7845,40 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-16T03:43:32+00:00</t>
+          <t>2026-09-16T04:41:38+00:00</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.1602129689146955</v>
+        <v>0.1442957203978096</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2187402179219718</v>
+        <v>0.2059639679861038</v>
       </c>
       <c r="M9" t="n">
-        <v>26.38968843606158</v>
+        <v>24.60010668803035</v>
       </c>
       <c r="N9" t="n">
-        <v>13.34734148800115</v>
+        <v>13.49752283326942</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" s="4" t="n">
-        <v>0.8983156581409857</v>
+        <v>0.9221978021978022</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.958904109589041</v>
+        <v>0.9633928571428572</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.7204030226700252</v>
+        <v>0.72544080604534</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.6525821596244131</v>
+        <v>0.5555555555555557</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.7225</v>
+        <v>0.7275</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -7700,46 +7886,46 @@
         </is>
       </c>
       <c r="X9" t="n">
-        <v>0.803</v>
+        <v>0.858</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.802</v>
+        <v>0.797</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.7737251717218584</v>
+        <v>0.846487306452871</v>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>0.7760490357248214</v>
+        <v>0.7859849948864567</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>0.8025</v>
+        <v>0.8275</v>
       </c>
       <c r="AC9" s="4" t="n">
-        <v>0.7750244596849166</v>
+        <v>0.8155753958777252</v>
       </c>
       <c r="AD9" s="4" t="n">
-        <v>0.851</v>
+        <v>0.867</v>
       </c>
       <c r="AE9" s="5" t="n">
-        <v>1190712</v>
+        <v>1293055</v>
       </c>
       <c r="AF9" s="5" t="n">
-        <v>63519</v>
+        <v>119092</v>
       </c>
       <c r="AG9" s="5" t="n">
-        <v>369477</v>
+        <v>104384</v>
       </c>
       <c r="AH9" s="5" t="n">
-        <v>0</v>
+        <v>35855</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>0.087699192003</v>
+        <v>0.21471714348</v>
       </c>
       <c r="AJ9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>0.08769919200300014</v>
+        <v>0.2147171434799998</v>
       </c>
       <c r="AL9" s="3" t="n">
         <v>0</v>
@@ -7748,17 +7934,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>deepseek/deepseek-v4-flash-0731</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>DeepSeek V4 Flash 0731</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -7772,12 +7958,14 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.04815</v>
+        <v>0.055</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.19305</v>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
+        <v>0.11</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0.011</v>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>openrouter</t>
@@ -7785,40 +7973,40 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-16T03:34:40+00:00</t>
+          <t>2026-09-16T03:43:32+00:00</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.1416464777859414</v>
+        <v>0.1602129689146955</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2093037662697218</v>
+        <v>0.2187402179219718</v>
       </c>
       <c r="M10" t="n">
-        <v>24.38575174114155</v>
+        <v>26.38968843606158</v>
       </c>
       <c r="N10" t="n">
-        <v>12.78420991940304</v>
+        <v>13.34734148800115</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" s="4" t="n">
-        <v>0.9091375770020534</v>
+        <v>0.8983156581409857</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.9739027283511269</v>
+        <v>0.958904109589041</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.6089743589743589</v>
+        <v>0.7204030226700252</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.4191176470588235</v>
+        <v>0.6525821596244131</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.695</v>
+        <v>0.7225</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.605</v>
+        <v>0.63</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -7826,46 +8014,46 @@
         </is>
       </c>
       <c r="X10" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.803</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.794</v>
+        <v>0.802</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.7992131261387427</v>
+        <v>0.7737251717218584</v>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>0.7717528819109728</v>
+        <v>0.7760490357248214</v>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>0.8015</v>
+        <v>0.8025</v>
       </c>
       <c r="AC10" s="4" t="n">
-        <v>0.7855676169719019</v>
+        <v>0.7750244596849166</v>
       </c>
       <c r="AD10" s="4" t="n">
-        <v>0.865</v>
+        <v>0.851</v>
       </c>
       <c r="AE10" s="5" t="n">
-        <v>1213604</v>
+        <v>1190712</v>
       </c>
       <c r="AF10" s="5" t="n">
-        <v>72595</v>
+        <v>63519</v>
       </c>
       <c r="AG10" s="5" t="n">
-        <v>102934</v>
+        <v>369477</v>
       </c>
       <c r="AH10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>0.12323393625</v>
+        <v>0.087699192003</v>
       </c>
       <c r="AJ10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>0.1232339362500001</v>
+        <v>0.08769919200300014</v>
       </c>
       <c r="AL10" s="3" t="n">
         <v>0</v>
@@ -7874,12 +8062,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -7898,14 +8086,12 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.03</v>
+        <v>0.04815</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>0.006</v>
-      </c>
+        <v>0.19305</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>openrouter</t>
@@ -7913,40 +8099,40 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-16T03:31:23+00:00</t>
+          <t>2026-09-16T03:34:40+00:00</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0.1608350962342315</v>
+        <v>0.1416464777859414</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2302580020788956</v>
+        <v>0.2093037662697218</v>
       </c>
       <c r="M11" t="n">
-        <v>26.04951109641535</v>
+        <v>24.38575174114155</v>
       </c>
       <c r="N11" t="n">
-        <v>13.75572799407668</v>
+        <v>12.78420991940304</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" s="4" t="n">
-        <v>0.8816067653276956</v>
+        <v>0.9091375770020534</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.947463768115942</v>
+        <v>0.9739027283511269</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.6589595375722543</v>
+        <v>0.6089743589743589</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.5407166123778501</v>
+        <v>0.4191176470588235</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.705</v>
+        <v>0.695</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.6475</v>
+        <v>0.605</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -7954,46 +8140,46 @@
         </is>
       </c>
       <c r="X11" t="n">
-        <v>0.796</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.76</v>
+        <v>0.794</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.7792340968020122</v>
+        <v>0.7992131261387427</v>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>0.7439524644750251</v>
+        <v>0.7717528819109728</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>0.778</v>
+        <v>0.8015</v>
       </c>
       <c r="AC11" s="4" t="n">
-        <v>0.7614406146917927</v>
+        <v>0.7855676169719019</v>
       </c>
       <c r="AD11" s="4" t="n">
-        <v>0.832</v>
+        <v>0.865</v>
       </c>
       <c r="AE11" s="5" t="n">
-        <v>1061596</v>
+        <v>1213604</v>
       </c>
       <c r="AF11" s="5" t="n">
-        <v>51608</v>
+        <v>72595</v>
       </c>
       <c r="AG11" s="5" t="n">
-        <v>24960</v>
+        <v>102934</v>
       </c>
       <c r="AH11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>0.03791827</v>
+        <v>0.12323393625</v>
       </c>
       <c r="AJ11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>0.03791826999999996</v>
+        <v>0.1232339362500001</v>
       </c>
       <c r="AL11" s="3" t="n">
         <v>0</v>
@@ -8002,12 +8188,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>local/qwen3.5-4b-q4km-gguf</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qwen3.5 4B (GGUF Q4_K_M, local)</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -8017,7 +8203,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -8025,89 +8211,127 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0.006</v>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>config</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>2026-09-16T03:31:23+00:00</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0.1608350962342315</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2302580020788956</v>
+      </c>
+      <c r="M12" t="n">
+        <v>26.04951109641535</v>
+      </c>
+      <c r="N12" t="n">
+        <v>13.75572799407668</v>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr"/>
-      <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+      <c r="Q12" s="4" t="n">
+        <v>0.8816067653276956</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>0.947463768115942</v>
+      </c>
+      <c r="S12" s="4" t="n">
+        <v>0.6589595375722543</v>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>0.5407166123778501</v>
+      </c>
+      <c r="U12" s="4" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>0.6475</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="X12" t="n">
-        <v>0.8</v>
+        <v>0.796</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.749</v>
+        <v>0.76</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.7784520148968087</v>
+        <v>0.7792340968020122</v>
       </c>
       <c r="AA12" s="4" t="n">
-        <v>0.7246091754455255</v>
+        <v>0.7439524644750251</v>
       </c>
       <c r="AB12" s="4" t="n">
-        <v>0.7745</v>
+        <v>0.778</v>
       </c>
       <c r="AC12" s="4" t="n">
-        <v>0.7528237438696134</v>
+        <v>0.7614406146917927</v>
       </c>
       <c r="AD12" s="4" t="n">
-        <v>0.835</v>
+        <v>0.832</v>
       </c>
       <c r="AE12" s="5" t="n">
-        <v>721898</v>
+        <v>1061596</v>
       </c>
       <c r="AF12" s="5" t="n">
-        <v>0</v>
+        <v>51608</v>
       </c>
       <c r="AG12" s="5" t="n">
-        <v>0</v>
+        <v>24960</v>
       </c>
       <c r="AH12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AI12" s="3" t="inlineStr"/>
-      <c r="AJ12" s="3" t="inlineStr"/>
-      <c r="AK12" s="3" t="inlineStr"/>
-      <c r="AL12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="n">
+        <v>0.03791827</v>
+      </c>
+      <c r="AJ12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="3" t="n">
+        <v>0.03791826999999996</v>
+      </c>
+      <c r="AL12" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>local/qwen3.5-4b-q4km-gguf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Qwen3.5 4B (GGUF Q4_K_M, local)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mistralai</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>local</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -8115,117 +8339,79 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-16T03:10:41+00:00</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>0.1340643496794257</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.200848621976299</v>
-      </c>
-      <c r="M13" t="n">
-        <v>23.15600037313629</v>
-      </c>
-      <c r="N13" t="n">
-        <v>12.32917653667287</v>
-      </c>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" s="4" t="n">
-        <v>0.8982440342188204</v>
-      </c>
-      <c r="R13" s="4" t="n">
-        <v>0.9363636363636364</v>
-      </c>
-      <c r="S13" s="4" t="n">
-        <v>0.7163461538461539</v>
-      </c>
-      <c r="T13" s="4" t="n">
-        <v>0.683291770573566</v>
-      </c>
-      <c r="U13" s="4" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="V13" s="4" t="n">
-        <v>0.6825</v>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="Q13" s="4" t="inlineStr"/>
+      <c r="R13" s="4" t="inlineStr"/>
+      <c r="S13" s="4" t="inlineStr"/>
+      <c r="T13" s="4" t="inlineStr"/>
+      <c r="U13" s="4" t="inlineStr"/>
+      <c r="V13" s="4" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
       <c r="X13" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.744</v>
+        <v>0.749</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.7603515978750895</v>
+        <v>0.7784520148968087</v>
       </c>
       <c r="AA13" s="4" t="n">
-        <v>0.7113942857254609</v>
+        <v>0.7246091754455255</v>
       </c>
       <c r="AB13" s="4" t="n">
-        <v>0.762</v>
+        <v>0.7745</v>
       </c>
       <c r="AC13" s="4" t="n">
-        <v>0.736163325053324</v>
+        <v>0.7528237438696134</v>
       </c>
       <c r="AD13" s="4" t="n">
-        <v>0.824</v>
+        <v>0.835</v>
       </c>
       <c r="AE13" s="5" t="n">
-        <v>1092316</v>
+        <v>721898</v>
       </c>
       <c r="AF13" s="5" t="n">
-        <v>71944</v>
+        <v>0</v>
       </c>
       <c r="AG13" s="5" t="n">
-        <v>295936</v>
+        <v>0</v>
       </c>
       <c r="AH13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AI13" s="3" t="n">
-        <v>0.17958352</v>
-      </c>
-      <c r="AJ13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="3" t="n">
-        <v>0.1795835200000001</v>
-      </c>
-      <c r="AL13" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -8244,13 +8430,13 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -8259,40 +8445,40 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-16T03:15:02+00:00</t>
+          <t>2026-09-16T03:10:41+00:00</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.1338576862477163</v>
+        <v>0.1340643496794257</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2022785739193924</v>
+        <v>0.200848621976299</v>
       </c>
       <c r="M14" t="n">
-        <v>23.2893881252992</v>
+        <v>23.15600037313629</v>
       </c>
       <c r="N14" t="n">
-        <v>12.28128440018327</v>
+        <v>12.32917653667287</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" s="4" t="n">
-        <v>0.8798944126704795</v>
+        <v>0.8982440342188204</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.9474768280123584</v>
+        <v>0.9363636363636364</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.6366366366366367</v>
+        <v>0.7163461538461539</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.5857988165680473</v>
+        <v>0.683291770573566</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.6975</v>
+        <v>0.705</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.65</v>
+        <v>0.6825</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -8300,46 +8486,46 @@
         </is>
       </c>
       <c r="X14" t="n">
-        <v>0.738</v>
+        <v>0.78</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.737</v>
+        <v>0.744</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.7285750142849275</v>
+        <v>0.7603515978750895</v>
       </c>
       <c r="AA14" s="4" t="n">
-        <v>0.712693713084553</v>
+        <v>0.7113942857254609</v>
       </c>
       <c r="AB14" s="4" t="n">
-        <v>0.7375</v>
+        <v>0.762</v>
       </c>
       <c r="AC14" s="4" t="n">
-        <v>0.7216311867724771</v>
+        <v>0.736163325053324</v>
       </c>
       <c r="AD14" s="4" t="n">
-        <v>0.763</v>
+        <v>0.824</v>
       </c>
       <c r="AE14" s="5" t="n">
         <v>1092316</v>
       </c>
       <c r="AF14" s="5" t="n">
-        <v>71698</v>
+        <v>71944</v>
       </c>
       <c r="AG14" s="5" t="n">
-        <v>299392</v>
+        <v>295936</v>
       </c>
       <c r="AH14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>0.13418418</v>
+        <v>0.17958352</v>
       </c>
       <c r="AJ14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>0.1341841799999999</v>
+        <v>0.1795835200000001</v>
       </c>
       <c r="AL14" s="3" t="n">
         <v>0</v>
@@ -8348,17 +8534,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>anthropic/claude-haiku-5.5</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Claude Haiku 5.5</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>anthropic</t>
+          <t>mistralai</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -8372,13 +8558,13 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -8387,40 +8573,40 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-10-09T22:53:18+00:00</t>
+          <t>2026-09-16T03:15:02+00:00</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.1508966289450845</v>
+        <v>0.1338576862477163</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2311362841535614</v>
+        <v>0.2022785739193924</v>
       </c>
       <c r="M15" t="n">
-        <v>25.66370942573976</v>
+        <v>23.2893881252992</v>
       </c>
       <c r="N15" t="n">
-        <v>13.76495728026645</v>
+        <v>12.28128440018327</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" s="4" t="n">
-        <v>0.9283683911313246</v>
+        <v>0.8798944126704795</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.9528432732316228</v>
+        <v>0.9474768280123584</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.7173913043478261</v>
+        <v>0.6366366366366367</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.6355555555555555</v>
+        <v>0.5857988165680473</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.675</v>
+        <v>0.6975</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -8428,46 +8614,46 @@
         </is>
       </c>
       <c r="X15" t="n">
-        <v>0.739</v>
+        <v>0.738</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.654</v>
+        <v>0.737</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.7300556851332078</v>
+        <v>0.7285750142849275</v>
       </c>
       <c r="AA15" s="4" t="n">
-        <v>0.6325396281985507</v>
+        <v>0.712693713084553</v>
       </c>
       <c r="AB15" s="4" t="n">
-        <v>0.6965</v>
+        <v>0.7375</v>
       </c>
       <c r="AC15" s="4" t="n">
-        <v>0.6796308583013593</v>
+        <v>0.7216311867724771</v>
       </c>
       <c r="AD15" s="4" t="n">
-        <v>0.743</v>
+        <v>0.763</v>
       </c>
       <c r="AE15" s="5" t="n">
-        <v>1789714</v>
+        <v>1092316</v>
       </c>
       <c r="AF15" s="5" t="n">
-        <v>86877</v>
+        <v>71698</v>
       </c>
       <c r="AG15" s="5" t="n">
-        <v>0</v>
+        <v>299392</v>
       </c>
       <c r="AH15" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>0.2224099</v>
+        <v>0.13418418</v>
       </c>
       <c r="AJ15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>0.2224099000000001</v>
+        <v>0.1341841799999999</v>
       </c>
       <c r="AL15" s="3" t="n">
         <v>0</v>
@@ -8476,17 +8662,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>anthropic/claude-haiku-5.5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>Claude Haiku 5.5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>anthropic</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -8500,13 +8686,13 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -8515,40 +8701,40 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-16T03:20:07+00:00</t>
+          <t>2026-10-09T22:53:18+00:00</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>0.1303590348428198</v>
+        <v>0.1508966289450845</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1872998825564791</v>
+        <v>0.2311362841535614</v>
       </c>
       <c r="M16" t="n">
-        <v>23.22067206524886</v>
+        <v>25.66370942573976</v>
       </c>
       <c r="N16" t="n">
-        <v>11.95596092668423</v>
+        <v>13.76495728026645</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" s="4" t="n">
-        <v>0.961978928080623</v>
+        <v>0.9283683911313246</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.9586330935251799</v>
+        <v>0.9528432732316228</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.6149068322981366</v>
+        <v>0.7173913043478261</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.2382978723404255</v>
+        <v>0.6355555555555555</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.675</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.5525</v>
+        <v>0.59</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -8556,31 +8742,31 @@
         </is>
       </c>
       <c r="X16" t="n">
-        <v>0.715</v>
+        <v>0.739</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.661</v>
+        <v>0.654</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.7079848008862988</v>
+        <v>0.7300556851332078</v>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>0.6593342425290085</v>
+        <v>0.6325396281985507</v>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6965</v>
       </c>
       <c r="AC16" s="4" t="n">
-        <v>0.6845822094887644</v>
+        <v>0.6796308583013593</v>
       </c>
       <c r="AD16" s="4" t="n">
-        <v>0.718</v>
+        <v>0.743</v>
       </c>
       <c r="AE16" s="5" t="n">
-        <v>1106945</v>
+        <v>1789714</v>
       </c>
       <c r="AF16" s="5" t="n">
-        <v>75745</v>
+        <v>86877</v>
       </c>
       <c r="AG16" s="5" t="n">
         <v>0</v>
@@ -8589,13 +8775,13 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>0.31607025</v>
+        <v>0.2224099</v>
       </c>
       <c r="AJ16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>0.3160702499999996</v>
+        <v>0.2224099000000001</v>
       </c>
       <c r="AL16" s="3" t="n">
         <v>0</v>
@@ -8604,17 +8790,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mistralai</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -8628,13 +8814,13 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.6</v>
+        <v>1.25</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -8643,40 +8829,40 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-16T03:07:59+00:00</t>
+          <t>2026-09-16T03:20:07+00:00</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.1486748430163934</v>
+        <v>0.1303590348428198</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2158566833442461</v>
+        <v>0.1872998825564791</v>
       </c>
       <c r="M17" t="n">
-        <v>24.85170132045256</v>
+        <v>23.22067206524886</v>
       </c>
       <c r="N17" t="n">
-        <v>12.57729783101797</v>
+        <v>11.95596092668423</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" s="4" t="n">
-        <v>0.9259462424574877</v>
+        <v>0.961978928080623</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.9627450980392157</v>
+        <v>0.9586330935251799</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.7247956403269755</v>
+        <v>0.6149068322981366</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.6195652173913043</v>
+        <v>0.2382978723404255</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.65</v>
+        <v>0.5525</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -8684,46 +8870,46 @@
         </is>
       </c>
       <c r="X17" t="n">
-        <v>0.509</v>
+        <v>0.715</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.711</v>
+        <v>0.661</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.5867378280355483</v>
+        <v>0.7079848008862988</v>
       </c>
       <c r="AA17" s="4" t="n">
-        <v>0.7031769757373104</v>
+        <v>0.6593342425290085</v>
       </c>
       <c r="AB17" s="4" t="n">
-        <v>0.61</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AC17" s="4" t="n">
-        <v>0.6504937686437986</v>
+        <v>0.6845822094887644</v>
       </c>
       <c r="AD17" s="4" t="n">
-        <v>0.7</v>
+        <v>0.718</v>
       </c>
       <c r="AE17" s="5" t="n">
-        <v>1107916</v>
+        <v>1106945</v>
       </c>
       <c r="AF17" s="5" t="n">
-        <v>62923</v>
+        <v>75745</v>
       </c>
       <c r="AG17" s="5" t="n">
-        <v>183856</v>
+        <v>0</v>
       </c>
       <c r="AH17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>0.1964076975</v>
+        <v>0.31607025</v>
       </c>
       <c r="AJ17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>0.1964076975000001</v>
+        <v>0.3160702499999996</v>
       </c>
       <c r="AL17" s="3" t="n">
         <v>0</v>
@@ -8732,22 +8918,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>local/qwen3.5-2b-q8-gguf</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Qwen3.5 2B (GGUF Q8_0, local)</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>mistralai</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,89 +8941,127 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>0.015</v>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>config</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>2026-09-16T03:07:59+00:00</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0.1486748430163934</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.2158566833442461</v>
+      </c>
+      <c r="M18" t="n">
+        <v>24.85170132045256</v>
+      </c>
+      <c r="N18" t="n">
+        <v>12.57729783101797</v>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" s="4" t="inlineStr"/>
-      <c r="R18" s="4" t="inlineStr"/>
-      <c r="S18" s="4" t="inlineStr"/>
-      <c r="T18" s="4" t="inlineStr"/>
-      <c r="U18" s="4" t="inlineStr"/>
-      <c r="V18" s="4" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+      <c r="Q18" s="4" t="n">
+        <v>0.9259462424574877</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>0.9627450980392157</v>
+      </c>
+      <c r="S18" s="4" t="n">
+        <v>0.7247956403269755</v>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>0.6195652173913043</v>
+      </c>
+      <c r="U18" s="4" t="n">
+        <v>0.7475000000000001</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="X18" t="n">
-        <v>0.648</v>
+        <v>0.509</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.517</v>
+        <v>0.711</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.6273835935085809</v>
+        <v>0.5867378280355483</v>
       </c>
       <c r="AA18" s="4" t="n">
-        <v>0.5062609313499989</v>
+        <v>0.7031769757373104</v>
       </c>
       <c r="AB18" s="4" t="n">
-        <v>0.5825</v>
+        <v>0.61</v>
       </c>
       <c r="AC18" s="4" t="n">
-        <v>0.5734975422659654</v>
+        <v>0.6504937686437986</v>
       </c>
       <c r="AD18" s="4" t="n">
-        <v>0.705</v>
+        <v>0.7</v>
       </c>
       <c r="AE18" s="5" t="n">
-        <v>721898</v>
+        <v>1107916</v>
       </c>
       <c r="AF18" s="5" t="n">
-        <v>0</v>
+        <v>62923</v>
       </c>
       <c r="AG18" s="5" t="n">
-        <v>0</v>
+        <v>183856</v>
       </c>
       <c r="AH18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AI18" s="3" t="inlineStr"/>
-      <c r="AJ18" s="3" t="inlineStr"/>
-      <c r="AK18" s="3" t="inlineStr"/>
-      <c r="AL18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="n">
+        <v>0.1964076975</v>
+      </c>
+      <c r="AJ18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="3" t="n">
+        <v>0.1964076975000001</v>
+      </c>
+      <c r="AL18" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>local/qwen3.5-2b-q8-gguf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Qwen3.5 2B (GGUF Q8_0, local)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mistralai</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>local</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8845,127 +9069,89 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-16T03:17:56+00:00</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>0.1344392234965607</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.1976921128927562</v>
-      </c>
-      <c r="M19" t="n">
-        <v>23.21465695587321</v>
-      </c>
-      <c r="N19" t="n">
-        <v>11.65156743434614</v>
-      </c>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" s="4" t="n">
-        <v>0.886284289276808</v>
-      </c>
-      <c r="R19" s="4" t="n">
-        <v>0.9119420989143546</v>
-      </c>
-      <c r="S19" s="4" t="n">
-        <v>0.6757493188010899</v>
-      </c>
-      <c r="T19" s="4" t="n">
-        <v>0.5591939546599498</v>
-      </c>
-      <c r="U19" s="4" t="n">
-        <v>0.7025</v>
-      </c>
-      <c r="V19" s="4" t="n">
-        <v>0.5625</v>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="Q19" s="4" t="inlineStr"/>
+      <c r="R19" s="4" t="inlineStr"/>
+      <c r="S19" s="4" t="inlineStr"/>
+      <c r="T19" s="4" t="inlineStr"/>
+      <c r="U19" s="4" t="inlineStr"/>
+      <c r="V19" s="4" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="n">
-        <v>0.465</v>
+        <v>0.648</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.606</v>
+        <v>0.517</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.5053205391654078</v>
+        <v>0.6273835935085809</v>
       </c>
       <c r="AA19" s="4" t="n">
-        <v>0.5671517703461975</v>
+        <v>0.5062609313499989</v>
       </c>
       <c r="AB19" s="4" t="n">
-        <v>0.5355</v>
+        <v>0.5825</v>
       </c>
       <c r="AC19" s="4" t="n">
-        <v>0.5411026333400099</v>
+        <v>0.5734975422659654</v>
       </c>
       <c r="AD19" s="4" t="n">
-        <v>0.651</v>
+        <v>0.705</v>
       </c>
       <c r="AE19" s="5" t="n">
-        <v>1092316</v>
+        <v>721898</v>
       </c>
       <c r="AF19" s="5" t="n">
-        <v>69602</v>
+        <v>0</v>
       </c>
       <c r="AG19" s="5" t="n">
-        <v>318592</v>
+        <v>0</v>
       </c>
       <c r="AH19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AI19" s="3" t="n">
-        <v>0.08751852</v>
-      </c>
-      <c r="AJ19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" s="3" t="n">
-        <v>0.08751852</v>
-      </c>
-      <c r="AL19" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>mistralai</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8973,79 +9159,117 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>0.01</v>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>config</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>2026-09-16T03:17:56+00:00</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0.1344392234965607</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.1976921128927562</v>
+      </c>
+      <c r="M20" t="n">
+        <v>23.21465695587321</v>
+      </c>
+      <c r="N20" t="n">
+        <v>11.65156743434614</v>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" s="4" t="inlineStr"/>
-      <c r="R20" s="4" t="inlineStr"/>
-      <c r="S20" s="4" t="inlineStr"/>
-      <c r="T20" s="4" t="inlineStr"/>
-      <c r="U20" s="4" t="inlineStr"/>
-      <c r="V20" s="4" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
+      <c r="Q20" s="4" t="n">
+        <v>0.886284289276808</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>0.9119420989143546</v>
+      </c>
+      <c r="S20" s="4" t="n">
+        <v>0.6757493188010899</v>
+      </c>
+      <c r="T20" s="4" t="n">
+        <v>0.5591939546599498</v>
+      </c>
+      <c r="U20" s="4" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="X20" t="n">
-        <v>0.578</v>
+        <v>0.465</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.462</v>
+        <v>0.606</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.5486232650628055</v>
+        <v>0.5053205391654078</v>
       </c>
       <c r="AA20" s="4" t="n">
-        <v>0.4225847136466017</v>
+        <v>0.5671517703461975</v>
       </c>
       <c r="AB20" s="4" t="n">
-        <v>0.52</v>
+        <v>0.5355</v>
       </c>
       <c r="AC20" s="4" t="n">
-        <v>0.4912105263425375</v>
+        <v>0.5411026333400099</v>
       </c>
       <c r="AD20" s="4" t="n">
-        <v>0.706</v>
+        <v>0.651</v>
       </c>
       <c r="AE20" s="5" t="n">
-        <v>2162979</v>
+        <v>1092316</v>
       </c>
       <c r="AF20" s="5" t="n">
-        <v>16353</v>
+        <v>69602</v>
       </c>
       <c r="AG20" s="5" t="n">
-        <v>0</v>
+        <v>318592</v>
       </c>
       <c r="AH20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AI20" s="3" t="inlineStr"/>
-      <c r="AJ20" s="3" t="inlineStr"/>
-      <c r="AK20" s="3" t="inlineStr"/>
-      <c r="AL20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="n">
+        <v>0.08751852</v>
+      </c>
+      <c r="AJ20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3" t="n">
+        <v>0.08751852</v>
+      </c>
+      <c r="AL20" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
+          <t>Qwen2.5 1.5B Q8 - grammar-guided generation (baseline)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -9090,31 +9314,31 @@
       <c r="V21" s="4" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="n">
-        <v>0.572</v>
+        <v>0.578</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.458</v>
+        <v>0.462</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.5383725106907433</v>
+        <v>0.5486232650628055</v>
       </c>
       <c r="AA21" s="4" t="n">
-        <v>0.4142792208259681</v>
+        <v>0.4225847136466017</v>
       </c>
       <c r="AB21" s="4" t="n">
-        <v>0.515</v>
+        <v>0.52</v>
       </c>
       <c r="AC21" s="4" t="n">
-        <v>0.4816940963179205</v>
+        <v>0.4912105263425375</v>
       </c>
       <c r="AD21" s="4" t="n">
-        <v>0.724</v>
+        <v>0.706</v>
       </c>
       <c r="AE21" s="5" t="n">
-        <v>1441986</v>
+        <v>2162979</v>
       </c>
       <c r="AF21" s="5" t="n">
-        <v>0</v>
+        <v>16353</v>
       </c>
       <c r="AG21" s="5" t="n">
         <v>0</v>
@@ -9130,22 +9354,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>local/qwen2.5-1.5b-instruct-q8-gguf-pcd</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Qwen2.5 1.5B Q8 - parallel constrained decoding</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>openai</t>
+          <t>qwen</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>local</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9153,127 +9377,89 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>0.025</v>
-      </c>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>openrouter</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-16T03:23:30+00:00</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>0.1434021604287071</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.2194519351485593</v>
-      </c>
-      <c r="M22" t="n">
-        <v>24.49324424955361</v>
-      </c>
-      <c r="N22" t="n">
-        <v>12.31697458631575</v>
-      </c>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" s="4" t="n">
-        <v>0.8991138377641446</v>
-      </c>
-      <c r="R22" s="4" t="n">
-        <v>0.9558232931726908</v>
-      </c>
-      <c r="S22" s="4" t="n">
-        <v>0.7005347593582888</v>
-      </c>
-      <c r="T22" s="4" t="n">
-        <v>0.5421686746987951</v>
-      </c>
-      <c r="U22" s="4" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="V22" s="4" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="Q22" s="4" t="inlineStr"/>
+      <c r="R22" s="4" t="inlineStr"/>
+      <c r="S22" s="4" t="inlineStr"/>
+      <c r="T22" s="4" t="inlineStr"/>
+      <c r="U22" s="4" t="inlineStr"/>
+      <c r="V22" s="4" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
       <c r="X22" t="n">
-        <v>0.529</v>
+        <v>0.572</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.398</v>
+        <v>0.458</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.5140122481389001</v>
+        <v>0.5383725106907433</v>
       </c>
       <c r="AA22" s="4" t="n">
-        <v>0.3758955615145875</v>
+        <v>0.4142792208259681</v>
       </c>
       <c r="AB22" s="4" t="n">
-        <v>0.4635</v>
+        <v>0.515</v>
       </c>
       <c r="AC22" s="4" t="n">
-        <v>0.4473337487719194</v>
+        <v>0.4816940963179205</v>
       </c>
       <c r="AD22" s="4" t="n">
-        <v>0.731</v>
+        <v>0.724</v>
       </c>
       <c r="AE22" s="5" t="n">
-        <v>1108245</v>
+        <v>1441986</v>
       </c>
       <c r="AF22" s="5" t="n">
-        <v>55419</v>
+        <v>0</v>
       </c>
       <c r="AG22" s="5" t="n">
-        <v>36224</v>
+        <v>0</v>
       </c>
       <c r="AH22" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AI22" s="3" t="n">
-        <v>0.1302753</v>
-      </c>
-      <c r="AJ22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="3" t="n">
-        <v>0.1302753</v>
-      </c>
-      <c r="AL22" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AI22" s="3" t="inlineStr"/>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>local/laya-multilingual</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Laya Multilingual (mmBERT-base decision head, local)</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>convaiinnovations</t>
+          <t>openai</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9281,72 +9467,200 @@
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>0.025</v>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>openrouter</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>config</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>2026-09-16T03:23:30+00:00</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0.1434021604287071</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.2194519351485593</v>
+      </c>
+      <c r="M23" t="n">
+        <v>24.49324424955361</v>
+      </c>
+      <c r="N23" t="n">
+        <v>12.31697458631575</v>
+      </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" s="4" t="inlineStr"/>
-      <c r="R23" s="4" t="inlineStr"/>
-      <c r="S23" s="4" t="inlineStr"/>
-      <c r="T23" s="4" t="inlineStr"/>
-      <c r="U23" s="4" t="inlineStr"/>
-      <c r="V23" s="4" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
+      <c r="Q23" s="4" t="n">
+        <v>0.8991138377641446</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>0.9558232931726908</v>
+      </c>
+      <c r="S23" s="4" t="n">
+        <v>0.7005347593582888</v>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>0.5421686746987951</v>
+      </c>
+      <c r="U23" s="4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
       <c r="X23" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="Y23" t="n">
         <v>0.398</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Z23" s="4" t="n">
+        <v>0.5140122481389001</v>
+      </c>
+      <c r="AA23" s="4" t="n">
+        <v>0.3758955615145875</v>
+      </c>
+      <c r="AB23" s="4" t="n">
+        <v>0.4635</v>
+      </c>
+      <c r="AC23" s="4" t="n">
+        <v>0.4473337487719194</v>
+      </c>
+      <c r="AD23" s="4" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="AE23" s="5" t="n">
+        <v>1108245</v>
+      </c>
+      <c r="AF23" s="5" t="n">
+        <v>55419</v>
+      </c>
+      <c r="AG23" s="5" t="n">
+        <v>36224</v>
+      </c>
+      <c r="AH23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="3" t="n">
+        <v>0.1302753</v>
+      </c>
+      <c r="AJ23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="3" t="n">
+        <v>0.1302753</v>
+      </c>
+      <c r="AL23" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>local/laya-multilingual</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Laya Multilingual (mmBERT-base decision head, local)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>convaiinnovations</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" s="4" t="inlineStr"/>
+      <c r="R24" s="4" t="inlineStr"/>
+      <c r="S24" s="4" t="inlineStr"/>
+      <c r="T24" s="4" t="inlineStr"/>
+      <c r="U24" s="4" t="inlineStr"/>
+      <c r="V24" s="4" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="Y24" t="n">
         <v>0.302</v>
       </c>
-      <c r="Z23" s="4" t="n">
+      <c r="Z24" s="4" t="n">
         <v>0.3312729217590112</v>
       </c>
-      <c r="AA23" s="4" t="n">
+      <c r="AA24" s="4" t="n">
         <v>0.2508535938503552</v>
       </c>
-      <c r="AB23" s="4" t="n">
+      <c r="AB24" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="AC23" s="4" t="n">
+      <c r="AC24" s="4" t="n">
         <v>0.2939712093714177</v>
       </c>
-      <c r="AD23" s="4" t="n">
+      <c r="AD24" s="4" t="n">
         <v>0.794</v>
       </c>
-      <c r="AE23" s="5" t="n">
+      <c r="AE24" s="5" t="n">
         <v>544388</v>
       </c>
-      <c r="AF23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" s="3" t="inlineStr"/>
-      <c r="AJ23" s="3" t="inlineStr"/>
-      <c r="AK23" s="3" t="inlineStr"/>
-      <c r="AL23" s="3" t="inlineStr"/>
+      <c r="AF24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3" t="inlineStr"/>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL23"/>
+  <autoFilter ref="A1:AL24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11308,7 +11622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -11848,12 +12162,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>microsoft/microsoft-decision-1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Microsoft Decision 1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -11873,25 +12187,25 @@
         <v>200</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.705</v>
+        <v>0.74</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.7045272435897436</v>
+        <v>0.7398373983739837</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.6898148148148148</v>
+        <v>0.7285714285714285</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.745</v>
+        <v>0.765</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.7163461538461539</v>
+        <v>0.7463414634146341</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.665</v>
+        <v>0.715</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.6927083333333334</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -11903,12 +12217,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>microsoft/microsoft-decision-1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Microsoft Decision 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -11928,25 +12242,25 @@
         <v>200</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.6825</v>
+        <v>0.65</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.6824980156125975</v>
+        <v>0.6361651810078224</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.681592039800995</v>
+        <v>0.7459016393442623</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.455</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.683291770573566</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.68</v>
+        <v>0.845</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.681704260651629</v>
+        <v>0.707112970711297</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -11958,12 +12272,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -11983,25 +12297,25 @@
         <v>200</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.7025</v>
+        <v>0.705</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.7004612644813764</v>
+        <v>0.7045272435897436</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.7425149700598802</v>
+        <v>0.6898148148148148</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.62</v>
+        <v>0.745</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.6757493188010899</v>
+        <v>0.7163461538461539</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.785</v>
+        <v>0.665</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.7251732101616628</v>
+        <v>0.6927083333333334</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -12013,12 +12327,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -12038,25 +12352,25 @@
         <v>200</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.5625</v>
+        <v>0.6825</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.5624753892406449</v>
+        <v>0.6824980156125975</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.5634517766497462</v>
+        <v>0.681592039800995</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.555</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.5591939546599498</v>
+        <v>0.683291770573566</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.56575682382134</v>
+        <v>0.681704260651629</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -12068,12 +12382,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -12093,25 +12407,25 @@
         <v>200</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.6975</v>
+        <v>0.7025</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.6887679971191749</v>
+        <v>0.7004612644813764</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.7969924812030075</v>
+        <v>0.7425149700598802</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.6366366366366367</v>
+        <v>0.6757493188010899</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.865</v>
+        <v>0.785</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.7408993576017131</v>
+        <v>0.7251732101616628</v>
       </c>
       <c r="N14" s="4" t="n">
         <v>0</v>
@@ -12123,12 +12437,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -12148,25 +12462,25 @@
         <v>200</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.65</v>
+        <v>0.5625</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.6413842567688721</v>
+        <v>0.5624753892406449</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.7173913043478261</v>
+        <v>0.5634517766497462</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.495</v>
+        <v>0.555</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.5857988165680473</v>
+        <v>0.5591939546599498</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.805</v>
+        <v>0.57</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.6969696969696969</v>
+        <v>0.56575682382134</v>
       </c>
       <c r="N15" s="4" t="n">
         <v>0</v>
@@ -12178,12 +12492,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -12203,25 +12517,25 @@
         <v>200</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.6975</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.7457696446438573</v>
+        <v>0.6887679971191749</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.7964071856287425</v>
+        <v>0.7969924812030075</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.665</v>
+        <v>0.53</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.7247956403269755</v>
+        <v>0.6366366366366367</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.83</v>
+        <v>0.865</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.7667436489607391</v>
+        <v>0.7408993576017131</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -12233,12 +12547,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -12261,22 +12575,22 @@
         <v>0.65</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.6477455716586151</v>
+        <v>0.6413842567688721</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.6785714285714286</v>
+        <v>0.7173913043478261</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.57</v>
+        <v>0.495</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.6195652173913043</v>
+        <v>0.5857988165680473</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.73</v>
+        <v>0.805</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.6759259259259258</v>
+        <v>0.6969696969696969</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
@@ -12288,12 +12602,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -12313,25 +12627,25 @@
         <v>200</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.72</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.7188119806181115</v>
+        <v>0.7457696446438573</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.7528735632183908</v>
+        <v>0.7964071856287425</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.655</v>
+        <v>0.665</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.7005347593582888</v>
+        <v>0.7247956403269755</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.785</v>
+        <v>0.83</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.7370892018779343</v>
+        <v>0.7667436489607391</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0</v>
@@ -12343,12 +12657,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -12368,25 +12682,25 @@
         <v>200</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.6086911749562351</v>
+        <v>0.6477455716586151</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.5421686746987951</v>
+        <v>0.6195652173913043</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.6752136752136753</v>
+        <v>0.6759259259259258</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0</v>
@@ -12398,12 +12712,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -12423,25 +12737,25 @@
         <v>200</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.6775</v>
+        <v>0.72</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.6774496015002344</v>
+        <v>0.7188119806181115</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.6731707317073171</v>
+        <v>0.7528735632183908</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.655</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.6814814814814814</v>
+        <v>0.7005347593582888</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.665</v>
+        <v>0.785</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.6734177215189874</v>
+        <v>0.7370892018779343</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>0</v>
@@ -12453,12 +12767,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -12478,25 +12792,25 @@
         <v>200</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.5059742647058822</v>
+        <v>0.6086911749562351</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.75</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.21</v>
+        <v>0.45</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.328125</v>
+        <v>0.5421686746987951</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.93</v>
+        <v>0.79</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.6838235294117646</v>
+        <v>0.6752136752136753</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
@@ -12508,12 +12822,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -12533,25 +12847,25 @@
         <v>200</v>
       </c>
       <c r="G22" s="4" t="n">
+        <v>0.6775</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>0.6774496015002344</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>0.6731707317073171</v>
+      </c>
+      <c r="J22" s="4" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="H22" s="4" t="n">
-        <v>0.677746303178357</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>0.8114754098360656</v>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>0.495</v>
-      </c>
       <c r="K22" s="4" t="n">
-        <v>0.6149068322981366</v>
+        <v>0.6814814814814814</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.885</v>
+        <v>0.665</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.7405857740585775</v>
+        <v>0.6734177215189874</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -12563,12 +12877,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -12588,25 +12902,25 @@
         <v>200</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.5525</v>
+        <v>0.57</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.4607418565241951</v>
+        <v>0.5059742647058822</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.2382978723404255</v>
+        <v>0.328125</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.965</v>
+        <v>0.93</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.6831858407079646</v>
+        <v>0.6838235294117646</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -12618,12 +12932,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -12643,25 +12957,25 @@
         <v>200</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.7474984218651367</v>
+        <v>0.677746303178357</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.746268656716418</v>
+        <v>0.8114754098360656</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.75</v>
+        <v>0.495</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.748129675810474</v>
+        <v>0.6149068322981366</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.745</v>
+        <v>0.885</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.7468671679197995</v>
+        <v>0.7405857740585775</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>0</v>
@@ -12673,12 +12987,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -12698,25 +13012,25 @@
         <v>200</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.6825</v>
+        <v>0.5525</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.6800503857660211</v>
+        <v>0.4607418565241951</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.7212121212121212</v>
+        <v>0.8</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.595</v>
+        <v>0.14</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.6520547945205479</v>
+        <v>0.2382978723404255</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.77</v>
+        <v>0.965</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.7080459770114942</v>
+        <v>0.6831858407079646</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
@@ -12728,12 +13042,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>openai/gpt-6-luna</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GPT-6 Luna</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -12753,25 +13067,25 @@
         <v>200</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.7</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.6969696969696968</v>
+        <v>0.7474984218651367</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.746268656716418</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.7272727272727272</v>
+        <v>0.748129675810474</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.6</v>
+        <v>0.745</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.7468671679197995</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>0</v>
@@ -12783,12 +13097,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>openai/gpt-6-luna</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GPT-6 Luna</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -12808,25 +13122,25 @@
         <v>200</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.6375</v>
+        <v>0.6825</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.6364980978822881</v>
+        <v>0.6800503857660211</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.6536312849162011</v>
+        <v>0.7212121212121212</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.585</v>
+        <v>0.595</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.6174142480211081</v>
+        <v>0.6520547945205479</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.6555819477434679</v>
+        <v>0.7080459770114942</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>0</v>
@@ -12838,12 +13152,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-6-luna</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-6 Luna</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -12863,25 +13177,25 @@
         <v>200</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.695</v>
+        <v>0.7</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.6794871794871795</v>
+        <v>0.6969696969696968</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.8482142857142857</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.475</v>
+        <v>0.8</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.6089743589743589</v>
+        <v>0.7272727272727272</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.915</v>
+        <v>0.6</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.7500000000000001</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>0</v>
@@ -12893,12 +13207,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-6-luna</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-6 Luna</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -12918,25 +13232,25 @@
         <v>200</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.605</v>
+        <v>0.6375</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.5599376114081996</v>
+        <v>0.6364980978822881</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.6536312849162011</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.285</v>
+        <v>0.585</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.4191176470588235</v>
+        <v>0.6174142480211081</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.925</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.7007575757575758</v>
+        <v>0.6555819477434679</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>0</v>
@@ -12948,12 +13262,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -12973,25 +13287,25 @@
         <v>200</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.705</v>
+        <v>0.695</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.6995238216495633</v>
+        <v>0.6794871794871795</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.7808219178082192</v>
+        <v>0.8482142857142857</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.57</v>
+        <v>0.475</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.6589595375722543</v>
+        <v>0.6089743589743589</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.84</v>
+        <v>0.915</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.7400881057268722</v>
+        <v>0.7500000000000001</v>
       </c>
       <c r="N30" s="4" t="n">
         <v>0</v>
@@ -13003,12 +13317,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -13028,25 +13342,25 @@
         <v>200</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.6475</v>
+        <v>0.605</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.6273562777913592</v>
+        <v>0.5599376114081996</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.7757009345794392</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.415</v>
+        <v>0.285</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.5407166123778501</v>
+        <v>0.4191176470588235</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.88</v>
+        <v>0.925</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.7139959432048683</v>
+        <v>0.7007575757575758</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>0</v>
@@ -13058,12 +13372,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -13083,25 +13397,25 @@
         <v>200</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.7675</v>
+        <v>0.705</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.7672541622088331</v>
+        <v>0.6995238216495633</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.786096256684492</v>
+        <v>0.7808219178082192</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.735</v>
+        <v>0.57</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.7596899224806202</v>
+        <v>0.6589595375722543</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.774818401937046</v>
+        <v>0.7400881057268722</v>
       </c>
       <c r="N32" s="4" t="n">
         <v>0</v>
@@ -13113,12 +13427,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -13138,25 +13452,25 @@
         <v>200</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.6575</v>
+        <v>0.6475</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.6404930755554972</v>
+        <v>0.6273562777913592</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.7787610619469026</v>
+        <v>0.7757009345794392</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.44</v>
+        <v>0.415</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.5623003194888179</v>
+        <v>0.5407166123778501</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.875</v>
+        <v>0.88</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.7186858316221766</v>
+        <v>0.7139959432048683</v>
       </c>
       <c r="N33" s="4" t="n">
         <v>0</v>
@@ -13168,12 +13482,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -13193,25 +13507,25 @@
         <v>200</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.7275</v>
+        <v>0.7675</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.7274846710127445</v>
+        <v>0.7672541622088331</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.7309644670050761</v>
+        <v>0.786096256684492</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.72</v>
+        <v>0.735</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.72544080604534</v>
+        <v>0.7596899224806202</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.735</v>
+        <v>0.8</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.729528535980149</v>
+        <v>0.774818401937046</v>
       </c>
       <c r="N34" s="4" t="n">
         <v>0</v>
@@ -13223,12 +13537,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -13248,35 +13562,145 @@
         <v>200</v>
       </c>
       <c r="G35" s="4" t="n">
+        <v>0.6575</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>0.6404930755554972</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>0.7787610619469026</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>0.5623003194888179</v>
+      </c>
+      <c r="L35" s="4" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="M35" s="4" t="n">
+        <v>0.7186858316221766</v>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>0.7275</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>0.7274846710127445</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>0.7309644670050761</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>0.72544080604534</v>
+      </c>
+      <c r="L36" s="4" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="M36" s="4" t="n">
+        <v>0.729528535980149</v>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>400</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="G37" s="4" t="n">
         <v>0.64</v>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>0.6265172735760971</v>
       </c>
-      <c r="I35" s="4" t="n">
+      <c r="I37" s="4" t="n">
         <v>0.7258064516129032</v>
       </c>
-      <c r="J35" s="4" t="n">
+      <c r="J37" s="4" t="n">
         <v>0.45</v>
       </c>
-      <c r="K35" s="4" t="n">
+      <c r="K37" s="4" t="n">
         <v>0.5555555555555557</v>
       </c>
-      <c r="L35" s="4" t="n">
+      <c r="L37" s="4" t="n">
         <v>0.83</v>
       </c>
-      <c r="M35" s="4" t="n">
+      <c r="M37" s="4" t="n">
         <v>0.6974789915966386</v>
       </c>
-      <c r="N35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="5" t="n">
+      <c r="N37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="5" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O35"/>
+  <autoFilter ref="A1:O37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13287,7 +13711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -14296,12 +14720,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>microsoft/microsoft-decision-1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Microsoft Decision 1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -14313,13 +14737,13 @@
         <v>1000</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.7603515978750895</v>
+        <v>0.9079095915191101</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>780</v>
+        <v>920</v>
       </c>
       <c r="H29" s="4" t="n">
         <v>0</v>
@@ -14331,12 +14755,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>microsoft/microsoft-decision-1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Microsoft Decision 1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -14348,13 +14772,13 @@
         <v>1000</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.744</v>
+        <v>0.887</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.7113942857254609</v>
+        <v>0.8758736466373309</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>744</v>
+        <v>887</v>
       </c>
       <c r="H30" s="4" t="n">
         <v>0</v>
@@ -14366,12 +14790,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>microsoft/microsoft-decision-1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Microsoft Decision 1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -14383,13 +14807,13 @@
         <v>2000</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.762</v>
+        <v>0.9035</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.736163325053324</v>
+        <v>0.8919585061895788</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>1524</v>
+        <v>1807</v>
       </c>
       <c r="H31" s="4" t="n">
         <v>0</v>
@@ -14401,12 +14825,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -14418,16 +14842,16 @@
         <v>1000</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.465</v>
+        <v>0.78</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.5053205391654078</v>
+        <v>0.7603515978750895</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>465</v>
+        <v>780</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.322</v>
+        <v>0</v>
       </c>
       <c r="I32" s="5" t="n">
         <v>60</v>
@@ -14436,12 +14860,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -14453,16 +14877,16 @@
         <v>1000</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.606</v>
+        <v>0.744</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.5671517703461975</v>
+        <v>0.7113942857254609</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>606</v>
+        <v>744</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="I33" s="5" t="n">
         <v>60</v>
@@ -14471,12 +14895,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -14488,16 +14912,16 @@
         <v>2000</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.5355</v>
+        <v>0.762</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.5411026333400099</v>
+        <v>0.736163325053324</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>1071</v>
+        <v>1524</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.165</v>
+        <v>0</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>60</v>
@@ -14506,12 +14930,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -14523,16 +14947,16 @@
         <v>1000</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.738</v>
+        <v>0.465</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.7285750142849275</v>
+        <v>0.5053205391654078</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>738</v>
+        <v>465</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.042</v>
+        <v>0.322</v>
       </c>
       <c r="I35" s="5" t="n">
         <v>60</v>
@@ -14541,12 +14965,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -14558,16 +14982,16 @@
         <v>1000</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.737</v>
+        <v>0.606</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.712693713084553</v>
+        <v>0.5671517703461975</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>737</v>
+        <v>606</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="I36" s="5" t="n">
         <v>60</v>
@@ -14576,12 +15000,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -14593,16 +15017,16 @@
         <v>2000</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.7375</v>
+        <v>0.5355</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0.7216311867724771</v>
+        <v>0.5411026333400099</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1475</v>
+        <v>1071</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0.021</v>
+        <v>0.165</v>
       </c>
       <c r="I37" s="5" t="n">
         <v>60</v>
@@ -14611,12 +15035,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -14628,16 +15052,16 @@
         <v>1000</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.509</v>
+        <v>0.738</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0.5867378280355483</v>
+        <v>0.7285750142849275</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>509</v>
+        <v>738</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0.343</v>
+        <v>0.042</v>
       </c>
       <c r="I38" s="5" t="n">
         <v>60</v>
@@ -14646,12 +15070,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -14663,16 +15087,16 @@
         <v>1000</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.711</v>
+        <v>0.737</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.7031769757373104</v>
+        <v>0.712693713084553</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>711</v>
+        <v>737</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="I39" s="5" t="n">
         <v>60</v>
@@ -14681,12 +15105,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -14698,16 +15122,16 @@
         <v>2000</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.61</v>
+        <v>0.7375</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.6504937686437986</v>
+        <v>0.7216311867724771</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>1220</v>
+        <v>1475</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.202</v>
+        <v>0.021</v>
       </c>
       <c r="I40" s="5" t="n">
         <v>60</v>
@@ -14716,12 +15140,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -14733,16 +15157,16 @@
         <v>1000</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.529</v>
+        <v>0.509</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.5140122481389001</v>
+        <v>0.5867378280355483</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>529</v>
+        <v>509</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0</v>
+        <v>0.343</v>
       </c>
       <c r="I41" s="5" t="n">
         <v>60</v>
@@ -14751,12 +15175,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -14768,16 +15192,16 @@
         <v>1000</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.398</v>
+        <v>0.711</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.3758955615145875</v>
+        <v>0.7031769757373104</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>398</v>
+        <v>711</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="I42" s="5" t="n">
         <v>60</v>
@@ -14786,12 +15210,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -14803,16 +15227,16 @@
         <v>2000</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.4635</v>
+        <v>0.61</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.4473337487719194</v>
+        <v>0.6504937686437986</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>927</v>
+        <v>1220</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>0</v>
+        <v>0.202</v>
       </c>
       <c r="I43" s="5" t="n">
         <v>60</v>
@@ -14821,12 +15245,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -14838,13 +15262,13 @@
         <v>1000</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.842</v>
+        <v>0.529</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.8314865753296514</v>
+        <v>0.5140122481389001</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>842</v>
+        <v>529</v>
       </c>
       <c r="H44" s="4" t="n">
         <v>0</v>
@@ -14856,12 +15280,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -14873,13 +15297,13 @@
         <v>1000</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.398</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.8034449936517111</v>
+        <v>0.3758955615145875</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>815</v>
+        <v>398</v>
       </c>
       <c r="H45" s="4" t="n">
         <v>0</v>
@@ -14891,12 +15315,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -14908,13 +15332,13 @@
         <v>2000</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.8285</v>
+        <v>0.4635</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.8179267929293625</v>
+        <v>0.4473337487719194</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>1657</v>
+        <v>927</v>
       </c>
       <c r="H46" s="4" t="n">
         <v>0</v>
@@ -14926,12 +15350,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -14943,16 +15367,16 @@
         <v>1000</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.715</v>
+        <v>0.842</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>0.7079848008862988</v>
+        <v>0.8314865753296514</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>715</v>
+        <v>842</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="I47" s="5" t="n">
         <v>60</v>
@@ -14961,12 +15385,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -14978,16 +15402,16 @@
         <v>1000</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.661</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>0.6593342425290085</v>
+        <v>0.8034449936517111</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>661</v>
+        <v>815</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I48" s="5" t="n">
         <v>60</v>
@@ -14996,12 +15420,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -15013,16 +15437,16 @@
         <v>2000</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.8285</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0.6845822094887644</v>
+        <v>0.8179267929293625</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>1376</v>
+        <v>1657</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I49" s="5" t="n">
         <v>60</v>
@@ -15031,12 +15455,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -15048,16 +15472,16 @@
         <v>1000</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.868</v>
+        <v>0.715</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.8492172170319239</v>
+        <v>0.7079848008862988</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>868</v>
+        <v>715</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="I50" s="5" t="n">
         <v>60</v>
@@ -15066,12 +15490,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -15083,16 +15507,16 @@
         <v>1000</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.831</v>
+        <v>0.661</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>0.8000988567676002</v>
+        <v>0.6593342425290085</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>831</v>
+        <v>661</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I51" s="5" t="n">
         <v>60</v>
@@ -15101,12 +15525,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -15118,16 +15542,16 @@
         <v>2000</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.8495</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.8278820044607954</v>
+        <v>0.6845822094887644</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>1699</v>
+        <v>1376</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I52" s="5" t="n">
         <v>60</v>
@@ -15136,12 +15560,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>openai/gpt-6-luna</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GPT-6 Luna</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -15153,13 +15577,13 @@
         <v>1000</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.863</v>
+        <v>0.868</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.8453007221886907</v>
+        <v>0.8492172170319239</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="H53" s="4" t="n">
         <v>0</v>
@@ -15171,12 +15595,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>openai/gpt-6-luna</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GPT-6 Luna</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -15188,13 +15612,13 @@
         <v>1000</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.839</v>
+        <v>0.831</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>0.8091186705197505</v>
+        <v>0.8000988567676002</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="H54" s="4" t="n">
         <v>0</v>
@@ -15206,12 +15630,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>openai/gpt-6-luna</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GPT-6 Luna</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -15223,13 +15647,13 @@
         <v>2000</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0.851</v>
+        <v>0.8495</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>0.829884804655604</v>
+        <v>0.8278820044607954</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>1702</v>
+        <v>1699</v>
       </c>
       <c r="H55" s="4" t="n">
         <v>0</v>
@@ -15241,12 +15665,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-6-luna</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-6 Luna</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -15258,16 +15682,16 @@
         <v>1000</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.863</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>0.7992131261387427</v>
+        <v>0.8453007221886907</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>809</v>
+        <v>863</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I56" s="5" t="n">
         <v>60</v>
@@ -15276,12 +15700,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-6-luna</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-6 Luna</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -15293,13 +15717,13 @@
         <v>1000</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.794</v>
+        <v>0.839</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>0.7717528819109728</v>
+        <v>0.8091186705197505</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>794</v>
+        <v>839</v>
       </c>
       <c r="H57" s="4" t="n">
         <v>0</v>
@@ -15311,12 +15735,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-6-luna</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-6 Luna</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -15328,16 +15752,16 @@
         <v>2000</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0.8015</v>
+        <v>0.851</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>0.7855676169719019</v>
+        <v>0.829884804655604</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>1603</v>
+        <v>1702</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I58" s="5" t="n">
         <v>60</v>
@@ -15346,12 +15770,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -15363,13 +15787,13 @@
         <v>1000</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.796</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>0.7792340968020122</v>
+        <v>0.7992131261387427</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>796</v>
+        <v>809</v>
       </c>
       <c r="H59" s="4" t="n">
         <v>0.02</v>
@@ -15381,12 +15805,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -15398,16 +15822,16 @@
         <v>1000</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>0.76</v>
+        <v>0.794</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>0.7439524644750251</v>
+        <v>0.7717528819109728</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>760</v>
+        <v>794</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I60" s="5" t="n">
         <v>60</v>
@@ -15416,12 +15840,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -15433,16 +15857,16 @@
         <v>2000</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>0.778</v>
+        <v>0.8015</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>0.7614406146917927</v>
+        <v>0.7855676169719019</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>1556</v>
+        <v>1603</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="I61" s="5" t="n">
         <v>60</v>
@@ -15451,12 +15875,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -15468,16 +15892,16 @@
         <v>1000</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>0.882</v>
+        <v>0.796</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>0.8710472576948233</v>
+        <v>0.7792340968020122</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>882</v>
+        <v>796</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I62" s="5" t="n">
         <v>60</v>
@@ -15486,12 +15910,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -15503,16 +15927,16 @@
         <v>1000</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>0.846</v>
+        <v>0.76</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>0.8354346192098669</v>
+        <v>0.7439524644750251</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>846</v>
+        <v>760</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I63" s="5" t="n">
         <v>60</v>
@@ -15521,12 +15945,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -15538,16 +15962,16 @@
         <v>2000</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>0.864</v>
+        <v>0.778</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>0.8523414150627505</v>
+        <v>0.7614406146917927</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>1728</v>
+        <v>1556</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I64" s="5" t="n">
         <v>60</v>
@@ -15556,12 +15980,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -15573,13 +15997,13 @@
         <v>1000</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>0.858</v>
+        <v>0.882</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>0.846487306452871</v>
+        <v>0.8710472576948233</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>858</v>
+        <v>882</v>
       </c>
       <c r="H65" s="4" t="n">
         <v>0</v>
@@ -15591,12 +16015,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -15608,16 +16032,16 @@
         <v>1000</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>0.797</v>
+        <v>0.846</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>0.7859849948864567</v>
+        <v>0.8354346192098669</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>797</v>
+        <v>846</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I66" s="5" t="n">
         <v>60</v>
@@ -15626,12 +16050,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -15643,23 +16067,128 @@
         <v>2000</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>0.8275</v>
+        <v>0.864</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>0.8155753958777252</v>
+        <v>0.8523414150627505</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>1655</v>
+        <v>1728</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I67" s="5" t="n">
         <v>60</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>0.858</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>0.846487306452871</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>858</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ko</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>0.7859849948864567</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>797</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>overall</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>0.8275</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>0.8155753958777252</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>1655</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I67"/>
+  <autoFilter ref="A1:I70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15670,7 +16199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -16163,590 +16692,635 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>microsoft/microsoft-decision-1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ministral 3 14B</t>
+          <t>Microsoft Decision 1</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.824</v>
+        <v>0.927</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.768</v>
+        <v>0.916</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>674</v>
+        <v>867</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.674</v>
+        <v>0.867</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.106</v>
+        <v>0.053</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="L11" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.15</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ministral 3 3B</t>
+          <t>Ministral 3 14B</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.651</v>
+        <v>0.824</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.43</v>
+        <v>0.768</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>361</v>
+        <v>674</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.361</v>
+        <v>0.674</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.104</v>
+        <v>0.106</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>245</v>
+        <v>70</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.245</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>290</v>
+        <v>150</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.29</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ministral 3 8B</t>
+          <t>Ministral 3 3B</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.763</v>
+        <v>0.651</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.695</v>
+        <v>0.43</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>619</v>
+        <v>361</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.619</v>
+        <v>0.361</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.119</v>
+        <v>0.104</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>118</v>
+        <v>245</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.118</v>
+        <v>0.245</v>
       </c>
       <c r="L13" t="n">
-        <v>144</v>
+        <v>290</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.144</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mistral Small 4</t>
+          <t>Ministral 3 8B</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.7</v>
+        <v>0.763</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.519</v>
+        <v>0.695</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>460</v>
+        <v>619</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.46</v>
+        <v>0.619</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.049</v>
+        <v>0.119</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>251</v>
+        <v>118</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.251</v>
+        <v>0.118</v>
       </c>
       <c r="L14" t="n">
-        <v>240</v>
+        <v>144</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.24</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GPT-4.1 Nano</t>
+          <t>Mistral Small 4</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.731</v>
+        <v>0.7</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.505</v>
+        <v>0.519</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>329</v>
+        <v>460</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.329</v>
+        <v>0.46</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>200</v>
+        <v>49</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.2</v>
+        <v>0.049</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>69</v>
+        <v>251</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.251</v>
       </c>
       <c r="L15" t="n">
-        <v>402</v>
+        <v>240</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.402</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GPT-5 Nano</t>
+          <t>GPT-4.1 Nano</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.863</v>
+        <v>0.731</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.833</v>
+        <v>0.505</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>760</v>
+        <v>329</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.76</v>
+        <v>0.329</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.082</v>
+        <v>0.2</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.055</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>103</v>
+        <v>402</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.103</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GPT-5.4 Nano</t>
+          <t>GPT-5 Nano</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.718</v>
+        <v>0.863</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.612</v>
+        <v>0.833</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>547</v>
+        <v>760</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.547</v>
+        <v>0.76</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.168</v>
+        <v>0.082</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.114</v>
+        <v>0.055</v>
       </c>
       <c r="L17" t="n">
-        <v>171</v>
+        <v>103</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.171</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GPT-5.6 Luna</t>
+          <t>GPT-5.4 Nano</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.895</v>
+        <v>0.718</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.866</v>
+        <v>0.612</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>797</v>
+        <v>547</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.797</v>
+        <v>0.547</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>71</v>
+        <v>168</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.168</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>34</v>
+        <v>114</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.034</v>
+        <v>0.114</v>
       </c>
       <c r="L18" t="n">
-        <v>98</v>
+        <v>171</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.098</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>openai/gpt-6-luna</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GPT-6 Luna</t>
+          <t>GPT-5.6 Luna</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.902</v>
+        <v>0.895</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0.866</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.802</v>
+        <v>0.797</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.061</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.037</v>
+        <v>0.034</v>
       </c>
       <c r="L19" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.1</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
+          <t>openai/gpt-6-luna</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Qwen3 30B A3B Instruct 2507</t>
+          <t>GPT-6 Luna</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.865</v>
+        <v>0.902</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.866</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>734</v>
+        <v>802</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.734</v>
+        <v>0.802</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.075</v>
+        <v>0.061</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.06</v>
+        <v>0.037</v>
       </c>
       <c r="L20" t="n">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.131</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>qwen/qwen3-30b-a3b-instruct-2507</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Qwen3.7 Flash</t>
+          <t>Qwen3 30B A3B Instruct 2507</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.832</v>
+        <v>0.865</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.77</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>694</v>
+        <v>734</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.694</v>
+        <v>0.734</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.102</v>
+        <v>0.075</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.066</v>
+        <v>0.06</v>
       </c>
       <c r="L21" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.138</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Qwen3.8 Flash</t>
+          <t>Qwen3.7 Flash</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.91</v>
+        <v>0.832</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.887</v>
+        <v>0.77</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>819</v>
+        <v>694</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.819</v>
+        <v>0.694</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.063</v>
+        <v>0.102</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.027</v>
+        <v>0.066</v>
       </c>
       <c r="L22" t="n">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.091</v>
+        <v>0.138</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flash</t>
+          <t>qwen/qwen3.8-flash</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GLM 5.3 Flash</t>
+          <t>Qwen3.8 Flash</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="D23" s="4" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0.887</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>819</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="L23" t="n">
+        <v>91</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>0.091</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>GLM 5.3 Flash</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D24" s="4" t="n">
         <v>0.867</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E24" s="4" t="n">
         <v>0.822</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F24" s="5" t="n">
         <v>761</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>0.761</v>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="H24" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="I24" s="4" t="n">
         <v>0.097</v>
       </c>
-      <c r="J23" s="5" t="n">
+      <c r="J24" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="K23" s="4" t="n">
+      <c r="K24" s="4" t="n">
         <v>0.036</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L24" t="n">
         <v>106</v>
       </c>
-      <c r="M23" s="4" t="n">
+      <c r="M24" s="4" t="n">
         <v>0.106</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M23"/>
+  <autoFilter ref="A1:M24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
